--- a/WorkBook/Jutland Gun Resolve.xlsx
+++ b/WorkBook/Jutland Gun Resolve.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="损伤表" sheetId="1" r:id="rId1"/>
     <sheet name="命中表 " sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="命中修正表" sheetId="4" r:id="rId3"/>
+    <sheet name="甲弹表" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="182">
   <si>
     <r>
       <rPr>
@@ -106,16 +107,16 @@
     </r>
   </si>
   <si>
-    <t>0-10</t>
-  </si>
-  <si>
-    <t>10-20</t>
-  </si>
-  <si>
-    <t>20-30</t>
-  </si>
-  <si>
-    <t>30-40</t>
+    <t>0-10°</t>
+  </si>
+  <si>
+    <t>10-20°</t>
+  </si>
+  <si>
+    <t>20-30°</t>
+  </si>
+  <si>
+    <t>30-40°</t>
   </si>
   <si>
     <t>12"/45 (30.5 cm) Mark X</t>
@@ -166,6 +167,9 @@
     <t>28 cm/50 (11") SK L/50</t>
   </si>
   <si>
+    <t>21000*</t>
+  </si>
+  <si>
     <t>30.5 cm/50 (12") SK L/50</t>
   </si>
   <si>
@@ -178,28 +182,249 @@
     <t>APC L/3,5</t>
   </si>
   <si>
-    <t>考虑：大角度入射，RN右移一列?</t>
-  </si>
-  <si>
     <t>致命打击</t>
   </si>
   <si>
+    <t>再1D6，若此值小于等于命中骰值-3，则生效</t>
+  </si>
+  <si>
+    <t>注：为了绘图方便，部分数据做了取整处理</t>
+  </si>
+  <si>
     <t>追加打击</t>
   </si>
   <si>
+    <t>再投一骰，损伤再加上此骰查表结果</t>
+  </si>
+  <si>
+    <t>*：毛奇19500</t>
+  </si>
+  <si>
     <t>炮塔命中</t>
   </si>
   <si>
+    <t>查甲弹表，击穿则1D10</t>
+  </si>
+  <si>
+    <t>解释：如13.4/45H对装甲6命中，骰值5+6=11致命打击，
+再1D6，若结果小于等于2（5-3），则进入致命打击表</t>
+  </si>
+  <si>
+    <t>炮座炮廓命中</t>
+  </si>
+  <si>
+    <t>特殊损伤</t>
+  </si>
+  <si>
+    <t>指挥塔、水中弹、炮管、火控</t>
+  </si>
+  <si>
+    <t>1D10</t>
+  </si>
+  <si>
+    <t>特殊损伤结果</t>
+  </si>
+  <si>
+    <t>效果</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>水中弹</t>
+  </si>
+  <si>
+    <t>船体受损3D20，航速降低1D6</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>船体受损2D20，航速降低1D4</t>
+  </si>
+  <si>
+    <t>3 - 4</t>
+  </si>
+  <si>
+    <t>船体受损1D20</t>
+  </si>
+  <si>
+    <t>5 - 6</t>
+  </si>
+  <si>
+    <t>舰桥</t>
+  </si>
+  <si>
+    <t>查甲弹表，击穿则 转向失灵+不能开火+不能通讯 1D6回合</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>火控</t>
+  </si>
+  <si>
+    <t>命中率降低 1D6，持续 1D4 回合</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>船舵</t>
+  </si>
+  <si>
+    <t>转向失灵 1D4 回合</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>通讯</t>
+  </si>
+  <si>
+    <t>不能通讯（发出） 1D4 回合</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>炮管</t>
+  </si>
+  <si>
+    <t>向敌侧随机一座炮塔受损，射数-5</t>
+  </si>
+  <si>
+    <t>1 - 4</t>
+  </si>
+  <si>
+    <t>炮座命中</t>
+  </si>
+  <si>
+    <t>先查甲弹表，再执行一次炮塔命中1D10判定</t>
+  </si>
+  <si>
+    <t>炮廓命中（英）</t>
+  </si>
+  <si>
+    <t>船体受损2D10，向敌侧副炮受损50%</t>
+  </si>
+  <si>
+    <t>炮廓命中（德）</t>
+  </si>
+  <si>
+    <t>船体受损1D10，向敌侧副炮受损20%</t>
+  </si>
+  <si>
+    <t>7 - 8</t>
+  </si>
+  <si>
     <t>炮廓命中</t>
   </si>
   <si>
-    <t>特殊损伤</t>
-  </si>
-  <si>
-    <t>指挥塔、水中弹、炮管、火控</t>
+    <t>船体受损1D6，向敌侧副炮受损10%</t>
+  </si>
+  <si>
+    <t>9 - 10</t>
+  </si>
+  <si>
+    <t>副炮命中</t>
+  </si>
+  <si>
+    <t>向敌侧副炮受损10%</t>
+  </si>
+  <si>
+    <t>1 - 3</t>
+  </si>
+  <si>
+    <t>诱爆药库（英）</t>
+  </si>
+  <si>
+    <t>沉没</t>
+  </si>
+  <si>
+    <t>4 - 5</t>
+  </si>
+  <si>
+    <t>引燃发射药（英）</t>
+  </si>
+  <si>
+    <t>船体受损2D10，随机一炮塔彻底受损</t>
+  </si>
+  <si>
+    <t>6 - 8</t>
+  </si>
+  <si>
+    <t>炮塔损毁</t>
+  </si>
+  <si>
+    <t>向敌侧随机一炮塔彻底受损</t>
+  </si>
+  <si>
+    <t>炮塔卡死</t>
+  </si>
+  <si>
+    <t>向敌侧随机一炮塔受损 1D6 回合</t>
+  </si>
+  <si>
+    <t>诱爆药库（德）</t>
+  </si>
+  <si>
+    <t>2 - 3</t>
+  </si>
+  <si>
+    <t>引燃发射药（德）</t>
+  </si>
+  <si>
+    <t>船体受损2D20，随机两相邻炮塔彻底受损</t>
+  </si>
+  <si>
+    <t>命中弹药库</t>
+  </si>
+  <si>
+    <t>动力受损</t>
+  </si>
+  <si>
+    <t>船体受损1D20，航速降低1D4</t>
+  </si>
+  <si>
+    <t>无需查表，执行一次炮塔命中1D10判定</t>
+  </si>
+  <si>
+    <t>引燃副炮</t>
+  </si>
+  <si>
+    <t>船体受损1D20，向敌侧副炮受损50%</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>火控瘫痪</t>
+  </si>
+  <si>
+    <t>不能开火 1D4 回合</t>
+  </si>
+  <si>
+    <t>转向机构命中</t>
+  </si>
+  <si>
+    <t>不能通讯 1D4 回合</t>
+  </si>
+  <si>
+    <t>进水</t>
+  </si>
+  <si>
+    <t>船体受损 1D10</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>命中率</t>
     </r>
     <r>
@@ -214,46 +439,579 @@
     </r>
   </si>
   <si>
-    <t>1D10</t>
-  </si>
-  <si>
-    <t>修正</t>
+    <t>命中数</t>
+  </si>
+  <si>
+    <t>修正骰</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>+ 20%</t>
-  </si>
-  <si>
-    <t>向上取整</t>
+    <t>1D4 -2</t>
   </si>
   <si>
     <t>1 - 2</t>
   </si>
   <si>
-    <t>+ 10%</t>
-  </si>
-  <si>
-    <t>3 - 6</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>7 - 8</t>
-  </si>
-  <si>
-    <t>- 10%</t>
-  </si>
-  <si>
-    <t>向下取整</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>- 20%</t>
+    <t>1D6 -3</t>
+  </si>
+  <si>
+    <t>3 - 7</t>
+  </si>
+  <si>
+    <t>2D6 -7</t>
+  </si>
+  <si>
+    <t>8 - 12</t>
+  </si>
+  <si>
+    <t>2D10 -11</t>
+  </si>
+  <si>
+    <t>13 - 20</t>
+  </si>
+  <si>
+    <t>2D12 -13</t>
+  </si>
+  <si>
+    <t>21 - 30</t>
+  </si>
+  <si>
+    <t>3D10 -16</t>
+  </si>
+  <si>
+    <t>31 - 42</t>
+  </si>
+  <si>
+    <t>2D20 -21</t>
+  </si>
+  <si>
+    <t>43+</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>修正值</t>
+  </si>
+  <si>
+    <t>目标规避机动、大幅转向（英）</t>
+  </si>
+  <si>
+    <t>-3%</t>
+  </si>
+  <si>
+    <t>目标规避机动、大幅转向（德）</t>
+  </si>
+  <si>
+    <t>-2%</t>
+  </si>
+  <si>
+    <t>我舰规避机动、大幅转向</t>
+  </si>
+  <si>
+    <t>双方规避机动、大幅转向</t>
+  </si>
+  <si>
+    <t>-8%</t>
+  </si>
+  <si>
+    <t>对目标纵射</t>
+  </si>
+  <si>
+    <t>+2%</t>
+  </si>
+  <si>
+    <t>我舰纵射</t>
+  </si>
+  <si>
+    <t>我舰被射击</t>
+  </si>
+  <si>
+    <t>-1%</t>
+  </si>
+  <si>
+    <t>目标背光</t>
+  </si>
+  <si>
+    <t>两艘集火</t>
+  </si>
+  <si>
+    <t>三+集火</t>
+  </si>
+  <si>
+    <t>疲劳（德）</t>
+  </si>
+  <si>
+    <t>缺乏训练（BCF）</t>
+  </si>
+  <si>
+    <t>低火控</t>
+  </si>
+  <si>
+    <t>-4%</t>
+  </si>
+  <si>
+    <t>优火控</t>
+  </si>
+  <si>
+    <t>烟雾射击（英）</t>
+  </si>
+  <si>
+    <t>烟雾射击（德）</t>
+  </si>
+  <si>
+    <t>黑夜射击(英）</t>
+  </si>
+  <si>
+    <t>-5%</t>
+  </si>
+  <si>
+    <t>黑夜射击（德）</t>
+  </si>
+  <si>
+    <t>命中率不低于0%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>落弹角</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>FG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>G</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>G</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>FG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>FG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>G</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>EFG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>EFG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DEFG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>FG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>EFG</t>
+    </r>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <r>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>FG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DEFG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>EFG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>FG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>黑色字体：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1D6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+  </si>
+  <si>
+    <t>A:14</t>
+  </si>
+  <si>
+    <r>
+      <t>蓝色字体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1D6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+  </si>
+  <si>
+    <t>B:12</t>
+  </si>
+  <si>
+    <r>
+      <t>红色字体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1D6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+  </si>
+  <si>
+    <t>C:11</t>
+  </si>
+  <si>
+    <t>D:10.5</t>
+  </si>
+  <si>
+    <t>E:9</t>
+  </si>
+  <si>
+    <t>F:8</t>
+  </si>
+  <si>
+    <t>G:7</t>
   </si>
 </sst>
 </file>
@@ -266,7 +1024,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="51">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,9 +1033,72 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -306,28 +1127,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="20"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -351,7 +1160,27 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -520,6 +1349,13 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
@@ -530,13 +1366,30 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="62">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -552,7 +1405,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
+        <fgColor rgb="FF91AADF"/>
         <bgColor theme="4" tint="0.799981688894314"/>
       </patternFill>
     </fill>
@@ -565,12 +1418,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.4"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FF4874CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91AADF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,13 +1459,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
+        <fgColor rgb="FFF4B7BE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE796"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE796"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC91D32"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC91D32"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,12 +1538,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -809,12 +1740,110 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="30">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalDown="1">
@@ -841,17 +1870,6 @@
       <bottom style="thin">
         <color theme="4" tint="0.399975585192419"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -897,15 +1915,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -1102,447 +2111,603 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="34" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="9" fontId="15" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1600,7 +2765,13 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="0091AADF"/>
+      <color rgb="00F4B7BE"/>
+      <color rgb="00FFF3CA"/>
       <color rgb="004874CB"/>
+      <color rgb="00FEE796"/>
+      <color rgb="00FFC000"/>
+      <color rgb="00C91D32"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1861,3212 +3032,4575 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AF60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="32.75" style="15" customWidth="1"/>
-    <col min="2" max="2" width="18.875" style="15" customWidth="1"/>
-    <col min="3" max="6" width="6.375" style="15" customWidth="1"/>
-    <col min="7" max="26" width="3.33333333333333" style="15" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="15"/>
+    <col min="1" max="1" width="32.75" style="42" customWidth="1"/>
+    <col min="2" max="2" width="18.875" style="42" customWidth="1"/>
+    <col min="3" max="6" width="6.375" style="42" customWidth="1"/>
+    <col min="7" max="26" width="3.33333333333333" style="42" customWidth="1"/>
+    <col min="27" max="27" width="9" style="42"/>
+    <col min="28" max="28" width="10.625" style="42" customWidth="1"/>
+    <col min="29" max="29" width="15.625" style="42" customWidth="1"/>
+    <col min="30" max="30" width="9" style="42"/>
+    <col min="31" max="31" width="10.625" style="42" customWidth="1"/>
+    <col min="32" max="32" width="15.625" style="42" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:26">
-      <c r="A1" s="16" t="s">
+    <row r="1" customHeight="1" spans="1:32">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="21" t="s">
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="22"/>
-      <c r="I1" s="65" t="s">
+      <c r="H1" s="49"/>
+      <c r="I1" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="101"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:26">
-      <c r="A2" s="23"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25" t="s">
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="150"/>
+      <c r="AB1" s="151"/>
+      <c r="AC1" s="151"/>
+      <c r="AD1" s="151"/>
+      <c r="AE1" s="151"/>
+      <c r="AF1" s="151"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:32">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="55">
         <v>1</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="56">
         <v>2</v>
       </c>
-      <c r="I2" s="68">
+      <c r="I2" s="115">
         <v>3</v>
       </c>
-      <c r="J2" s="69">
+      <c r="J2" s="116">
         <v>4</v>
       </c>
-      <c r="K2" s="70">
+      <c r="K2" s="117">
         <v>5</v>
       </c>
-      <c r="L2" s="71">
+      <c r="L2" s="118">
         <v>6</v>
       </c>
-      <c r="M2" s="71">
+      <c r="M2" s="118">
         <v>7</v>
       </c>
-      <c r="N2" s="71">
+      <c r="N2" s="118">
         <v>8</v>
       </c>
-      <c r="O2" s="71">
+      <c r="O2" s="118">
         <v>9</v>
       </c>
-      <c r="P2" s="71">
+      <c r="P2" s="118">
         <v>10</v>
       </c>
-      <c r="Q2" s="71">
+      <c r="Q2" s="118">
         <v>11</v>
       </c>
-      <c r="R2" s="71">
+      <c r="R2" s="118">
         <v>12</v>
       </c>
-      <c r="S2" s="71">
+      <c r="S2" s="118">
         <v>13</v>
       </c>
-      <c r="T2" s="71">
+      <c r="T2" s="118">
         <v>14</v>
       </c>
-      <c r="U2" s="71">
+      <c r="U2" s="118">
         <v>15</v>
       </c>
-      <c r="V2" s="71">
+      <c r="V2" s="118">
         <v>16</v>
       </c>
-      <c r="W2" s="71">
+      <c r="W2" s="118">
         <v>17</v>
       </c>
-      <c r="X2" s="71">
+      <c r="X2" s="118">
         <v>18</v>
       </c>
-      <c r="Y2" s="71">
+      <c r="Y2" s="118">
         <v>19</v>
       </c>
-      <c r="Z2" s="102">
+      <c r="Z2" s="152">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:26">
-      <c r="A3" s="30" t="s">
+      <c r="AB2" s="151"/>
+      <c r="AC2" s="151"/>
+      <c r="AD2" s="151"/>
+      <c r="AE2" s="151"/>
+      <c r="AF2" s="151"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:32">
+      <c r="A3" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="59">
         <v>10500</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="60">
         <v>15000</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="60">
         <v>18000</v>
       </c>
-      <c r="F3" s="34">
-        <v>18850</v>
-      </c>
-      <c r="G3" s="35">
+      <c r="F3" s="61">
+        <v>18500</v>
+      </c>
+      <c r="G3" s="62">
         <v>1</v>
       </c>
-      <c r="H3" s="36">
+      <c r="H3" s="63">
         <v>2</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73">
+      <c r="I3" s="119"/>
+      <c r="J3" s="120">
         <v>6</v>
       </c>
-      <c r="K3" s="74">
+      <c r="K3" s="121">
         <v>6</v>
       </c>
-      <c r="L3" s="75">
+      <c r="L3" s="122">
         <v>6</v>
       </c>
-      <c r="M3" s="72">
+      <c r="M3" s="119">
         <v>5</v>
       </c>
-      <c r="N3" s="72">
+      <c r="N3" s="119">
         <v>5</v>
       </c>
-      <c r="O3" s="72">
+      <c r="O3" s="119">
         <v>4</v>
       </c>
-      <c r="P3" s="76">
+      <c r="P3" s="123">
         <v>5</v>
       </c>
-      <c r="Q3" s="100">
+      <c r="Q3" s="149">
         <v>5</v>
       </c>
-      <c r="R3" s="74">
+      <c r="R3" s="121">
         <v>4</v>
       </c>
-      <c r="S3" s="75">
+      <c r="S3" s="122">
         <v>4</v>
       </c>
-      <c r="T3" s="72">
+      <c r="T3" s="119">
         <v>3</v>
       </c>
-      <c r="U3" s="72">
+      <c r="U3" s="119">
         <v>2</v>
       </c>
-      <c r="V3" s="72" t="s">
+      <c r="V3" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="W3" s="72" t="s">
+      <c r="W3" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="X3" s="72" t="s">
+      <c r="X3" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="Y3" s="72" t="s">
+      <c r="Y3" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="Z3" s="36" t="s">
+      <c r="Z3" s="63" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:26">
-      <c r="A4" s="37" t="s">
+      <c r="AB3" s="153"/>
+      <c r="AC3" s="153"/>
+      <c r="AD3" s="154"/>
+      <c r="AE3" s="153"/>
+      <c r="AF3" s="153"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:32">
+      <c r="A4" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="66">
         <v>10500</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="67">
         <v>15000</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="67">
         <v>18000</v>
       </c>
-      <c r="F4" s="41">
-        <v>18850</v>
-      </c>
-      <c r="G4" s="42">
+      <c r="F4" s="68">
+        <v>18500</v>
+      </c>
+      <c r="G4" s="69">
         <v>1</v>
       </c>
-      <c r="H4" s="43">
+      <c r="H4" s="70">
         <v>2</v>
       </c>
-      <c r="I4" s="47"/>
-      <c r="J4" s="77">
+      <c r="I4" s="74"/>
+      <c r="J4" s="124">
         <v>6</v>
       </c>
-      <c r="K4" s="78">
+      <c r="K4" s="125">
         <v>6</v>
       </c>
-      <c r="L4" s="79">
+      <c r="L4" s="126">
         <v>6</v>
       </c>
-      <c r="M4" s="47">
+      <c r="M4" s="74">
         <v>5</v>
       </c>
-      <c r="N4" s="47">
+      <c r="N4" s="74">
         <v>5</v>
       </c>
-      <c r="O4" s="47">
+      <c r="O4" s="74">
         <v>4</v>
       </c>
-      <c r="P4" s="80">
+      <c r="P4" s="127">
         <v>5</v>
       </c>
-      <c r="Q4" s="82">
+      <c r="Q4" s="129">
         <v>5</v>
       </c>
-      <c r="R4" s="78">
+      <c r="R4" s="125">
         <v>4</v>
       </c>
-      <c r="S4" s="79">
+      <c r="S4" s="126">
         <v>4</v>
       </c>
-      <c r="T4" s="47">
+      <c r="T4" s="74">
         <v>3</v>
       </c>
-      <c r="U4" s="47">
+      <c r="U4" s="74">
         <v>2</v>
       </c>
-      <c r="V4" s="42" t="s">
+      <c r="V4" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="W4" s="47" t="s">
+      <c r="W4" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="X4" s="47" t="s">
+      <c r="X4" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Y4" s="47" t="s">
+      <c r="Y4" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="43" t="s">
+      <c r="Z4" s="70" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:26">
-      <c r="A5" s="37" t="s">
+      <c r="AB4" s="153"/>
+      <c r="AC4" s="153"/>
+      <c r="AD4" s="154"/>
+      <c r="AE4" s="153"/>
+      <c r="AF4" s="153"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:32">
+      <c r="A5" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="39">
+      <c r="C5" s="66">
         <v>13500</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="67">
         <v>19500</v>
       </c>
-      <c r="E5" s="40">
-        <v>21200</v>
-      </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="42">
+      <c r="E5" s="67">
+        <v>21000</v>
+      </c>
+      <c r="F5" s="71"/>
+      <c r="G5" s="69">
         <v>1</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="70">
         <v>2</v>
       </c>
-      <c r="I5" s="47"/>
-      <c r="J5" s="77">
+      <c r="I5" s="74"/>
+      <c r="J5" s="124">
         <v>6</v>
       </c>
-      <c r="K5" s="78">
+      <c r="K5" s="125">
         <v>6</v>
       </c>
-      <c r="L5" s="79">
+      <c r="L5" s="126">
         <v>6</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="74">
         <v>5</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="74">
         <v>5</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="74">
         <v>4</v>
       </c>
-      <c r="P5" s="80">
+      <c r="P5" s="127">
         <v>5</v>
       </c>
-      <c r="Q5" s="82">
+      <c r="Q5" s="129">
         <v>5</v>
       </c>
-      <c r="R5" s="78">
+      <c r="R5" s="125">
         <v>5</v>
       </c>
-      <c r="S5" s="79">
+      <c r="S5" s="126">
         <v>5</v>
       </c>
-      <c r="T5" s="47">
+      <c r="T5" s="74">
         <v>4</v>
       </c>
-      <c r="U5" s="47">
+      <c r="U5" s="74">
         <v>4</v>
       </c>
-      <c r="V5" s="42" t="s">
+      <c r="V5" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="W5" s="47" t="s">
+      <c r="W5" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="X5" s="47" t="s">
+      <c r="X5" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Y5" s="47" t="s">
+      <c r="Y5" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Z5" s="43" t="s">
+      <c r="Z5" s="70" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:26">
-      <c r="A6" s="37" t="s">
+      <c r="AB5" s="153"/>
+      <c r="AC5" s="153"/>
+      <c r="AD5" s="154"/>
+      <c r="AE5" s="153"/>
+      <c r="AF5" s="153"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:32">
+      <c r="A6" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="66">
         <v>13000</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="67">
         <v>19500</v>
       </c>
-      <c r="E6" s="40">
-        <v>23820</v>
-      </c>
-      <c r="F6" s="44"/>
-      <c r="G6" s="42">
+      <c r="E6" s="67">
+        <v>23500</v>
+      </c>
+      <c r="F6" s="71"/>
+      <c r="G6" s="69">
         <v>2</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="70">
         <v>4</v>
       </c>
-      <c r="I6" s="47"/>
-      <c r="J6" s="81">
+      <c r="I6" s="74"/>
+      <c r="J6" s="128">
         <v>9</v>
       </c>
-      <c r="K6" s="82">
+      <c r="K6" s="129">
         <v>9</v>
       </c>
-      <c r="L6" s="78">
+      <c r="L6" s="125">
         <v>9</v>
       </c>
-      <c r="M6" s="79">
+      <c r="M6" s="126">
         <v>9</v>
       </c>
-      <c r="N6" s="47">
+      <c r="N6" s="74">
         <v>8</v>
       </c>
-      <c r="O6" s="47">
+      <c r="O6" s="74">
         <v>8</v>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="74">
         <v>7</v>
       </c>
-      <c r="Q6" s="80">
+      <c r="Q6" s="127">
         <v>8</v>
       </c>
-      <c r="R6" s="82">
+      <c r="R6" s="129">
         <v>8</v>
       </c>
-      <c r="S6" s="78">
+      <c r="S6" s="125">
         <v>8</v>
       </c>
-      <c r="T6" s="79">
+      <c r="T6" s="126">
         <v>8</v>
       </c>
-      <c r="U6" s="47">
+      <c r="U6" s="74">
         <v>7</v>
       </c>
-      <c r="V6" s="47">
+      <c r="V6" s="74">
         <v>7</v>
       </c>
-      <c r="W6" s="47" t="s">
+      <c r="W6" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="X6" s="47" t="s">
+      <c r="X6" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Y6" s="47" t="s">
+      <c r="Y6" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Z6" s="43" t="s">
+      <c r="Z6" s="70" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:26">
-      <c r="A7" s="37" t="s">
+      <c r="AB6" s="153"/>
+      <c r="AC6" s="153"/>
+      <c r="AD6" s="154"/>
+      <c r="AE6" s="153"/>
+      <c r="AF6" s="153"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:32">
+      <c r="A7" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="66">
         <v>13000</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="67">
         <v>19500</v>
       </c>
-      <c r="E7" s="40">
-        <v>23740</v>
-      </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="42">
+      <c r="E7" s="67">
+        <v>23500</v>
+      </c>
+      <c r="F7" s="71"/>
+      <c r="G7" s="69">
         <v>2</v>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="70">
         <v>4</v>
       </c>
-      <c r="I7" s="47"/>
-      <c r="J7" s="81">
+      <c r="I7" s="74"/>
+      <c r="J7" s="128">
         <v>9</v>
       </c>
-      <c r="K7" s="82">
+      <c r="K7" s="129">
         <v>9</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="125">
         <v>9</v>
       </c>
-      <c r="M7" s="79">
+      <c r="M7" s="126">
         <v>9</v>
       </c>
-      <c r="N7" s="47">
+      <c r="N7" s="74">
         <v>8</v>
       </c>
-      <c r="O7" s="47">
+      <c r="O7" s="74">
         <v>8</v>
       </c>
-      <c r="P7" s="47">
+      <c r="P7" s="74">
         <v>7</v>
       </c>
-      <c r="Q7" s="80">
+      <c r="Q7" s="127">
         <v>8</v>
       </c>
-      <c r="R7" s="82">
+      <c r="R7" s="129">
         <v>8</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="125">
         <v>8</v>
       </c>
-      <c r="T7" s="79">
+      <c r="T7" s="126">
         <v>8</v>
       </c>
-      <c r="U7" s="47">
+      <c r="U7" s="74">
         <v>7</v>
       </c>
-      <c r="V7" s="47">
+      <c r="V7" s="74">
         <v>7</v>
       </c>
-      <c r="W7" s="47">
+      <c r="W7" s="74">
         <v>5</v>
       </c>
-      <c r="X7" s="47" t="s">
+      <c r="X7" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Y7" s="47" t="s">
+      <c r="Y7" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Z7" s="43" t="s">
+      <c r="Z7" s="70" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:26">
-      <c r="A8" s="37" t="s">
+      <c r="AB7" s="153"/>
+      <c r="AC7" s="153"/>
+      <c r="AD7" s="154"/>
+      <c r="AE7" s="153"/>
+      <c r="AF7" s="153"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:32">
+      <c r="A8" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="66">
         <v>12000</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="67">
         <v>18500</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="67">
         <v>24000</v>
       </c>
-      <c r="F8" s="41">
-        <v>24400</v>
-      </c>
-      <c r="G8" s="42">
+      <c r="F8" s="68">
+        <v>24500</v>
+      </c>
+      <c r="G8" s="69">
         <v>3</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="70">
         <v>5</v>
       </c>
-      <c r="I8" s="47"/>
-      <c r="J8" s="83">
+      <c r="I8" s="74"/>
+      <c r="J8" s="130">
         <v>10</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="127">
         <v>12</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="129">
         <v>12</v>
       </c>
-      <c r="M8" s="78">
+      <c r="M8" s="125">
         <v>12</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="126">
         <v>12</v>
       </c>
-      <c r="O8" s="47">
+      <c r="O8" s="74">
         <v>10</v>
       </c>
-      <c r="P8" s="47">
+      <c r="P8" s="74">
         <v>10</v>
       </c>
-      <c r="Q8" s="47">
+      <c r="Q8" s="74">
         <v>10</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="127">
         <v>11</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="129">
         <v>11</v>
       </c>
-      <c r="T8" s="78">
+      <c r="T8" s="125">
         <v>11</v>
       </c>
-      <c r="U8" s="79">
+      <c r="U8" s="126">
         <v>11</v>
       </c>
-      <c r="V8" s="47">
+      <c r="V8" s="74">
         <v>9</v>
       </c>
-      <c r="W8" s="47">
+      <c r="W8" s="74">
         <v>9</v>
       </c>
-      <c r="X8" s="47" t="s">
+      <c r="X8" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Y8" s="47" t="s">
+      <c r="Y8" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Z8" s="43" t="s">
+      <c r="Z8" s="70" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:26">
-      <c r="A9" s="45" t="s">
+      <c r="AB8" s="153"/>
+      <c r="AC8" s="153"/>
+      <c r="AD8" s="154"/>
+      <c r="AE8" s="153"/>
+      <c r="AF8" s="153"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:32">
+      <c r="A9" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="66">
         <v>12000</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="67">
         <v>18500</v>
       </c>
-      <c r="E9" s="40">
-        <v>23734</v>
-      </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="47">
+      <c r="E9" s="67">
+        <v>23500</v>
+      </c>
+      <c r="F9" s="71"/>
+      <c r="G9" s="74">
         <v>3</v>
       </c>
-      <c r="H9" s="43">
+      <c r="H9" s="70">
         <v>5</v>
       </c>
-      <c r="I9" s="47"/>
-      <c r="J9" s="84">
+      <c r="I9" s="74"/>
+      <c r="J9" s="131">
         <v>10</v>
       </c>
-      <c r="K9" s="85">
+      <c r="K9" s="132">
         <v>12</v>
       </c>
-      <c r="L9" s="86">
+      <c r="L9" s="133">
         <v>12</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="134">
         <v>12</v>
       </c>
-      <c r="N9" s="88">
+      <c r="N9" s="135">
         <v>12</v>
       </c>
-      <c r="O9" s="58">
+      <c r="O9" s="85">
         <v>10</v>
       </c>
-      <c r="P9" s="58">
+      <c r="P9" s="85">
         <v>10</v>
       </c>
-      <c r="Q9" s="58">
+      <c r="Q9" s="85">
         <v>10</v>
       </c>
-      <c r="R9" s="85">
+      <c r="R9" s="132">
         <v>11</v>
       </c>
-      <c r="S9" s="86">
+      <c r="S9" s="133">
         <v>11</v>
       </c>
-      <c r="T9" s="87">
+      <c r="T9" s="134">
         <v>11</v>
       </c>
-      <c r="U9" s="88">
+      <c r="U9" s="135">
         <v>11</v>
       </c>
-      <c r="V9" s="58">
+      <c r="V9" s="85">
         <v>9</v>
       </c>
-      <c r="W9" s="58">
+      <c r="W9" s="85">
         <v>9</v>
       </c>
-      <c r="X9" s="58">
+      <c r="X9" s="85">
         <v>7</v>
       </c>
-      <c r="Y9" s="58" t="s">
+      <c r="Y9" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="Z9" s="59" t="s">
+      <c r="Z9" s="86" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:26">
-      <c r="A10" s="37"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="42"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="42"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="42"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="43"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:26">
-      <c r="A11" s="30" t="s">
+      <c r="AB9" s="153"/>
+      <c r="AC9" s="153"/>
+      <c r="AD9" s="154"/>
+      <c r="AE9" s="154"/>
+      <c r="AF9" s="154"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:32">
+      <c r="A10" s="64"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="69"/>
+      <c r="Q10" s="69"/>
+      <c r="R10" s="69"/>
+      <c r="S10" s="69"/>
+      <c r="T10" s="69"/>
+      <c r="U10" s="69"/>
+      <c r="V10" s="69"/>
+      <c r="W10" s="69"/>
+      <c r="X10" s="69"/>
+      <c r="Y10" s="69"/>
+      <c r="Z10" s="70"/>
+      <c r="AB10" s="153"/>
+      <c r="AC10" s="153"/>
+      <c r="AD10" s="154"/>
+      <c r="AE10" s="154"/>
+      <c r="AF10" s="154"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:32">
+      <c r="A11" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="78">
         <v>12000</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="79">
         <v>17000</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="79">
         <v>21000</v>
       </c>
-      <c r="F11" s="44">
-        <v>22944</v>
-      </c>
-      <c r="G11" s="47" t="s">
+      <c r="F11" s="71">
+        <v>22000</v>
+      </c>
+      <c r="G11" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="70">
         <v>1</v>
       </c>
-      <c r="I11" s="47"/>
-      <c r="J11" s="73">
+      <c r="I11" s="74"/>
+      <c r="J11" s="120">
         <v>4</v>
       </c>
-      <c r="K11" s="74">
+      <c r="K11" s="121">
         <v>4</v>
       </c>
-      <c r="L11" s="75">
+      <c r="L11" s="122">
         <v>4</v>
       </c>
-      <c r="M11" s="72">
+      <c r="M11" s="119">
         <v>3</v>
       </c>
-      <c r="N11" s="72">
+      <c r="N11" s="119">
         <v>3</v>
       </c>
-      <c r="O11" s="72">
+      <c r="O11" s="119">
         <v>2</v>
       </c>
-      <c r="P11" s="76">
+      <c r="P11" s="123">
         <v>3</v>
       </c>
-      <c r="Q11" s="100">
+      <c r="Q11" s="149">
         <v>3</v>
       </c>
-      <c r="R11" s="74">
+      <c r="R11" s="121">
         <v>2</v>
       </c>
-      <c r="S11" s="75">
+      <c r="S11" s="122">
         <v>2</v>
       </c>
-      <c r="T11" s="72">
+      <c r="T11" s="119">
         <v>2</v>
       </c>
-      <c r="U11" s="72">
+      <c r="U11" s="119">
         <v>1</v>
       </c>
-      <c r="V11" s="72" t="s">
+      <c r="V11" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="W11" s="72" t="s">
+      <c r="W11" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="X11" s="72" t="s">
+      <c r="X11" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="Y11" s="72" t="s">
+      <c r="Y11" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="Z11" s="36" t="s">
+      <c r="Z11" s="63" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:26">
-      <c r="A12" s="37" t="s">
+      <c r="AB11" s="153"/>
+      <c r="AC11" s="154"/>
+      <c r="AD11" s="154"/>
+      <c r="AE11" s="154"/>
+      <c r="AF11" s="154"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:28">
+      <c r="A12" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="78">
         <v>12000</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="80">
         <v>17500</v>
       </c>
-      <c r="E12" s="53">
-        <v>21511</v>
-      </c>
-      <c r="F12" s="44"/>
-      <c r="G12" s="42" t="s">
+      <c r="E12" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="71"/>
+      <c r="G12" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="70">
         <v>1</v>
       </c>
-      <c r="I12" s="47"/>
-      <c r="J12" s="77">
+      <c r="I12" s="74"/>
+      <c r="J12" s="124">
         <v>4</v>
       </c>
-      <c r="K12" s="78">
+      <c r="K12" s="125">
         <v>4</v>
       </c>
-      <c r="L12" s="79">
+      <c r="L12" s="126">
         <v>4</v>
       </c>
-      <c r="M12" s="47">
+      <c r="M12" s="74">
         <v>3</v>
       </c>
-      <c r="N12" s="47">
+      <c r="N12" s="74">
         <v>3</v>
       </c>
-      <c r="O12" s="47">
+      <c r="O12" s="74">
         <v>2</v>
       </c>
-      <c r="P12" s="80">
+      <c r="P12" s="127">
         <v>3</v>
       </c>
-      <c r="Q12" s="82">
+      <c r="Q12" s="129">
         <v>3</v>
       </c>
-      <c r="R12" s="78">
+      <c r="R12" s="125">
         <v>3</v>
       </c>
-      <c r="S12" s="79">
+      <c r="S12" s="126">
         <v>3</v>
       </c>
-      <c r="T12" s="47">
+      <c r="T12" s="74">
         <v>2</v>
       </c>
-      <c r="U12" s="47">
+      <c r="U12" s="74">
         <v>2</v>
       </c>
-      <c r="V12" s="42" t="s">
+      <c r="V12" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="W12" s="47" t="s">
+      <c r="W12" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="X12" s="47" t="s">
+      <c r="X12" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Y12" s="47" t="s">
+      <c r="Y12" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Z12" s="43" t="s">
+      <c r="Z12" s="70" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:26">
-      <c r="A13" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="38" t="s">
+      <c r="AB12" s="153"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:28">
+      <c r="A13" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="51">
+      <c r="B13" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="78">
         <v>13000</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="80">
         <v>19000</v>
       </c>
-      <c r="E13" s="53">
-        <v>22857</v>
-      </c>
-      <c r="F13" s="44"/>
-      <c r="G13" s="42">
+      <c r="E13" s="80">
+        <v>20500</v>
+      </c>
+      <c r="F13" s="71"/>
+      <c r="G13" s="69">
         <v>1</v>
       </c>
-      <c r="H13" s="43">
+      <c r="H13" s="70">
         <v>2</v>
       </c>
-      <c r="I13" s="47"/>
-      <c r="J13" s="81">
+      <c r="I13" s="74"/>
+      <c r="J13" s="128">
         <v>5</v>
       </c>
-      <c r="K13" s="82">
+      <c r="K13" s="129">
         <v>5</v>
       </c>
-      <c r="L13" s="78">
+      <c r="L13" s="125">
         <v>5</v>
       </c>
-      <c r="M13" s="79">
+      <c r="M13" s="126">
         <v>5</v>
       </c>
-      <c r="N13" s="47">
+      <c r="N13" s="74">
         <v>4</v>
       </c>
-      <c r="O13" s="47">
+      <c r="O13" s="74">
         <v>4</v>
       </c>
-      <c r="P13" s="47">
+      <c r="P13" s="74">
         <v>3</v>
       </c>
-      <c r="Q13" s="80">
+      <c r="Q13" s="127">
         <v>4</v>
       </c>
-      <c r="R13" s="82">
+      <c r="R13" s="129">
         <v>4</v>
       </c>
-      <c r="S13" s="78">
+      <c r="S13" s="125">
         <v>4</v>
       </c>
-      <c r="T13" s="79">
+      <c r="T13" s="126">
         <v>4</v>
       </c>
-      <c r="U13" s="47">
+      <c r="U13" s="74">
         <v>3</v>
       </c>
-      <c r="V13" s="47">
+      <c r="V13" s="74">
         <v>3</v>
       </c>
-      <c r="W13" s="47" t="s">
+      <c r="W13" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="X13" s="47" t="s">
+      <c r="X13" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Y13" s="47" t="s">
+      <c r="Y13" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="Z13" s="43" t="s">
+      <c r="Z13" s="70" t="s">
         <v>12</v>
       </c>
+      <c r="AB13" s="153"/>
     </row>
     <row r="14" customHeight="1" spans="1:26">
-      <c r="A14" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="54" t="s">
+      <c r="A14" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="55">
+      <c r="B14" s="81" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="82">
         <v>13000</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D14" s="83">
         <v>19500</v>
       </c>
-      <c r="E14" s="56">
-        <v>22146</v>
-      </c>
-      <c r="F14" s="57"/>
-      <c r="G14" s="58">
+      <c r="E14" s="83">
+        <v>22000</v>
+      </c>
+      <c r="F14" s="84"/>
+      <c r="G14" s="85">
         <v>3</v>
       </c>
-      <c r="H14" s="59">
+      <c r="H14" s="86">
         <v>4</v>
       </c>
-      <c r="I14" s="58"/>
-      <c r="J14" s="84">
+      <c r="I14" s="85"/>
+      <c r="J14" s="131">
         <v>9</v>
       </c>
-      <c r="K14" s="89">
+      <c r="K14" s="136">
         <v>9</v>
       </c>
-      <c r="L14" s="85">
+      <c r="L14" s="132">
         <v>11</v>
       </c>
-      <c r="M14" s="86">
+      <c r="M14" s="133">
         <v>11</v>
       </c>
-      <c r="N14" s="87">
+      <c r="N14" s="134">
         <v>11</v>
       </c>
-      <c r="O14" s="88">
+      <c r="O14" s="135">
         <v>11</v>
       </c>
-      <c r="P14" s="58">
+      <c r="P14" s="85">
         <v>9</v>
       </c>
-      <c r="Q14" s="58">
+      <c r="Q14" s="85">
         <v>9</v>
       </c>
-      <c r="R14" s="58">
+      <c r="R14" s="85">
         <v>9</v>
       </c>
-      <c r="S14" s="85">
+      <c r="S14" s="132">
         <v>10</v>
       </c>
-      <c r="T14" s="86">
+      <c r="T14" s="133">
         <v>10</v>
       </c>
-      <c r="U14" s="87">
+      <c r="U14" s="134">
         <v>10</v>
       </c>
-      <c r="V14" s="88">
+      <c r="V14" s="135">
         <v>10</v>
       </c>
-      <c r="W14" s="58">
+      <c r="W14" s="85">
         <v>8</v>
       </c>
-      <c r="X14" s="58">
+      <c r="X14" s="85">
         <v>8</v>
       </c>
-      <c r="Y14" s="58" t="s">
+      <c r="Y14" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="Z14" s="59" t="s">
+      <c r="Z14" s="86" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:26">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="60"/>
-      <c r="U15" s="60"/>
-      <c r="V15" s="60"/>
-      <c r="W15" s="60"/>
-      <c r="X15" s="60"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="60"/>
+      <c r="A15" s="87"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="88"/>
+      <c r="Z15" s="88"/>
     </row>
     <row r="16" customHeight="1" spans="1:26">
-      <c r="A16" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="90"/>
-      <c r="K16" s="91" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="89"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="L16" s="91"/>
-      <c r="M16" s="91"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="92"/>
-      <c r="P16" s="92"/>
-      <c r="Q16" s="61"/>
-      <c r="R16" s="61"/>
-      <c r="S16" s="61"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="61"/>
-      <c r="V16" s="61"/>
-      <c r="W16" s="61"/>
-      <c r="X16" s="61"/>
-      <c r="Y16" s="61"/>
-      <c r="Z16" s="61"/>
+      <c r="L16" s="138"/>
+      <c r="M16" s="138"/>
+      <c r="N16" s="138"/>
+      <c r="O16" s="139" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" s="139"/>
+      <c r="Q16" s="139"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="139"/>
+      <c r="T16" s="139"/>
+      <c r="U16" s="139"/>
+      <c r="V16" s="139"/>
+      <c r="W16" s="139"/>
+      <c r="X16" s="139"/>
+      <c r="Y16" s="139"/>
+      <c r="Z16" s="139"/>
     </row>
     <row r="17" customHeight="1" spans="1:26">
-      <c r="A17" s="60"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="91" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="92"/>
-      <c r="P17" s="94"/>
-      <c r="Q17" s="94"/>
-      <c r="R17" s="94"/>
-      <c r="S17" s="94"/>
-      <c r="T17" s="92"/>
-      <c r="U17" s="92"/>
-      <c r="V17" s="92"/>
-      <c r="W17" s="92"/>
-      <c r="X17" s="92"/>
-      <c r="Y17" s="92"/>
-      <c r="Z17" s="92"/>
+      <c r="A17" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="28"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="140"/>
+      <c r="K17" s="138" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="138"/>
+      <c r="M17" s="138"/>
+      <c r="N17" s="138"/>
+      <c r="O17" s="139" t="s">
+        <v>35</v>
+      </c>
+      <c r="P17" s="139"/>
+      <c r="Q17" s="139"/>
+      <c r="R17" s="139"/>
+      <c r="S17" s="139"/>
+      <c r="T17" s="139"/>
+      <c r="U17" s="139"/>
+      <c r="V17" s="139"/>
+      <c r="W17" s="139"/>
+      <c r="X17" s="139"/>
+      <c r="Y17" s="139"/>
+      <c r="Z17" s="139"/>
     </row>
     <row r="18" customHeight="1" spans="1:26">
-      <c r="A18" s="60"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="91" t="s">
-        <v>33</v>
-      </c>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="92"/>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="92"/>
-      <c r="R18" s="94"/>
-      <c r="S18" s="94"/>
-      <c r="T18" s="94"/>
-      <c r="U18" s="94"/>
-      <c r="V18" s="92"/>
-      <c r="W18" s="92"/>
-      <c r="X18" s="92"/>
-      <c r="Y18" s="92"/>
-      <c r="Z18" s="92"/>
+      <c r="A18" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="28"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="141"/>
+      <c r="K18" s="138" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18" s="138"/>
+      <c r="M18" s="138"/>
+      <c r="N18" s="138"/>
+      <c r="O18" s="139" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
+      <c r="S18" s="139"/>
+      <c r="T18" s="139"/>
+      <c r="U18" s="139"/>
+      <c r="V18" s="139"/>
+      <c r="W18" s="139"/>
+      <c r="X18" s="139"/>
+      <c r="Y18" s="139"/>
+      <c r="Z18" s="139"/>
     </row>
     <row r="19" customHeight="1" spans="1:27">
-      <c r="A19" s="60"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="91" t="s">
-        <v>34</v>
-      </c>
-      <c r="L19" s="91"/>
-      <c r="M19" s="91"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="92"/>
-      <c r="P19" s="92"/>
-      <c r="Q19" s="94"/>
-      <c r="R19" s="94"/>
-      <c r="S19" s="94"/>
-      <c r="T19" s="94"/>
-      <c r="U19" s="92"/>
-      <c r="V19" s="92"/>
-      <c r="W19" s="92"/>
-      <c r="X19" s="92"/>
-      <c r="Y19" s="92"/>
-      <c r="Z19" s="92"/>
-      <c r="AA19" s="103"/>
+      <c r="A19" s="90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="138" t="s">
+        <v>40</v>
+      </c>
+      <c r="L19" s="138"/>
+      <c r="M19" s="138"/>
+      <c r="N19" s="138"/>
+      <c r="O19" s="139"/>
+      <c r="P19" s="139"/>
+      <c r="Q19" s="139"/>
+      <c r="R19" s="139"/>
+      <c r="S19" s="139"/>
+      <c r="T19" s="139"/>
+      <c r="U19" s="139"/>
+      <c r="V19" s="139"/>
+      <c r="W19" s="139"/>
+      <c r="X19" s="139"/>
+      <c r="Y19" s="139"/>
+      <c r="Z19" s="139"/>
+      <c r="AA19" s="155"/>
     </row>
     <row r="20" customHeight="1" spans="1:27">
-      <c r="A20" s="60"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="L20" s="94"/>
-      <c r="M20" s="94"/>
-      <c r="N20" s="94"/>
-      <c r="O20" s="92" t="s">
-        <v>36</v>
-      </c>
-      <c r="P20" s="92"/>
-      <c r="Q20" s="92"/>
-      <c r="R20" s="92"/>
-      <c r="S20" s="92"/>
-      <c r="T20" s="92"/>
-      <c r="U20" s="92"/>
-      <c r="V20" s="92"/>
-      <c r="W20" s="92"/>
-      <c r="X20" s="92"/>
-      <c r="Y20" s="92"/>
-      <c r="Z20" s="92"/>
-      <c r="AA20" s="103"/>
-    </row>
-    <row r="21" customHeight="1" spans="7:27">
-      <c r="G21" s="62"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="99"/>
-      <c r="N21" s="99"/>
-      <c r="O21" s="99"/>
-      <c r="P21" s="98"/>
-      <c r="Q21" s="98"/>
-      <c r="R21" s="98"/>
-      <c r="S21" s="98"/>
-      <c r="T21" s="99"/>
-      <c r="U21" s="99"/>
-      <c r="V21" s="99"/>
-      <c r="W21" s="99"/>
-      <c r="X21" s="99"/>
-      <c r="Y21" s="99"/>
-      <c r="Z21" s="99"/>
-      <c r="AA21" s="103"/>
-    </row>
-    <row r="22" customHeight="1" spans="8:26">
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="64"/>
-      <c r="R22" s="64"/>
-      <c r="S22" s="64"/>
-      <c r="T22" s="64"/>
-      <c r="U22" s="64"/>
-      <c r="V22" s="64"/>
-      <c r="W22" s="64"/>
-      <c r="X22" s="64"/>
-      <c r="Y22" s="64"/>
-      <c r="Z22" s="64"/>
+      <c r="A20" s="90"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="144" t="s">
+        <v>41</v>
+      </c>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="144" t="s">
+        <v>42</v>
+      </c>
+      <c r="P20" s="144"/>
+      <c r="Q20" s="144"/>
+      <c r="R20" s="144"/>
+      <c r="S20" s="144"/>
+      <c r="T20" s="144"/>
+      <c r="U20" s="144"/>
+      <c r="V20" s="144"/>
+      <c r="W20" s="144"/>
+      <c r="X20" s="144"/>
+      <c r="Y20" s="144"/>
+      <c r="Z20" s="144"/>
+      <c r="AA20" s="155"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:27">
+      <c r="A21" s="91"/>
+      <c r="B21" s="91"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="147"/>
+      <c r="K21" s="147"/>
+      <c r="L21" s="147"/>
+      <c r="M21" s="148"/>
+      <c r="N21" s="148"/>
+      <c r="O21" s="148"/>
+      <c r="P21" s="147"/>
+      <c r="Q21" s="147"/>
+      <c r="R21" s="147"/>
+      <c r="S21" s="147"/>
+      <c r="T21" s="148"/>
+      <c r="U21" s="148"/>
+      <c r="V21" s="148"/>
+      <c r="W21" s="148"/>
+      <c r="X21" s="148"/>
+      <c r="Y21" s="148"/>
+      <c r="Z21" s="148"/>
+      <c r="AA21" s="155"/>
+    </row>
+    <row r="22" customHeight="1" spans="2:26">
+      <c r="B22" s="94" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="96"/>
+      <c r="I22" s="96"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="96"/>
+      <c r="L22" s="96"/>
+      <c r="M22" s="96"/>
+      <c r="N22" s="96"/>
+      <c r="O22" s="96"/>
+      <c r="P22" s="96"/>
+      <c r="Q22" s="96"/>
+      <c r="R22" s="96"/>
+      <c r="S22" s="96"/>
+      <c r="T22" s="96"/>
+      <c r="U22" s="96"/>
+      <c r="V22" s="96"/>
+      <c r="W22" s="96"/>
+      <c r="X22" s="96"/>
+      <c r="Y22" s="96"/>
+      <c r="Z22" s="96"/>
+    </row>
+    <row r="23" customHeight="1" spans="2:26">
+      <c r="B23" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="98" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="91"/>
+      <c r="P23" s="91"/>
+      <c r="Q23" s="91"/>
+      <c r="R23" s="91"/>
+      <c r="S23" s="91"/>
+      <c r="T23" s="91"/>
+      <c r="U23" s="91"/>
+      <c r="V23" s="91"/>
+      <c r="W23" s="91"/>
+      <c r="X23" s="91"/>
+      <c r="Y23" s="91"/>
+      <c r="Z23" s="91"/>
+    </row>
+    <row r="24" customHeight="1" spans="2:26">
+      <c r="B24" s="97" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="91"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="91"/>
+      <c r="M24" s="91"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="91"/>
+      <c r="P24" s="91"/>
+      <c r="Q24" s="91"/>
+      <c r="R24" s="91"/>
+      <c r="S24" s="91"/>
+      <c r="T24" s="91"/>
+      <c r="U24" s="91"/>
+      <c r="V24" s="91"/>
+      <c r="W24" s="91"/>
+      <c r="X24" s="91"/>
+      <c r="Y24" s="91"/>
+      <c r="Z24" s="91"/>
+    </row>
+    <row r="25" customHeight="1" spans="2:26">
+      <c r="B25" s="97" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="91"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="91"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="91"/>
+      <c r="P25" s="91"/>
+      <c r="Q25" s="91"/>
+      <c r="R25" s="91"/>
+      <c r="S25" s="91"/>
+      <c r="T25" s="91"/>
+      <c r="U25" s="91"/>
+      <c r="V25" s="91"/>
+      <c r="W25" s="91"/>
+      <c r="X25" s="91"/>
+      <c r="Y25" s="91"/>
+      <c r="Z25" s="91"/>
+    </row>
+    <row r="26" customHeight="1" spans="2:26">
+      <c r="B26" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="98" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="91"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="91"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="91"/>
+      <c r="Q26" s="91"/>
+      <c r="R26" s="91"/>
+      <c r="S26" s="91"/>
+      <c r="T26" s="91"/>
+      <c r="U26" s="91"/>
+      <c r="V26" s="91"/>
+      <c r="W26" s="91"/>
+      <c r="X26" s="91"/>
+      <c r="Y26" s="91"/>
+      <c r="Z26" s="91"/>
+    </row>
+    <row r="27" customHeight="1" spans="2:26">
+      <c r="B27" s="97" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="98" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="98" t="s">
+        <v>58</v>
+      </c>
+      <c r="H27" s="91"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="91"/>
+      <c r="K27" s="91"/>
+      <c r="L27" s="91"/>
+      <c r="M27" s="91"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="91"/>
+      <c r="P27" s="91"/>
+      <c r="Q27" s="91"/>
+      <c r="R27" s="91"/>
+      <c r="S27" s="91"/>
+      <c r="T27" s="91"/>
+      <c r="U27" s="91"/>
+      <c r="V27" s="91"/>
+      <c r="W27" s="91"/>
+      <c r="X27" s="91"/>
+      <c r="Y27" s="91"/>
+      <c r="Z27" s="91"/>
+    </row>
+    <row r="28" customHeight="1" spans="2:26">
+      <c r="B28" s="97" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="98" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="98"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="98" t="s">
+        <v>61</v>
+      </c>
+      <c r="H28" s="91"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="91"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="91"/>
+      <c r="M28" s="91"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="91"/>
+      <c r="P28" s="91"/>
+      <c r="Q28" s="91"/>
+      <c r="R28" s="91"/>
+      <c r="S28" s="91"/>
+      <c r="T28" s="91"/>
+      <c r="U28" s="91"/>
+      <c r="V28" s="91"/>
+      <c r="W28" s="91"/>
+      <c r="X28" s="91"/>
+      <c r="Y28" s="91"/>
+      <c r="Z28" s="91"/>
+    </row>
+    <row r="29" customHeight="1" spans="2:26">
+      <c r="B29" s="97" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="98" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="H29" s="91"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="91"/>
+      <c r="K29" s="91"/>
+      <c r="L29" s="91"/>
+      <c r="M29" s="91"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="91"/>
+      <c r="P29" s="91"/>
+      <c r="Q29" s="91"/>
+      <c r="R29" s="91"/>
+      <c r="S29" s="91"/>
+      <c r="T29" s="91"/>
+      <c r="U29" s="91"/>
+      <c r="V29" s="91"/>
+      <c r="W29" s="91"/>
+      <c r="X29" s="91"/>
+      <c r="Y29" s="91"/>
+      <c r="Z29" s="91"/>
+    </row>
+    <row r="30" customHeight="1" spans="2:26">
+      <c r="B30" s="97" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="98" t="s">
+        <v>67</v>
+      </c>
+      <c r="H30" s="91"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="91"/>
+      <c r="K30" s="91"/>
+      <c r="L30" s="91"/>
+      <c r="M30" s="91"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="91"/>
+      <c r="P30" s="91"/>
+      <c r="Q30" s="91"/>
+      <c r="R30" s="91"/>
+      <c r="S30" s="91"/>
+      <c r="T30" s="91"/>
+      <c r="U30" s="91"/>
+      <c r="V30" s="91"/>
+      <c r="W30" s="91"/>
+      <c r="X30" s="91"/>
+      <c r="Y30" s="91"/>
+      <c r="Z30" s="91"/>
+    </row>
+    <row r="32" customHeight="1" spans="2:26">
+      <c r="B32" s="99" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="100" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="100"/>
+      <c r="G32" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="101"/>
+      <c r="N32" s="101"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="101"/>
+      <c r="Q32" s="101"/>
+      <c r="R32" s="101"/>
+      <c r="S32" s="101"/>
+      <c r="T32" s="101"/>
+      <c r="U32" s="101"/>
+      <c r="V32" s="101"/>
+      <c r="W32" s="101"/>
+      <c r="X32" s="101"/>
+      <c r="Y32" s="101"/>
+      <c r="Z32" s="101"/>
+    </row>
+    <row r="33" customHeight="1" spans="2:26">
+      <c r="B33" s="102" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="98" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="98"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
+      <c r="N33" s="91"/>
+      <c r="O33" s="91"/>
+      <c r="P33" s="91"/>
+      <c r="Q33" s="91"/>
+      <c r="R33" s="91"/>
+      <c r="S33" s="91"/>
+      <c r="T33" s="91"/>
+      <c r="U33" s="91"/>
+      <c r="V33" s="91"/>
+      <c r="W33" s="91"/>
+      <c r="X33" s="91"/>
+      <c r="Y33" s="91"/>
+      <c r="Z33" s="91"/>
+    </row>
+    <row r="34" customHeight="1" spans="2:26">
+      <c r="B34" s="102" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="98" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="91"/>
+      <c r="I34" s="91"/>
+      <c r="J34" s="91"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="91"/>
+      <c r="M34" s="91"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="91"/>
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="91"/>
+      <c r="S34" s="91"/>
+      <c r="T34" s="91"/>
+      <c r="U34" s="91"/>
+      <c r="V34" s="91"/>
+      <c r="W34" s="91"/>
+      <c r="X34" s="91"/>
+      <c r="Y34" s="91"/>
+      <c r="Z34" s="91"/>
+    </row>
+    <row r="35" customHeight="1" spans="2:26">
+      <c r="B35" s="102" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="98" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="98"/>
+      <c r="E35" s="98"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="98" t="s">
+        <v>74</v>
+      </c>
+      <c r="H35" s="91"/>
+      <c r="I35" s="91"/>
+      <c r="J35" s="91"/>
+      <c r="K35" s="91"/>
+      <c r="L35" s="91"/>
+      <c r="M35" s="91"/>
+      <c r="N35" s="91"/>
+      <c r="O35" s="91"/>
+      <c r="P35" s="91"/>
+      <c r="Q35" s="91"/>
+      <c r="R35" s="91"/>
+      <c r="S35" s="91"/>
+      <c r="T35" s="91"/>
+      <c r="U35" s="91"/>
+      <c r="V35" s="91"/>
+      <c r="W35" s="91"/>
+      <c r="X35" s="91"/>
+      <c r="Y35" s="91"/>
+      <c r="Z35" s="91"/>
+    </row>
+    <row r="36" customHeight="1" spans="2:26">
+      <c r="B36" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="98"/>
+      <c r="E36" s="98"/>
+      <c r="F36" s="98"/>
+      <c r="G36" s="98" t="s">
+        <v>77</v>
+      </c>
+      <c r="H36" s="91"/>
+      <c r="I36" s="91"/>
+      <c r="J36" s="91"/>
+      <c r="K36" s="91"/>
+      <c r="L36" s="91"/>
+      <c r="M36" s="91"/>
+      <c r="N36" s="91"/>
+      <c r="O36" s="91"/>
+      <c r="P36" s="91"/>
+      <c r="Q36" s="91"/>
+      <c r="R36" s="91"/>
+      <c r="S36" s="91"/>
+      <c r="T36" s="91"/>
+      <c r="U36" s="91"/>
+      <c r="V36" s="91"/>
+      <c r="W36" s="91"/>
+      <c r="X36" s="91"/>
+      <c r="Y36" s="91"/>
+      <c r="Z36" s="91"/>
+    </row>
+    <row r="37" customHeight="1" spans="2:26">
+      <c r="B37" s="102" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="98" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="H37" s="91"/>
+      <c r="I37" s="91"/>
+      <c r="J37" s="91"/>
+      <c r="K37" s="91"/>
+      <c r="L37" s="91"/>
+      <c r="M37" s="91"/>
+      <c r="N37" s="91"/>
+      <c r="O37" s="91"/>
+      <c r="P37" s="91"/>
+      <c r="Q37" s="91"/>
+      <c r="R37" s="91"/>
+      <c r="S37" s="91"/>
+      <c r="T37" s="91"/>
+      <c r="U37" s="91"/>
+      <c r="V37" s="91"/>
+      <c r="W37" s="91"/>
+      <c r="X37" s="91"/>
+      <c r="Y37" s="91"/>
+      <c r="Z37" s="91"/>
+    </row>
+    <row r="39" customHeight="1" spans="2:26">
+      <c r="B39" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="104" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="105" t="s">
+        <v>45</v>
+      </c>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+      <c r="J39" s="105"/>
+      <c r="K39" s="105"/>
+      <c r="L39" s="105"/>
+      <c r="M39" s="105"/>
+      <c r="N39" s="105"/>
+      <c r="O39" s="105"/>
+      <c r="P39" s="105"/>
+      <c r="Q39" s="105"/>
+      <c r="R39" s="105"/>
+      <c r="S39" s="105"/>
+      <c r="T39" s="105"/>
+      <c r="U39" s="105"/>
+      <c r="V39" s="105"/>
+      <c r="W39" s="105"/>
+      <c r="X39" s="105"/>
+      <c r="Y39" s="105"/>
+      <c r="Z39" s="105"/>
+    </row>
+    <row r="40" customHeight="1" spans="2:26">
+      <c r="B40" s="106" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="98" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="98"/>
+      <c r="E40" s="98"/>
+      <c r="F40" s="98"/>
+      <c r="G40" s="98" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="91"/>
+      <c r="I40" s="91"/>
+      <c r="J40" s="91"/>
+      <c r="K40" s="91"/>
+      <c r="L40" s="91"/>
+      <c r="M40" s="91"/>
+      <c r="N40" s="91"/>
+      <c r="O40" s="91"/>
+      <c r="P40" s="91"/>
+      <c r="Q40" s="91"/>
+      <c r="R40" s="91"/>
+      <c r="S40" s="91"/>
+      <c r="T40" s="91"/>
+      <c r="U40" s="91"/>
+      <c r="V40" s="91"/>
+      <c r="W40" s="91"/>
+      <c r="X40" s="91"/>
+      <c r="Y40" s="91"/>
+      <c r="Z40" s="91"/>
+    </row>
+    <row r="41" customHeight="1" spans="2:26">
+      <c r="B41" s="106" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="98" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="98"/>
+      <c r="E41" s="98"/>
+      <c r="F41" s="98"/>
+      <c r="G41" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="H41" s="91"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="91"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="91"/>
+      <c r="N41" s="91"/>
+      <c r="O41" s="91"/>
+      <c r="P41" s="91"/>
+      <c r="Q41" s="91"/>
+      <c r="R41" s="91"/>
+      <c r="S41" s="91"/>
+      <c r="T41" s="91"/>
+      <c r="U41" s="91"/>
+      <c r="V41" s="91"/>
+      <c r="W41" s="91"/>
+      <c r="X41" s="91"/>
+      <c r="Y41" s="91"/>
+      <c r="Z41" s="91"/>
+    </row>
+    <row r="42" customHeight="1" spans="2:26">
+      <c r="B42" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="98" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="98"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="98" t="s">
+        <v>89</v>
+      </c>
+      <c r="H42" s="91"/>
+      <c r="I42" s="91"/>
+      <c r="J42" s="91"/>
+      <c r="K42" s="91"/>
+      <c r="L42" s="91"/>
+      <c r="M42" s="91"/>
+      <c r="N42" s="91"/>
+      <c r="O42" s="91"/>
+      <c r="P42" s="91"/>
+      <c r="Q42" s="91"/>
+      <c r="R42" s="91"/>
+      <c r="S42" s="91"/>
+      <c r="T42" s="91"/>
+      <c r="U42" s="91"/>
+      <c r="V42" s="91"/>
+      <c r="W42" s="91"/>
+      <c r="X42" s="91"/>
+      <c r="Y42" s="91"/>
+      <c r="Z42" s="91"/>
+    </row>
+    <row r="43" customHeight="1" spans="2:26">
+      <c r="B43" s="106" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" s="98" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="98"/>
+      <c r="E43" s="98"/>
+      <c r="F43" s="98"/>
+      <c r="G43" s="98" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" s="91"/>
+      <c r="I43" s="91"/>
+      <c r="J43" s="91"/>
+      <c r="K43" s="91"/>
+      <c r="L43" s="91"/>
+      <c r="M43" s="91"/>
+      <c r="N43" s="91"/>
+      <c r="O43" s="91"/>
+      <c r="P43" s="91"/>
+      <c r="Q43" s="91"/>
+      <c r="R43" s="91"/>
+      <c r="S43" s="91"/>
+      <c r="T43" s="91"/>
+      <c r="U43" s="91"/>
+      <c r="V43" s="91"/>
+      <c r="W43" s="91"/>
+      <c r="X43" s="91"/>
+      <c r="Y43" s="91"/>
+      <c r="Z43" s="91"/>
+    </row>
+    <row r="45" customHeight="1" spans="2:26">
+      <c r="B45" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="104" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="104"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="105" t="s">
+        <v>45</v>
+      </c>
+      <c r="H45" s="105"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="105"/>
+      <c r="K45" s="105"/>
+      <c r="L45" s="105"/>
+      <c r="M45" s="105"/>
+      <c r="N45" s="105"/>
+      <c r="O45" s="105"/>
+      <c r="P45" s="105"/>
+      <c r="Q45" s="105"/>
+      <c r="R45" s="105"/>
+      <c r="S45" s="105"/>
+      <c r="T45" s="105"/>
+      <c r="U45" s="105"/>
+      <c r="V45" s="105"/>
+      <c r="W45" s="105"/>
+      <c r="X45" s="105"/>
+      <c r="Y45" s="105"/>
+      <c r="Z45" s="105"/>
+    </row>
+    <row r="46" customHeight="1" spans="2:26">
+      <c r="B46" s="106" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="98" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46" s="98"/>
+      <c r="E46" s="98"/>
+      <c r="F46" s="98"/>
+      <c r="G46" s="98" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46" s="91"/>
+      <c r="I46" s="91"/>
+      <c r="J46" s="91"/>
+      <c r="K46" s="91"/>
+      <c r="L46" s="91"/>
+      <c r="M46" s="91"/>
+      <c r="N46" s="91"/>
+      <c r="O46" s="91"/>
+      <c r="P46" s="91"/>
+      <c r="Q46" s="91"/>
+      <c r="R46" s="91"/>
+      <c r="S46" s="91"/>
+      <c r="T46" s="91"/>
+      <c r="U46" s="91"/>
+      <c r="V46" s="91"/>
+      <c r="W46" s="91"/>
+      <c r="X46" s="91"/>
+      <c r="Y46" s="91"/>
+      <c r="Z46" s="91"/>
+    </row>
+    <row r="47" customHeight="1" spans="2:26">
+      <c r="B47" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="98" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="98"/>
+      <c r="E47" s="98"/>
+      <c r="F47" s="98"/>
+      <c r="G47" s="98" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" s="91"/>
+      <c r="I47" s="91"/>
+      <c r="J47" s="91"/>
+      <c r="K47" s="91"/>
+      <c r="L47" s="91"/>
+      <c r="M47" s="91"/>
+      <c r="N47" s="91"/>
+      <c r="O47" s="91"/>
+      <c r="P47" s="91"/>
+      <c r="Q47" s="91"/>
+      <c r="R47" s="91"/>
+      <c r="S47" s="91"/>
+      <c r="T47" s="91"/>
+      <c r="U47" s="91"/>
+      <c r="V47" s="91"/>
+      <c r="W47" s="91"/>
+      <c r="X47" s="91"/>
+      <c r="Y47" s="91"/>
+      <c r="Z47" s="91"/>
+    </row>
+    <row r="48" customHeight="1" spans="2:26">
+      <c r="B48" s="106" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" s="98" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="98"/>
+      <c r="E48" s="98"/>
+      <c r="F48" s="98"/>
+      <c r="G48" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48" s="91"/>
+      <c r="I48" s="91"/>
+      <c r="J48" s="91"/>
+      <c r="K48" s="91"/>
+      <c r="L48" s="91"/>
+      <c r="M48" s="91"/>
+      <c r="N48" s="91"/>
+      <c r="O48" s="91"/>
+      <c r="P48" s="91"/>
+      <c r="Q48" s="91"/>
+      <c r="R48" s="91"/>
+      <c r="S48" s="91"/>
+      <c r="T48" s="91"/>
+      <c r="U48" s="91"/>
+      <c r="V48" s="91"/>
+      <c r="W48" s="91"/>
+      <c r="X48" s="91"/>
+      <c r="Y48" s="91"/>
+      <c r="Z48" s="91"/>
+    </row>
+    <row r="49" customHeight="1" spans="2:26">
+      <c r="B49" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="98" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" s="98"/>
+      <c r="E49" s="98"/>
+      <c r="F49" s="98"/>
+      <c r="G49" s="98" t="s">
+        <v>89</v>
+      </c>
+      <c r="H49" s="91"/>
+      <c r="I49" s="91"/>
+      <c r="J49" s="91"/>
+      <c r="K49" s="91"/>
+      <c r="L49" s="91"/>
+      <c r="M49" s="91"/>
+      <c r="N49" s="91"/>
+      <c r="O49" s="91"/>
+      <c r="P49" s="91"/>
+      <c r="Q49" s="91"/>
+      <c r="R49" s="91"/>
+      <c r="S49" s="91"/>
+      <c r="T49" s="91"/>
+      <c r="U49" s="91"/>
+      <c r="V49" s="91"/>
+      <c r="W49" s="91"/>
+      <c r="X49" s="91"/>
+      <c r="Y49" s="91"/>
+      <c r="Z49" s="91"/>
+    </row>
+    <row r="50" customHeight="1" spans="2:26">
+      <c r="B50" s="106" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="98" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="98"/>
+      <c r="E50" s="98"/>
+      <c r="F50" s="98"/>
+      <c r="G50" s="98" t="s">
+        <v>91</v>
+      </c>
+      <c r="H50" s="91"/>
+      <c r="I50" s="91"/>
+      <c r="J50" s="91"/>
+      <c r="K50" s="91"/>
+      <c r="L50" s="91"/>
+      <c r="M50" s="91"/>
+      <c r="N50" s="91"/>
+      <c r="O50" s="91"/>
+      <c r="P50" s="91"/>
+      <c r="Q50" s="91"/>
+      <c r="R50" s="91"/>
+      <c r="S50" s="91"/>
+      <c r="T50" s="91"/>
+      <c r="U50" s="91"/>
+      <c r="V50" s="91"/>
+      <c r="W50" s="91"/>
+      <c r="X50" s="91"/>
+      <c r="Y50" s="91"/>
+      <c r="Z50" s="91"/>
+    </row>
+    <row r="52" customHeight="1" spans="2:26">
+      <c r="B52" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="108" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="108"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="108"/>
+      <c r="G52" s="109" t="s">
+        <v>45</v>
+      </c>
+      <c r="H52" s="109"/>
+      <c r="I52" s="109"/>
+      <c r="J52" s="109"/>
+      <c r="K52" s="109"/>
+      <c r="L52" s="109"/>
+      <c r="M52" s="109"/>
+      <c r="N52" s="109"/>
+      <c r="O52" s="109"/>
+      <c r="P52" s="109"/>
+      <c r="Q52" s="109"/>
+      <c r="R52" s="109"/>
+      <c r="S52" s="109"/>
+      <c r="T52" s="109"/>
+      <c r="U52" s="109"/>
+      <c r="V52" s="109"/>
+      <c r="W52" s="109"/>
+      <c r="X52" s="109"/>
+      <c r="Y52" s="109"/>
+      <c r="Z52" s="109"/>
+    </row>
+    <row r="53" customHeight="1" spans="2:26">
+      <c r="B53" s="110" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="111" t="s">
+        <v>96</v>
+      </c>
+      <c r="D53" s="111"/>
+      <c r="E53" s="111"/>
+      <c r="F53" s="111"/>
+      <c r="G53" s="98" t="s">
+        <v>83</v>
+      </c>
+      <c r="H53" s="91"/>
+      <c r="I53" s="91"/>
+      <c r="J53" s="91"/>
+      <c r="K53" s="91"/>
+      <c r="L53" s="91"/>
+      <c r="M53" s="91"/>
+      <c r="N53" s="91"/>
+      <c r="O53" s="91"/>
+      <c r="P53" s="91"/>
+      <c r="Q53" s="91"/>
+      <c r="R53" s="91"/>
+      <c r="S53" s="91"/>
+      <c r="T53" s="91"/>
+      <c r="U53" s="91"/>
+      <c r="V53" s="91"/>
+      <c r="W53" s="91"/>
+      <c r="X53" s="91"/>
+      <c r="Y53" s="91"/>
+      <c r="Z53" s="91"/>
+    </row>
+    <row r="54" customHeight="1" spans="2:26">
+      <c r="B54" s="110" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="111" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="111"/>
+      <c r="F54" s="111"/>
+      <c r="G54" s="98" t="s">
+        <v>98</v>
+      </c>
+      <c r="H54" s="91"/>
+      <c r="I54" s="91"/>
+      <c r="J54" s="91"/>
+      <c r="K54" s="91"/>
+      <c r="L54" s="91"/>
+      <c r="M54" s="91"/>
+      <c r="N54" s="91"/>
+      <c r="O54" s="91"/>
+      <c r="P54" s="91"/>
+      <c r="Q54" s="91"/>
+      <c r="R54" s="91"/>
+      <c r="S54" s="91"/>
+      <c r="T54" s="91"/>
+      <c r="U54" s="91"/>
+      <c r="V54" s="91"/>
+      <c r="W54" s="91"/>
+      <c r="X54" s="91"/>
+      <c r="Y54" s="91"/>
+      <c r="Z54" s="91"/>
+    </row>
+    <row r="55" customHeight="1" spans="2:26">
+      <c r="B55" s="110" t="s">
+        <v>93</v>
+      </c>
+      <c r="C55" s="98" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="98"/>
+      <c r="E55" s="98"/>
+      <c r="F55" s="98"/>
+      <c r="G55" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H55" s="91"/>
+      <c r="I55" s="91"/>
+      <c r="J55" s="91"/>
+      <c r="K55" s="91"/>
+      <c r="L55" s="91"/>
+      <c r="M55" s="91"/>
+      <c r="N55" s="91"/>
+      <c r="O55" s="91"/>
+      <c r="P55" s="91"/>
+      <c r="Q55" s="91"/>
+      <c r="R55" s="91"/>
+      <c r="S55" s="91"/>
+      <c r="T55" s="91"/>
+      <c r="U55" s="91"/>
+      <c r="V55" s="91"/>
+      <c r="W55" s="91"/>
+      <c r="X55" s="91"/>
+      <c r="Y55" s="91"/>
+      <c r="Z55" s="91"/>
+    </row>
+    <row r="56" customHeight="1" spans="2:26">
+      <c r="B56" s="110" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="98" t="s">
+        <v>100</v>
+      </c>
+      <c r="D56" s="98"/>
+      <c r="E56" s="98"/>
+      <c r="F56" s="98"/>
+      <c r="G56" s="98" t="s">
+        <v>101</v>
+      </c>
+      <c r="H56" s="91"/>
+      <c r="I56" s="91"/>
+      <c r="J56" s="91"/>
+      <c r="K56" s="91"/>
+      <c r="L56" s="91"/>
+      <c r="M56" s="91"/>
+      <c r="N56" s="91"/>
+      <c r="O56" s="91"/>
+      <c r="P56" s="91"/>
+      <c r="Q56" s="91"/>
+      <c r="R56" s="91"/>
+      <c r="S56" s="91"/>
+      <c r="T56" s="91"/>
+      <c r="U56" s="91"/>
+      <c r="V56" s="91"/>
+      <c r="W56" s="91"/>
+      <c r="X56" s="91"/>
+      <c r="Y56" s="91"/>
+      <c r="Z56" s="91"/>
+    </row>
+    <row r="57" customHeight="1" spans="2:26">
+      <c r="B57" s="110" t="s">
+        <v>102</v>
+      </c>
+      <c r="C57" s="98" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" s="98"/>
+      <c r="E57" s="98"/>
+      <c r="F57" s="98"/>
+      <c r="G57" s="98" t="s">
+        <v>104</v>
+      </c>
+      <c r="H57" s="91"/>
+      <c r="I57" s="91"/>
+      <c r="J57" s="91"/>
+      <c r="K57" s="91"/>
+      <c r="L57" s="91"/>
+      <c r="M57" s="91"/>
+      <c r="N57" s="91"/>
+      <c r="O57" s="91"/>
+      <c r="P57" s="91"/>
+      <c r="Q57" s="91"/>
+      <c r="R57" s="91"/>
+      <c r="S57" s="91"/>
+      <c r="T57" s="91"/>
+      <c r="U57" s="91"/>
+      <c r="V57" s="91"/>
+      <c r="W57" s="91"/>
+      <c r="X57" s="91"/>
+      <c r="Y57" s="91"/>
+      <c r="Z57" s="91"/>
+    </row>
+    <row r="58" customHeight="1" spans="2:26">
+      <c r="B58" s="110" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="98" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" s="98"/>
+      <c r="E58" s="98"/>
+      <c r="F58" s="98"/>
+      <c r="G58" s="98" t="s">
+        <v>61</v>
+      </c>
+      <c r="H58" s="91"/>
+      <c r="I58" s="91"/>
+      <c r="J58" s="91"/>
+      <c r="K58" s="91"/>
+      <c r="L58" s="91"/>
+      <c r="M58" s="91"/>
+      <c r="N58" s="91"/>
+      <c r="O58" s="91"/>
+      <c r="P58" s="91"/>
+      <c r="Q58" s="91"/>
+      <c r="R58" s="91"/>
+      <c r="S58" s="91"/>
+      <c r="T58" s="91"/>
+      <c r="U58" s="91"/>
+      <c r="V58" s="91"/>
+      <c r="W58" s="91"/>
+      <c r="X58" s="91"/>
+      <c r="Y58" s="91"/>
+      <c r="Z58" s="91"/>
+    </row>
+    <row r="59" customHeight="1" spans="2:26">
+      <c r="B59" s="110" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="98" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" s="98"/>
+      <c r="E59" s="98"/>
+      <c r="F59" s="98"/>
+      <c r="G59" s="98" t="s">
+        <v>106</v>
+      </c>
+      <c r="H59" s="91"/>
+      <c r="I59" s="91"/>
+      <c r="J59" s="91"/>
+      <c r="K59" s="91"/>
+      <c r="L59" s="91"/>
+      <c r="M59" s="91"/>
+      <c r="N59" s="91"/>
+      <c r="O59" s="91"/>
+      <c r="P59" s="91"/>
+      <c r="Q59" s="91"/>
+      <c r="R59" s="91"/>
+      <c r="S59" s="91"/>
+      <c r="T59" s="91"/>
+      <c r="U59" s="91"/>
+      <c r="V59" s="91"/>
+      <c r="W59" s="91"/>
+      <c r="X59" s="91"/>
+      <c r="Y59" s="91"/>
+      <c r="Z59" s="91"/>
+    </row>
+    <row r="60" customHeight="1" spans="2:26">
+      <c r="B60" s="110" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" s="98" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="98"/>
+      <c r="E60" s="98"/>
+      <c r="F60" s="98"/>
+      <c r="G60" s="98" t="s">
+        <v>108</v>
+      </c>
+      <c r="H60" s="91"/>
+      <c r="I60" s="91"/>
+      <c r="J60" s="91"/>
+      <c r="K60" s="91"/>
+      <c r="L60" s="91"/>
+      <c r="M60" s="91"/>
+      <c r="N60" s="91"/>
+      <c r="O60" s="91"/>
+      <c r="P60" s="91"/>
+      <c r="Q60" s="91"/>
+      <c r="R60" s="91"/>
+      <c r="S60" s="91"/>
+      <c r="T60" s="91"/>
+      <c r="U60" s="91"/>
+      <c r="V60" s="91"/>
+      <c r="W60" s="91"/>
+      <c r="X60" s="91"/>
+      <c r="Y60" s="91"/>
+      <c r="Z60" s="91"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="91">
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:Z1"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:Z16"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:Z17"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:Z18"/>
     <mergeCell ref="K19:N19"/>
+    <mergeCell ref="O19:Z19"/>
     <mergeCell ref="K20:N20"/>
     <mergeCell ref="O20:Z20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:Z22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:Z23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G24:Z24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:Z25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G26:Z26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="G27:Z27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:Z28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:Z29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:Z30"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="G32:Z32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="G33:Z33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="G34:Z34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G35:Z35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="G36:Z36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G37:Z37"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="G39:Z39"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="G40:Z40"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="G41:Z41"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="G42:Z42"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="G43:Z43"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="G45:Z45"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="G46:Z46"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="G47:Z47"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="G48:Z48"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="G49:Z49"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="G50:Z50"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="G52:Z52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="G53:Z53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="G54:Z54"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="G55:Z55"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="G56:Z56"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="G57:Z57"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="G58:Z58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="G59:Z59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="G60:Z60"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A19:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="B57:B60 B53:B54 B46 B23:B25 B27:B31" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
-    <col min="2" max="15" width="6.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1"/>
-    <col min="17" max="17" width="15.625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="20.625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.625" style="28" customWidth="1"/>
+    <col min="2" max="15" width="6.625" style="28" customWidth="1"/>
+    <col min="16" max="16" width="9" style="28"/>
+    <col min="17" max="17" width="15.625" style="28" customWidth="1"/>
+    <col min="18" max="18" width="20.625" style="28" customWidth="1"/>
+    <col min="19" max="19" width="9" style="28"/>
+    <col min="20" max="20" width="39.625" style="28" customWidth="1"/>
+    <col min="21" max="21" width="9.5" style="28" customWidth="1"/>
+    <col min="22" max="22" width="20.625" style="28" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="3">
+      <c r="A1" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="30">
         <v>10</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="30">
         <v>20</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="30">
         <v>30</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="30">
         <v>40</v>
       </c>
-      <c r="F1" s="4">
+      <c r="F1" s="31">
         <v>50</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="30">
         <v>60</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="31">
         <v>70</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="30">
         <v>80</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="30">
         <v>90</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="30">
         <v>100</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="30">
         <v>110</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="30">
         <v>120</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="30">
         <v>130</v>
       </c>
-      <c r="O1" s="9">
+      <c r="O1" s="38">
         <v>140</v>
       </c>
-      <c r="Q1" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>39</v>
+      <c r="Q1" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="R1" s="39" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:18">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="9"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="13"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:19">
-      <c r="A3" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="A2" s="32"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="38"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:18">
+      <c r="A3" s="33">
+        <v>0</v>
+      </c>
+      <c r="B3" s="34">
         <f>ROUND($A3*B$1,0)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="34">
         <f t="shared" ref="C3:O3" si="0">ROUND($A3*C$1,0)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="34">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H3" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I3" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J3" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K3" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L3" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M3" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N3" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O3" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="R3" s="41" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:18">
+      <c r="A4" s="35">
+        <v>0.01</v>
+      </c>
+      <c r="B4" s="36">
+        <f>ROUND($A4*B$1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="36">
+        <f>ROUND($A4*C$1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="36">
+        <f>ROUND($A4*D$1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="36">
+        <f>ROUND($A4*E$1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="36">
+        <f>ROUND($A4*F$1,0)</f>
         <v>1</v>
       </c>
-      <c r="G3" s="7">
-        <f t="shared" si="0"/>
+      <c r="G4" s="36">
+        <f>ROUND($A4*G$1,0)</f>
         <v>1</v>
       </c>
-      <c r="H3" s="7">
-        <f t="shared" si="0"/>
+      <c r="H4" s="36">
+        <f>ROUND($A4*H$1,0)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="7">
-        <f t="shared" si="0"/>
+      <c r="I4" s="36">
+        <f>ROUND($A4*I$1,0)</f>
         <v>1</v>
       </c>
-      <c r="J3" s="7">
-        <f t="shared" si="0"/>
+      <c r="J4" s="36">
+        <f>ROUND($A4*J$1,0)</f>
         <v>1</v>
       </c>
-      <c r="K3" s="7">
-        <f t="shared" si="0"/>
+      <c r="K4" s="36">
+        <f>ROUND($A4*K$1,0)</f>
         <v>1</v>
       </c>
-      <c r="L3" s="7">
-        <f t="shared" si="0"/>
+      <c r="L4" s="36">
+        <f>ROUND($A4*L$1,0)</f>
         <v>1</v>
       </c>
-      <c r="M3" s="7">
-        <f t="shared" si="0"/>
+      <c r="M4" s="36">
+        <f>ROUND($A4*M$1,0)</f>
         <v>1</v>
       </c>
-      <c r="N3" s="7">
-        <f t="shared" si="0"/>
+      <c r="N4" s="36">
+        <f>ROUND($A4*N$1,0)</f>
         <v>1</v>
       </c>
-      <c r="O3" s="7">
-        <f t="shared" si="0"/>
+      <c r="O4" s="36">
+        <f>ROUND($A4*O$1,0)</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:19">
-      <c r="A4" s="8">
+      <c r="Q4" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="R4" s="41" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:18">
+      <c r="A5" s="37">
         <v>0.02</v>
       </c>
-      <c r="B4" s="7">
-        <f t="shared" ref="B4:B32" si="1">ROUND($A4*B$1,0)</f>
+      <c r="B5" s="34">
+        <f t="shared" ref="B5:B33" si="1">ROUND($A5*B$1,0)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="7">
-        <f t="shared" ref="C4:C32" si="2">ROUND($A4*C$1,0)</f>
+      <c r="C5" s="34">
+        <f t="shared" ref="C5:C33" si="2">ROUND($A5*C$1,0)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="7">
-        <f t="shared" ref="D4:D32" si="3">ROUND($A4*D$1,0)</f>
+      <c r="D5" s="34">
+        <f t="shared" ref="D5:D33" si="3">ROUND($A5*D$1,0)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="7">
-        <f t="shared" ref="E4:E32" si="4">ROUND($A4*E$1,0)</f>
+      <c r="E5" s="34">
+        <f t="shared" ref="E5:E33" si="4">ROUND($A5*E$1,0)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="7">
-        <f t="shared" ref="F4:F32" si="5">ROUND($A4*F$1,0)</f>
+      <c r="F5" s="34">
+        <f t="shared" ref="F5:F33" si="5">ROUND($A5*F$1,0)</f>
         <v>1</v>
       </c>
-      <c r="G4" s="7">
-        <f t="shared" ref="G4:G32" si="6">ROUND($A4*G$1,0)</f>
+      <c r="G5" s="34">
+        <f t="shared" ref="G5:G33" si="6">ROUND($A5*G$1,0)</f>
         <v>1</v>
       </c>
-      <c r="H4" s="7">
-        <f t="shared" ref="H4:H32" si="7">ROUND($A4*H$1,0)</f>
+      <c r="H5" s="34">
+        <f t="shared" ref="H5:H33" si="7">ROUND($A5*H$1,0)</f>
         <v>1</v>
       </c>
-      <c r="I4" s="7">
-        <f t="shared" ref="I4:I32" si="8">ROUND($A4*I$1,0)</f>
+      <c r="I5" s="34">
+        <f t="shared" ref="I5:I33" si="8">ROUND($A5*I$1,0)</f>
         <v>2</v>
       </c>
-      <c r="J4" s="7">
-        <f t="shared" ref="J4:J32" si="9">ROUND($A4*J$1,0)</f>
+      <c r="J5" s="34">
+        <f t="shared" ref="J5:J33" si="9">ROUND($A5*J$1,0)</f>
         <v>2</v>
       </c>
-      <c r="K4" s="7">
-        <f t="shared" ref="K4:K32" si="10">ROUND($A4*K$1,0)</f>
+      <c r="K5" s="34">
+        <f t="shared" ref="K5:K33" si="10">ROUND($A5*K$1,0)</f>
         <v>2</v>
       </c>
-      <c r="L4" s="7">
-        <f t="shared" ref="L4:L32" si="11">ROUND($A4*L$1,0)</f>
+      <c r="L5" s="34">
+        <f t="shared" ref="L5:L33" si="11">ROUND($A5*L$1,0)</f>
         <v>2</v>
       </c>
-      <c r="M4" s="7">
-        <f t="shared" ref="M4:M32" si="12">ROUND($A4*M$1,0)</f>
+      <c r="M5" s="34">
+        <f t="shared" ref="M5:M33" si="12">ROUND($A5*M$1,0)</f>
         <v>2</v>
       </c>
-      <c r="N4" s="7">
-        <f t="shared" ref="N4:N32" si="13">ROUND($A4*N$1,0)</f>
+      <c r="N5" s="34">
+        <f t="shared" ref="N5:N33" si="13">ROUND($A5*N$1,0)</f>
         <v>3</v>
       </c>
-      <c r="O4" s="7">
-        <f t="shared" ref="O4:O32" si="14">ROUND($A4*O$1,0)</f>
+      <c r="O5" s="34">
+        <f t="shared" ref="O5:O33" si="14">ROUND($A5*O$1,0)</f>
         <v>3</v>
       </c>
-      <c r="Q4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:18">
-      <c r="A5" s="6">
+      <c r="Q5" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="R5" s="41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:18">
+      <c r="A6" s="35">
         <v>0.03</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B6" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C6" s="36">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D6" s="36">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E6" s="36">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F6" s="36">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G6" s="36">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H6" s="36">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I6" s="36">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J6" s="36">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K6" s="36">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L6" s="36">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M6" s="36">
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N6" s="36">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O6" s="36">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="Q5" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="R5" s="14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:19">
-      <c r="A6" s="8">
+      <c r="Q6" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="R6" s="41" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:18">
+      <c r="A7" s="37">
         <v>0.04</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B7" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C7" s="34">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D7" s="34">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E7" s="34">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F7" s="34">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G7" s="34">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H7" s="34">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I7" s="34">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J7" s="34">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K7" s="34">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L7" s="34">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M7" s="34">
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N7" s="34">
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O7" s="34">
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="Q6" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="R6" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:19">
-      <c r="A7" s="6">
+      <c r="Q7" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="R7" s="41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:18">
+      <c r="A8" s="35">
         <v>0.05</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B8" s="36">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C8" s="36">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D8" s="36">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E8" s="36">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F8" s="36">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G8" s="36">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H8" s="36">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I8" s="36">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J8" s="36">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K8" s="36">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L8" s="36">
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M8" s="36">
         <f t="shared" si="12"/>
         <v>6</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N8" s="36">
         <f t="shared" si="13"/>
         <v>7</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O8" s="36">
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="Q7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="R7" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:15">
-      <c r="A8" s="8">
+      <c r="Q8" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="R8" s="41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:18">
+      <c r="A9" s="37">
         <v>0.06</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B9" s="34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C9" s="34">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D9" s="34">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E9" s="34">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F9" s="34">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G9" s="34">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H9" s="34">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I9" s="34">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J9" s="34">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K9" s="34">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L9" s="34">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M9" s="34">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N9" s="34">
         <f t="shared" si="13"/>
         <v>8</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O9" s="34">
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:15">
-      <c r="A9" s="6">
+      <c r="Q9" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="R9" s="41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:18">
+      <c r="A10" s="35">
         <v>0.07</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B10" s="36">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C10" s="36">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D10" s="36">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E10" s="36">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F10" s="36">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G10" s="36">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H10" s="36">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I10" s="36">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J10" s="36">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K10" s="36">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L10" s="36">
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M10" s="36">
         <f t="shared" si="12"/>
         <v>8</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N10" s="36">
         <f t="shared" si="13"/>
         <v>9</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O10" s="36">
         <f t="shared" si="14"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:15">
-      <c r="A10" s="8">
+      <c r="Q10" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="R10" s="41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:15">
+      <c r="A11" s="37">
         <v>0.08</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B11" s="34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C11" s="34">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D11" s="34">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E11" s="34">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F11" s="34">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G11" s="34">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H11" s="34">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I11" s="34">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J11" s="34">
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K11" s="34">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L11" s="34">
         <f t="shared" si="11"/>
         <v>9</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M11" s="34">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N11" s="34">
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O11" s="34">
         <f t="shared" si="14"/>
         <v>11</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:15">
-      <c r="A11" s="6">
+    <row r="12" ht="30" customHeight="1" spans="1:15">
+      <c r="A12" s="35">
         <v>0.09</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B12" s="36">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C12" s="36">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D12" s="36">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E12" s="36">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F12" s="36">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G12" s="36">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H12" s="36">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I12" s="36">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J12" s="36">
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K12" s="36">
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L12" s="36">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M12" s="36">
         <f t="shared" si="12"/>
         <v>11</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N12" s="36">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O12" s="36">
         <f t="shared" si="14"/>
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="1:15">
-      <c r="A12" s="8">
+    <row r="13" ht="30" customHeight="1" spans="1:15">
+      <c r="A13" s="37">
         <v>0.1</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B13" s="34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C13" s="34">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D13" s="34">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E13" s="34">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F13" s="34">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G13" s="34">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H13" s="34">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I13" s="34">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J13" s="34">
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K13" s="34">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L13" s="34">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M13" s="34">
         <f t="shared" si="12"/>
         <v>12</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N13" s="34">
         <f t="shared" si="13"/>
         <v>13</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O13" s="34">
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:15">
-      <c r="A13" s="6">
+    <row r="14" ht="30" customHeight="1" spans="1:15">
+      <c r="A14" s="35">
         <v>0.11</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B14" s="36">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C14" s="36">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D14" s="36">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E14" s="36">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F14" s="36">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G14" s="36">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H14" s="36">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I14" s="36">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J14" s="36">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K14" s="36">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L14" s="36">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M14" s="36">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N14" s="36">
         <f t="shared" si="13"/>
         <v>14</v>
       </c>
-      <c r="O13" s="7">
+      <c r="O14" s="36">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:15">
-      <c r="A14" s="8">
+    <row r="15" ht="30" customHeight="1" spans="1:15">
+      <c r="A15" s="37">
         <v>0.12</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B15" s="34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C15" s="34">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D15" s="34">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E15" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F15" s="34">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G15" s="34">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H15" s="34">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I15" s="34">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J15" s="34">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K15" s="34">
         <f t="shared" si="10"/>
         <v>12</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L15" s="34">
         <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M15" s="34">
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N15" s="34">
         <f t="shared" si="13"/>
         <v>16</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O15" s="34">
         <f t="shared" si="14"/>
         <v>17</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="1:15">
-      <c r="A15" s="6">
+    <row r="16" ht="30" customHeight="1" spans="1:15">
+      <c r="A16" s="35">
         <v>0.13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B16" s="36">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C16" s="36">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D16" s="36">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E16" s="36">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F16" s="36">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G16" s="36">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H16" s="36">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I16" s="36">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J16" s="36">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K16" s="36">
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L16" s="36">
         <f t="shared" si="11"/>
         <v>14</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M16" s="36">
         <f t="shared" si="12"/>
         <v>16</v>
       </c>
-      <c r="N15" s="7">
+      <c r="N16" s="36">
         <f t="shared" si="13"/>
         <v>17</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O16" s="36">
         <f t="shared" si="14"/>
         <v>18</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" spans="1:15">
-      <c r="A16" s="8">
+    <row r="17" ht="30" customHeight="1" spans="1:15">
+      <c r="A17" s="37">
         <v>0.14</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B17" s="34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C17" s="34">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D17" s="34">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E17" s="34">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F17" s="34">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G17" s="34">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H17" s="34">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I17" s="34">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J17" s="34">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K17" s="34">
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L17" s="34">
         <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M17" s="34">
         <f t="shared" si="12"/>
         <v>17</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N17" s="34">
         <f t="shared" si="13"/>
         <v>18</v>
       </c>
-      <c r="O16" s="7">
+      <c r="O17" s="34">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" spans="1:15">
-      <c r="A17" s="6">
+    <row r="18" ht="30" customHeight="1" spans="1:15">
+      <c r="A18" s="35">
         <v>0.15</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B18" s="36">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C18" s="36">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D18" s="36">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E18" s="36">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F18" s="36">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G18" s="36">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H18" s="36">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I18" s="36">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J18" s="36">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K18" s="36">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L18" s="36">
         <f t="shared" si="11"/>
         <v>17</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M18" s="36">
         <f t="shared" si="12"/>
         <v>18</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N18" s="36">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="O17" s="7">
+      <c r="O18" s="36">
         <f t="shared" si="14"/>
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" spans="1:15">
-      <c r="A18" s="8">
+    <row r="19" ht="30" customHeight="1" spans="1:15">
+      <c r="A19" s="37">
         <v>0.16</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B19" s="34">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C19" s="34">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D19" s="34">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E19" s="34">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F19" s="34">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G19" s="34">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H19" s="34">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I19" s="34">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J19" s="34">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K19" s="34">
         <f t="shared" si="10"/>
         <v>16</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L19" s="34">
         <f t="shared" si="11"/>
         <v>18</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M19" s="34">
         <f t="shared" si="12"/>
         <v>19</v>
       </c>
-      <c r="N18" s="7">
+      <c r="N19" s="34">
         <f t="shared" si="13"/>
         <v>21</v>
       </c>
-      <c r="O18" s="7">
+      <c r="O19" s="34">
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" spans="1:15">
-      <c r="A19" s="6">
+    <row r="20" ht="30" customHeight="1" spans="1:15">
+      <c r="A20" s="35">
         <v>0.17</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B20" s="36">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C20" s="36">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D20" s="36">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E20" s="36">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F20" s="36">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G20" s="36">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H20" s="36">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I20" s="36">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J20" s="36">
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K20" s="36">
         <f t="shared" si="10"/>
         <v>17</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L20" s="36">
         <f t="shared" si="11"/>
         <v>19</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M20" s="36">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="N19" s="7">
+      <c r="N20" s="36">
         <f t="shared" si="13"/>
         <v>22</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O20" s="36">
         <f t="shared" si="14"/>
         <v>24</v>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="1:15">
-      <c r="A20" s="8">
+    <row r="21" ht="30" customHeight="1" spans="1:15">
+      <c r="A21" s="37">
         <v>0.18</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B21" s="34">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C21" s="34">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D21" s="34">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E21" s="34">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F21" s="34">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G21" s="34">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H21" s="34">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I21" s="34">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J21" s="34">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K21" s="34">
         <f t="shared" si="10"/>
         <v>18</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L21" s="34">
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M21" s="34">
         <f t="shared" si="12"/>
         <v>22</v>
       </c>
-      <c r="N20" s="7">
+      <c r="N21" s="34">
         <f t="shared" si="13"/>
         <v>23</v>
       </c>
-      <c r="O20" s="7">
+      <c r="O21" s="34">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" spans="1:15">
-      <c r="A21" s="6">
+    <row r="22" ht="30" customHeight="1" spans="1:15">
+      <c r="A22" s="35">
         <v>0.19</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B22" s="36">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C22" s="36">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D22" s="36">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E22" s="36">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F22" s="36">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G22" s="36">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H22" s="36">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I22" s="36">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J22" s="36">
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K22" s="36">
         <f t="shared" si="10"/>
         <v>19</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L22" s="36">
         <f t="shared" si="11"/>
         <v>21</v>
       </c>
-      <c r="M21" s="7">
+      <c r="M22" s="36">
         <f t="shared" si="12"/>
         <v>23</v>
       </c>
-      <c r="N21" s="7">
+      <c r="N22" s="36">
         <f t="shared" si="13"/>
         <v>25</v>
       </c>
-      <c r="O21" s="7">
+      <c r="O22" s="36">
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1" spans="1:15">
-      <c r="A22" s="8">
+    <row r="23" ht="30" customHeight="1" spans="1:15">
+      <c r="A23" s="37">
         <v>0.2</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B23" s="34">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C23" s="34">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D23" s="34">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E23" s="34">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F23" s="34">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G23" s="34">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H23" s="34">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I23" s="34">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J23" s="34">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K23" s="34">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="L22" s="7">
+      <c r="L23" s="34">
         <f t="shared" si="11"/>
         <v>22</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M23" s="34">
         <f t="shared" si="12"/>
         <v>24</v>
       </c>
-      <c r="N22" s="7">
+      <c r="N23" s="34">
         <f t="shared" si="13"/>
         <v>26</v>
       </c>
-      <c r="O22" s="7">
+      <c r="O23" s="34">
         <f t="shared" si="14"/>
         <v>28</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" spans="1:15">
-      <c r="A23" s="6">
+    <row r="24" ht="30" customHeight="1" spans="1:15">
+      <c r="A24" s="35">
         <v>0.21</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B24" s="36">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C24" s="36">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D24" s="36">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E24" s="36">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F24" s="36">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G24" s="36">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H24" s="36">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I24" s="36">
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J24" s="36">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K24" s="36">
         <f t="shared" si="10"/>
         <v>21</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L24" s="36">
         <f t="shared" si="11"/>
         <v>23</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M24" s="36">
         <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="N23" s="7">
+      <c r="N24" s="36">
         <f t="shared" si="13"/>
         <v>27</v>
       </c>
-      <c r="O23" s="7">
+      <c r="O24" s="36">
         <f t="shared" si="14"/>
         <v>29</v>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" spans="1:15">
-      <c r="A24" s="8">
+    <row r="25" ht="30" customHeight="1" spans="1:15">
+      <c r="A25" s="37">
         <v>0.22</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B25" s="34">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C25" s="34">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D25" s="34">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E25" s="34">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F25" s="34">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G25" s="34">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H25" s="34">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I25" s="34">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J25" s="34">
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K25" s="34">
         <f t="shared" si="10"/>
         <v>22</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L25" s="34">
         <f t="shared" si="11"/>
         <v>24</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M25" s="34">
         <f t="shared" si="12"/>
         <v>26</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N25" s="34">
         <f t="shared" si="13"/>
         <v>29</v>
       </c>
-      <c r="O24" s="7">
+      <c r="O25" s="34">
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" spans="1:15">
-      <c r="A25" s="6">
+    <row r="26" ht="30" customHeight="1" spans="1:15">
+      <c r="A26" s="35">
         <v>0.23</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B26" s="36">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C26" s="36">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D26" s="36">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E26" s="36">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F26" s="36">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G26" s="36">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H26" s="36">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I26" s="36">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J26" s="36">
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K26" s="36">
         <f t="shared" si="10"/>
         <v>23</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L26" s="36">
         <f t="shared" si="11"/>
         <v>25</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M26" s="36">
         <f t="shared" si="12"/>
         <v>28</v>
       </c>
-      <c r="N25" s="7">
+      <c r="N26" s="36">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
-      <c r="O25" s="7">
+      <c r="O26" s="36">
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1" spans="1:15">
-      <c r="A26" s="8">
+    <row r="27" ht="30" customHeight="1" spans="1:15">
+      <c r="A27" s="37">
         <v>0.24</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B27" s="34">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C27" s="34">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D27" s="34">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E27" s="34">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F27" s="34">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G27" s="34">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H27" s="34">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I27" s="34">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J27" s="34">
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K27" s="34">
         <f t="shared" si="10"/>
         <v>24</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L27" s="34">
         <f t="shared" si="11"/>
         <v>26</v>
       </c>
-      <c r="M26" s="7">
+      <c r="M27" s="34">
         <f t="shared" si="12"/>
         <v>29</v>
       </c>
-      <c r="N26" s="7">
+      <c r="N27" s="34">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
-      <c r="O26" s="7">
+      <c r="O27" s="34">
         <f t="shared" si="14"/>
         <v>34</v>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" spans="1:15">
-      <c r="A27" s="6">
+    <row r="28" ht="30" customHeight="1" spans="1:15">
+      <c r="A28" s="35">
         <v>0.25</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B28" s="36">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C28" s="36">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D28" s="36">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E28" s="36">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F28" s="36">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G28" s="36">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H28" s="36">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I28" s="36">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J28" s="36">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K28" s="36">
         <f t="shared" si="10"/>
         <v>25</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L28" s="36">
         <f t="shared" si="11"/>
         <v>28</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M28" s="36">
         <f t="shared" si="12"/>
         <v>30</v>
       </c>
-      <c r="N27" s="7">
+      <c r="N28" s="36">
         <f t="shared" si="13"/>
         <v>33</v>
       </c>
-      <c r="O27" s="7">
+      <c r="O28" s="36">
         <f t="shared" si="14"/>
         <v>35</v>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" spans="1:15">
-      <c r="A28" s="8">
+    <row r="29" ht="30" customHeight="1" spans="1:15">
+      <c r="A29" s="37">
         <v>0.26</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B29" s="34">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C29" s="34">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D29" s="34">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E29" s="34">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F29" s="34">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G29" s="34">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H29" s="34">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I29" s="34">
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J29" s="34">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K29" s="34">
         <f t="shared" si="10"/>
         <v>26</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L29" s="34">
         <f t="shared" si="11"/>
         <v>29</v>
       </c>
-      <c r="M28" s="7">
+      <c r="M29" s="34">
         <f t="shared" si="12"/>
         <v>31</v>
       </c>
-      <c r="N28" s="7">
+      <c r="N29" s="34">
         <f t="shared" si="13"/>
         <v>34</v>
       </c>
-      <c r="O28" s="7">
+      <c r="O29" s="34">
         <f t="shared" si="14"/>
         <v>36</v>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1" spans="1:15">
-      <c r="A29" s="6">
+    <row r="30" ht="30" customHeight="1" spans="1:15">
+      <c r="A30" s="35">
         <v>0.27</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B30" s="36">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C30" s="36">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D30" s="36">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E30" s="36">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F30" s="36">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G30" s="36">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H30" s="36">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I30" s="36">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J30" s="36">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K30" s="36">
         <f t="shared" si="10"/>
         <v>27</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L30" s="36">
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="M29" s="7">
+      <c r="M30" s="36">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="N29" s="7">
+      <c r="N30" s="36">
         <f t="shared" si="13"/>
         <v>35</v>
       </c>
-      <c r="O29" s="7">
+      <c r="O30" s="36">
         <f t="shared" si="14"/>
         <v>38</v>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1" spans="1:15">
-      <c r="A30" s="8">
+    <row r="31" ht="30" customHeight="1" spans="1:15">
+      <c r="A31" s="37">
         <v>0.28</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B31" s="34">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C31" s="34">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D31" s="34">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E31" s="34">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F31" s="34">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G31" s="34">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H31" s="34">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="I30" s="7">
+      <c r="I31" s="34">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="J30" s="7">
+      <c r="J31" s="34">
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K31" s="34">
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
-      <c r="L30" s="7">
+      <c r="L31" s="34">
         <f t="shared" si="11"/>
         <v>31</v>
       </c>
-      <c r="M30" s="7">
+      <c r="M31" s="34">
         <f t="shared" si="12"/>
         <v>34</v>
       </c>
-      <c r="N30" s="7">
+      <c r="N31" s="34">
         <f t="shared" si="13"/>
         <v>36</v>
       </c>
-      <c r="O30" s="7">
+      <c r="O31" s="34">
         <f t="shared" si="14"/>
         <v>39</v>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" spans="1:15">
-      <c r="A31" s="6">
+    <row r="32" ht="30" customHeight="1" spans="1:15">
+      <c r="A32" s="35">
         <v>0.29</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B32" s="36">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C32" s="36">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D32" s="36">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E32" s="36">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F32" s="36">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G32" s="36">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H32" s="36">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I32" s="36">
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J32" s="36">
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K32" s="36">
         <f t="shared" si="10"/>
         <v>29</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L32" s="36">
         <f t="shared" si="11"/>
         <v>32</v>
       </c>
-      <c r="M31" s="7">
+      <c r="M32" s="36">
         <f t="shared" si="12"/>
         <v>35</v>
       </c>
-      <c r="N31" s="7">
+      <c r="N32" s="36">
         <f t="shared" si="13"/>
         <v>38</v>
       </c>
-      <c r="O31" s="7">
+      <c r="O32" s="36">
         <f t="shared" si="14"/>
         <v>41</v>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" spans="1:15">
-      <c r="A32" s="8">
+    <row r="33" ht="30" customHeight="1" spans="1:15">
+      <c r="A33" s="37">
         <v>0.3</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B33" s="34">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C33" s="34">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D33" s="34">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E33" s="34">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F33" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G33" s="34">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H33" s="34">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I33" s="34">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J33" s="34">
         <f t="shared" si="9"/>
         <v>27</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K33" s="34">
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L33" s="34">
         <f t="shared" si="11"/>
         <v>33</v>
       </c>
-      <c r="M32" s="7">
+      <c r="M33" s="34">
         <f t="shared" si="12"/>
         <v>36</v>
       </c>
-      <c r="N32" s="7">
+      <c r="N33" s="34">
         <f t="shared" si="13"/>
         <v>39</v>
       </c>
-      <c r="O32" s="7">
+      <c r="O33" s="34">
         <f t="shared" si="14"/>
         <v>42</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5085,12 +7619,13 @@
     <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="S1:S2"/>
+    <mergeCell ref="W1:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="R3:R4 R6:R7 Q7 Q3" numberStoredAsText="1"/>
+    <ignoredError sqref="Q3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5098,9 +7633,512 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="39.625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="21" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" spans="1:2">
+      <c r="A1" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" ht="20.25" spans="1:2">
+      <c r="A2" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" ht="20.25" spans="1:2">
+      <c r="A3" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" ht="20.25" spans="1:2">
+      <c r="A4" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" ht="20.25" spans="1:2">
+      <c r="A5" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" ht="20.25" spans="1:2">
+      <c r="A6" s="24"/>
+      <c r="B6" s="26"/>
+    </row>
+    <row r="7" ht="20.25" spans="1:2">
+      <c r="A7" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" ht="20.25" spans="1:2">
+      <c r="A8" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" ht="20.25" spans="1:2">
+      <c r="A9" s="24"/>
+      <c r="B9" s="26"/>
+    </row>
+    <row r="10" ht="20.25" spans="1:2">
+      <c r="A10" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" ht="20.25" spans="1:2">
+      <c r="A11" s="24"/>
+      <c r="B11" s="26"/>
+    </row>
+    <row r="12" ht="20.25" spans="1:2">
+      <c r="A12" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" ht="20.25" spans="1:2">
+      <c r="A13" s="24"/>
+      <c r="B13" s="26"/>
+    </row>
+    <row r="14" ht="20.25" spans="1:2">
+      <c r="A14" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" ht="20.25" spans="1:2">
+      <c r="A15" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" ht="20.25" spans="1:2">
+      <c r="A16" s="24"/>
+      <c r="B16" s="26"/>
+    </row>
+    <row r="17" ht="20.25" spans="1:2">
+      <c r="A17" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" ht="20.25" spans="1:2">
+      <c r="A18" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" ht="20.25" spans="1:2">
+      <c r="A19" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" ht="20.25" spans="1:2">
+      <c r="A20" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" ht="20.25" spans="1:2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="26"/>
+    </row>
+    <row r="22" ht="20.25" spans="1:2">
+      <c r="A22" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" ht="20.25" spans="1:2">
+      <c r="A23" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" ht="20.25" spans="1:2">
+      <c r="A24" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" ht="21" spans="1:2">
+      <c r="A25" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" ht="19.5" spans="1:2">
+      <c r="A26" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A26:B26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="B2:B25" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="34.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="7.375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" spans="1:5">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" spans="1:5">
+      <c r="A4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" spans="1:5">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" ht="15.75" spans="1:5">
+      <c r="A6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" ht="15.75" spans="1:5">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" ht="15.75" spans="1:5">
+      <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" spans="1:5">
+      <c r="A9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" spans="1:5">
+      <c r="A14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15" ht="15.75" spans="1:5">
+      <c r="A15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" ht="15.75" spans="1:5">
+      <c r="A16" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" ht="15.75" spans="1:5">
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" ht="15.75" spans="1:5">
+      <c r="A18" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="17" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" spans="1:5">
+      <c r="A19" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="17" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" spans="1:5">
+      <c r="A20" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="20"/>
+      <c r="E21" s="17" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" s="17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="17" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="17" t="s">
+        <v>181</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/WorkBook/Jutland Gun Resolve.xlsx
+++ b/WorkBook/Jutland Gun Resolve.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="200">
   <si>
     <r>
       <rPr>
@@ -119,7 +119,7 @@
     <t>30-40°</t>
   </si>
   <si>
-    <t>12"/45 (30.5 cm) Mark X</t>
+    <t>12"/45  Mark X</t>
   </si>
   <si>
     <t>APC Mark VIa (4crh)</t>
@@ -128,91 +128,94 @@
     <t>-</t>
   </si>
   <si>
-    <t>12"/45 (30.5 cm) Elswick Pattern L</t>
+    <t>12"/45  Mark XIII</t>
   </si>
   <si>
     <t>APC Mark VI (2crh)</t>
   </si>
   <si>
-    <t>12"/50 (30.5 cm) Marks XI,XI* and XII</t>
-  </si>
-  <si>
-    <t>13.5"/45 (34.3 cm) Mark V(L)</t>
+    <t>12"/50  Marks XI,XI* and XII</t>
+  </si>
+  <si>
+    <t>13.5"/45  Mark V(L)</t>
   </si>
   <si>
     <t>APC Mark IIa</t>
   </si>
   <si>
-    <t>13.5"/45 (34.3 cm) Mark V,VI(H)</t>
+    <t>13.5"/45  Mark V,VI(H)</t>
   </si>
   <si>
     <t>APC Mark Ia</t>
   </si>
   <si>
-    <t>14"/45 (35.6 cm) Mark I</t>
-  </si>
-  <si>
-    <t>15"/42 (38.1 cm) Mark I</t>
+    <t>14"/45  Mark I</t>
+  </si>
+  <si>
+    <t>15"/42  Mark I</t>
   </si>
   <si>
     <t>APC Mark Ia (4crh)</t>
   </si>
   <si>
-    <t>28 cm/45 (11") SK L/45</t>
+    <t>28 cm/45  SK L/45</t>
   </si>
   <si>
     <t>APC L/3,2</t>
   </si>
   <si>
-    <t>28 cm/50 (11") SK L/50</t>
+    <t>28 cm/50  SK L/50</t>
   </si>
   <si>
     <t>21000*</t>
   </si>
   <si>
-    <t>30.5 cm/50 (12") SK L/50</t>
+    <t>30.5 cm/50  SK L/50</t>
   </si>
   <si>
     <t>APC L/3,4</t>
   </si>
   <si>
-    <t>38 cm/45 (14.96") SK L/45</t>
+    <t>38 cm/45  SK L/45</t>
   </si>
   <si>
     <t>APC L/3,5</t>
   </si>
   <si>
+    <t>注：为了绘图方便，部分数据做了取整处理</t>
+  </si>
+  <si>
     <t>致命打击</t>
   </si>
   <si>
     <t>再1D6，若此值小于等于命中骰值-3，则生效</t>
   </si>
   <si>
-    <t>注：为了绘图方便，部分数据做了取整处理</t>
+    <t>*：毛奇19500</t>
   </si>
   <si>
     <t>追加打击</t>
   </si>
   <si>
     <t>再投一骰，损伤再加上此骰查表结果</t>
-  </si>
-  <si>
-    <t>*：毛奇19500</t>
-  </si>
-  <si>
-    <t>炮塔命中</t>
-  </si>
-  <si>
-    <t>查甲弹表，击穿则1D10</t>
   </si>
   <si>
     <t>解释：如13.4/45H对装甲6命中，骰值5+6=11致命打击，
 再1D6，若结果小于等于2（5-3），则进入致命打击表</t>
   </si>
   <si>
+    <t>炮塔命中</t>
+  </si>
+  <si>
+    <t>查甲弹表，击穿则1D10</t>
+  </si>
+  <si>
     <t>炮座炮廓命中</t>
   </si>
   <si>
+    <t>炮塔、炮管命中可重复命中同一炮塔、炮管，则不计损伤</t>
+  </si>
+  <si>
     <t>特殊损伤</t>
   </si>
   <si>
@@ -234,13 +237,13 @@
     <t>水中弹</t>
   </si>
   <si>
-    <t>船体受损3D20，航速降低1D6</t>
+    <t>船体受损3D20，航速降低1D6节</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>船体受损2D20，航速降低1D4</t>
+    <t>船体受损2D20，航速降低1D4节</t>
   </si>
   <si>
     <t>3 - 4</t>
@@ -291,7 +294,7 @@
     <t>炮管</t>
   </si>
   <si>
-    <t>向敌侧随机一座炮塔受损，射数-5</t>
+    <t>向敌侧随机一座炮塔火力减半</t>
   </si>
   <si>
     <t>1 - 4</t>
@@ -384,7 +387,10 @@
     <t>动力受损</t>
   </si>
   <si>
-    <t>船体受损1D20，航速降低1D4</t>
+    <t>船体受损1D20，航速降低1D4节</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>无需查表，执行一次炮塔命中1D10判定</t>
@@ -454,7 +460,7 @@
     <t>1 - 2</t>
   </si>
   <si>
-    <t>1D6 -3</t>
+    <t>2D4 -5</t>
   </si>
   <si>
     <t>3 - 7</t>
@@ -496,22 +502,28 @@
     <t>修正值</t>
   </si>
   <si>
-    <t>目标规避机动、大幅转向（英）</t>
+    <t>目标舰规避机动（英射击）</t>
   </si>
   <si>
     <t>-3%</t>
   </si>
   <si>
-    <t>目标规避机动、大幅转向（德）</t>
+    <t>目标舰规避机动（德射击）</t>
   </si>
   <si>
     <t>-2%</t>
   </si>
   <si>
-    <t>我舰规避机动、大幅转向</t>
-  </si>
-  <si>
-    <t>双方规避机动、大幅转向</t>
+    <t>我舰规避机动</t>
+  </si>
+  <si>
+    <t>目标舰大幅转向</t>
+  </si>
+  <si>
+    <t>我舰大幅转向</t>
+  </si>
+  <si>
+    <t>双方规避机动，大幅转向*</t>
   </si>
   <si>
     <t>-8%</t>
@@ -550,12 +562,12 @@
     <t>低火控</t>
   </si>
   <si>
-    <t>-4%</t>
-  </si>
-  <si>
     <t>优火控</t>
   </si>
   <si>
+    <t>+1%</t>
+  </si>
+  <si>
     <t>烟雾射击（英）</t>
   </si>
   <si>
@@ -572,6 +584,15 @@
   </si>
   <si>
     <t>命中率不低于0%</t>
+  </si>
+  <si>
+    <t>*：双方均机动，忽略单独修正，使用此格</t>
+  </si>
+  <si>
+    <t>规避机动：此回合航速-3kn</t>
+  </si>
+  <si>
+    <t>大幅转向：回合内转向过4+个罗经点，与规避机动叠加</t>
   </si>
   <si>
     <r>
@@ -585,7 +606,22 @@
     </r>
   </si>
   <si>
+    <t>A:14</t>
+  </si>
+  <si>
+    <t>B:12</t>
+  </si>
+  <si>
+    <t>12"/45 (30.5 cm) Mark X</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>E</t>
     </r>
     <r>
@@ -600,6 +636,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>F</t>
     </r>
     <r>
@@ -614,6 +656,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>F</t>
     </r>
     <r>
@@ -628,6 +676,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>DE</t>
     </r>
     <r>
@@ -641,7 +695,25 @@
     </r>
   </si>
   <si>
+    <t>C:11</t>
+  </si>
+  <si>
+    <t>12"/45 (30.5 cm) Elswick Pattern L</t>
+  </si>
+  <si>
+    <t>D:10.5</t>
+  </si>
+  <si>
+    <t>12"/50 (30.5 cm) Marks XI,XI* and XII</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>D</t>
     </r>
     <r>
@@ -665,6 +737,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>E</t>
     </r>
     <r>
@@ -687,7 +765,19 @@
     </r>
   </si>
   <si>
+    <t>E:9</t>
+  </si>
+  <si>
+    <t>13.5"/45 (34.3 cm) Mark V(L)</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>C</t>
     </r>
     <r>
@@ -711,6 +801,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>D</t>
     </r>
     <r>
@@ -724,7 +820,25 @@
     </r>
   </si>
   <si>
+    <t>F:8</t>
+  </si>
+  <si>
+    <t>13.5"/45 (34.3 cm) Mark V,VI(H)</t>
+  </si>
+  <si>
+    <t>G:7</t>
+  </si>
+  <si>
+    <t>14"/45 (35.6 cm) Mark I</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>B</t>
     </r>
     <r>
@@ -748,6 +862,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>CD</t>
     </r>
     <r>
@@ -771,6 +891,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>AB</t>
     </r>
     <r>
@@ -793,10 +919,22 @@
     </r>
   </si>
   <si>
+    <t>15"/42 (38.1 cm) Mark I</t>
+  </si>
+  <si>
+    <t>28 cm/45 (11") SK L/45</t>
+  </si>
+  <si>
     <t>G</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>E</t>
     </r>
     <r>
@@ -810,7 +948,22 @@
     </r>
   </si>
   <si>
+    <t>28 cm/50 (11") SK L/50</t>
+  </si>
+  <si>
+    <t>30.5 cm/50 (12") SK L/50</t>
+  </si>
+  <si>
+    <t>38 cm/45 (14.96") SK L/45</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>A</t>
     </r>
     <r>
@@ -834,6 +987,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>B</t>
     </r>
     <r>
@@ -857,6 +1016,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>C</t>
     </r>
     <r>
@@ -880,6 +1045,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>黑色字体：</t>
     </r>
     <r>
@@ -911,10 +1082,13 @@
     </r>
   </si>
   <si>
-    <t>A:14</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>蓝色字体</t>
     </r>
     <r>
@@ -955,10 +1129,13 @@
     </r>
   </si>
   <si>
-    <t>B:12</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC00000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>红色字体</t>
     </r>
     <r>
@@ -998,21 +1175,6 @@
       <t xml:space="preserve"> 3</t>
     </r>
   </si>
-  <si>
-    <t>C:11</t>
-  </si>
-  <si>
-    <t>D:10.5</t>
-  </si>
-  <si>
-    <t>E:9</t>
-  </si>
-  <si>
-    <t>F:8</t>
-  </si>
-  <si>
-    <t>G:7</t>
-  </si>
 </sst>
 </file>
 
@@ -1024,7 +1186,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="52">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1045,6 +1207,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
       <name val="Times New Roman"/>
@@ -1061,13 +1230,6 @@
       <color theme="1"/>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1194,6 +1356,12 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1360,19 +1528,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <vertAlign val="superscript"/>
       <sz val="14"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="62">
+  <fills count="58">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1471,19 +1639,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEE796"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1501,19 +1657,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC91D32"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1740,7 +1884,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1974,6 +2118,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -2111,137 +2281,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="34" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="29" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2254,24 +2424,18 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2284,17 +2448,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2320,13 +2478,16 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2374,7 +2535,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2455,7 +2616,7 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2470,46 +2631,52 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="14" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2530,25 +2697,28 @@
     <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2557,22 +2727,7 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2581,103 +2736,109 @@
     <xf numFmtId="0" fontId="2" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2689,16 +2850,16 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2706,6 +2867,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2767,11 +2931,11 @@
     <mruColors>
       <color rgb="0091AADF"/>
       <color rgb="00F4B7BE"/>
-      <color rgb="00FFF3CA"/>
       <color rgb="004874CB"/>
       <color rgb="00FEE796"/>
       <color rgb="00FFC000"/>
       <color rgb="00C91D32"/>
+      <color rgb="00FFF3CA"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3035,756 +3199,776 @@
   <dimension ref="A1:AF60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="32.75" style="42" customWidth="1"/>
-    <col min="2" max="2" width="18.875" style="42" customWidth="1"/>
-    <col min="3" max="6" width="6.375" style="42" customWidth="1"/>
-    <col min="7" max="26" width="3.33333333333333" style="42" customWidth="1"/>
-    <col min="27" max="27" width="9" style="42"/>
-    <col min="28" max="28" width="10.625" style="42" customWidth="1"/>
-    <col min="29" max="29" width="15.625" style="42" customWidth="1"/>
-    <col min="30" max="30" width="9" style="42"/>
-    <col min="31" max="31" width="10.625" style="42" customWidth="1"/>
-    <col min="32" max="32" width="15.625" style="42" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="42"/>
+    <col min="1" max="1" width="26" style="39" customWidth="1"/>
+    <col min="2" max="2" width="18.875" style="39" customWidth="1"/>
+    <col min="3" max="6" width="6.375" style="39" customWidth="1"/>
+    <col min="7" max="26" width="3.33333333333333" style="39" customWidth="1"/>
+    <col min="27" max="27" width="9" style="39"/>
+    <col min="28" max="28" width="10.625" style="39" customWidth="1"/>
+    <col min="29" max="29" width="15.625" style="39" customWidth="1"/>
+    <col min="30" max="30" width="9" style="39"/>
+    <col min="31" max="31" width="10.625" style="39" customWidth="1"/>
+    <col min="32" max="32" width="15.625" style="39" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="39"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:32">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="48" t="s">
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="49"/>
-      <c r="I1" s="112" t="s">
+      <c r="H1" s="46"/>
+      <c r="I1" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="113" t="s">
+      <c r="J1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="150"/>
-      <c r="AB1" s="151"/>
-      <c r="AC1" s="151"/>
-      <c r="AD1" s="151"/>
-      <c r="AE1" s="151"/>
-      <c r="AF1" s="151"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="147"/>
+      <c r="AB1" s="148"/>
+      <c r="AC1" s="148"/>
+      <c r="AD1" s="148"/>
+      <c r="AE1" s="148"/>
+      <c r="AF1" s="148"/>
     </row>
     <row r="2" customHeight="1" spans="1:32">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52" t="s">
+      <c r="A2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="52">
         <v>1</v>
       </c>
-      <c r="H2" s="56">
+      <c r="H2" s="53">
         <v>2</v>
       </c>
-      <c r="I2" s="115">
+      <c r="I2" s="110">
         <v>3</v>
       </c>
-      <c r="J2" s="116">
+      <c r="J2" s="111">
         <v>4</v>
       </c>
-      <c r="K2" s="117">
+      <c r="K2" s="112">
         <v>5</v>
       </c>
-      <c r="L2" s="118">
+      <c r="L2" s="113">
         <v>6</v>
       </c>
-      <c r="M2" s="118">
+      <c r="M2" s="113">
         <v>7</v>
       </c>
-      <c r="N2" s="118">
+      <c r="N2" s="113">
         <v>8</v>
       </c>
-      <c r="O2" s="118">
+      <c r="O2" s="113">
         <v>9</v>
       </c>
-      <c r="P2" s="118">
+      <c r="P2" s="113">
         <v>10</v>
       </c>
-      <c r="Q2" s="118">
+      <c r="Q2" s="113">
         <v>11</v>
       </c>
-      <c r="R2" s="118">
+      <c r="R2" s="113">
         <v>12</v>
       </c>
-      <c r="S2" s="118">
+      <c r="S2" s="113">
         <v>13</v>
       </c>
-      <c r="T2" s="118">
+      <c r="T2" s="113">
         <v>14</v>
       </c>
-      <c r="U2" s="118">
+      <c r="U2" s="113">
         <v>15</v>
       </c>
-      <c r="V2" s="118">
+      <c r="V2" s="113">
         <v>16</v>
       </c>
-      <c r="W2" s="118">
+      <c r="W2" s="113">
         <v>17</v>
       </c>
-      <c r="X2" s="118">
+      <c r="X2" s="113">
         <v>18</v>
       </c>
-      <c r="Y2" s="118">
+      <c r="Y2" s="113">
         <v>19</v>
       </c>
-      <c r="Z2" s="152">
+      <c r="Z2" s="149">
         <v>20</v>
       </c>
-      <c r="AB2" s="151"/>
-      <c r="AC2" s="151"/>
-      <c r="AD2" s="151"/>
-      <c r="AE2" s="151"/>
-      <c r="AF2" s="151"/>
+      <c r="AB2" s="148"/>
+      <c r="AC2" s="148"/>
+      <c r="AD2" s="148"/>
+      <c r="AE2" s="148"/>
+      <c r="AF2" s="148"/>
     </row>
     <row r="3" customHeight="1" spans="1:32">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="59">
+      <c r="C3" s="56">
         <v>10500</v>
       </c>
-      <c r="D3" s="60">
+      <c r="D3" s="57">
         <v>15000</v>
       </c>
-      <c r="E3" s="60">
+      <c r="E3" s="57">
         <v>18000</v>
       </c>
-      <c r="F3" s="61">
+      <c r="F3" s="58">
         <v>18500</v>
       </c>
-      <c r="G3" s="62">
+      <c r="G3" s="59">
         <v>1</v>
       </c>
-      <c r="H3" s="63">
+      <c r="H3" s="60">
         <v>2</v>
       </c>
-      <c r="I3" s="119"/>
-      <c r="J3" s="120">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115">
         <v>6</v>
       </c>
-      <c r="K3" s="121">
+      <c r="K3" s="116"/>
+      <c r="L3" s="117">
+        <v>3</v>
+      </c>
+      <c r="M3" s="114">
+        <v>5</v>
+      </c>
+      <c r="N3" s="114">
+        <v>5</v>
+      </c>
+      <c r="O3" s="114">
+        <v>4</v>
+      </c>
+      <c r="P3" s="118">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="146">
+        <v>5</v>
+      </c>
+      <c r="R3" s="116"/>
+      <c r="S3" s="117">
+        <v>2</v>
+      </c>
+      <c r="T3" s="114">
+        <v>3</v>
+      </c>
+      <c r="U3" s="114">
+        <v>2</v>
+      </c>
+      <c r="V3" s="114" t="s">
+        <v>12</v>
+      </c>
+      <c r="W3" s="114" t="s">
+        <v>12</v>
+      </c>
+      <c r="X3" s="114" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y3" s="114" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z3" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB3" s="150"/>
+      <c r="AC3" s="150"/>
+      <c r="AD3" s="151"/>
+      <c r="AE3" s="150"/>
+      <c r="AF3" s="150"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:32">
+      <c r="A4" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="63">
+        <v>10500</v>
+      </c>
+      <c r="D4" s="64">
+        <v>15000</v>
+      </c>
+      <c r="E4" s="64">
+        <v>18000</v>
+      </c>
+      <c r="F4" s="65">
+        <v>18500</v>
+      </c>
+      <c r="G4" s="66">
+        <v>1</v>
+      </c>
+      <c r="H4" s="67">
+        <v>2</v>
+      </c>
+      <c r="I4" s="71"/>
+      <c r="J4" s="119">
         <v>6</v>
       </c>
-      <c r="L3" s="122">
+      <c r="K4" s="120"/>
+      <c r="L4" s="121">
+        <v>3</v>
+      </c>
+      <c r="M4" s="71">
+        <v>5</v>
+      </c>
+      <c r="N4" s="71">
+        <v>5</v>
+      </c>
+      <c r="O4" s="71">
+        <v>4</v>
+      </c>
+      <c r="P4" s="122">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="124">
+        <v>5</v>
+      </c>
+      <c r="R4" s="120"/>
+      <c r="S4" s="121">
+        <v>2</v>
+      </c>
+      <c r="T4" s="71">
+        <v>3</v>
+      </c>
+      <c r="U4" s="71">
+        <v>2</v>
+      </c>
+      <c r="V4" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="W4" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="X4" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y4" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z4" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB4" s="150"/>
+      <c r="AC4" s="150"/>
+      <c r="AD4" s="151"/>
+      <c r="AE4" s="150"/>
+      <c r="AF4" s="150"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:32">
+      <c r="A5" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="63">
+        <v>13500</v>
+      </c>
+      <c r="D5" s="64">
+        <v>19500</v>
+      </c>
+      <c r="E5" s="64">
+        <v>21000</v>
+      </c>
+      <c r="F5" s="68"/>
+      <c r="G5" s="66">
+        <v>1</v>
+      </c>
+      <c r="H5" s="67">
+        <v>2</v>
+      </c>
+      <c r="I5" s="71"/>
+      <c r="J5" s="119">
         <v>6</v>
       </c>
-      <c r="M3" s="119">
+      <c r="K5" s="120"/>
+      <c r="L5" s="121">
+        <v>3</v>
+      </c>
+      <c r="M5" s="71">
         <v>5</v>
       </c>
-      <c r="N3" s="119">
+      <c r="N5" s="71">
         <v>5</v>
       </c>
-      <c r="O3" s="119">
+      <c r="O5" s="71">
         <v>4</v>
       </c>
-      <c r="P3" s="123">
+      <c r="P5" s="122">
         <v>5</v>
       </c>
-      <c r="Q3" s="149">
+      <c r="Q5" s="124">
         <v>5</v>
       </c>
-      <c r="R3" s="121">
+      <c r="R5" s="120"/>
+      <c r="S5" s="121">
+        <v>3</v>
+      </c>
+      <c r="T5" s="71">
         <v>4</v>
       </c>
-      <c r="S3" s="122">
+      <c r="U5" s="71">
         <v>4</v>
       </c>
-      <c r="T3" s="119">
+      <c r="V5" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="W5" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="X5" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y5" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z5" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB5" s="150"/>
+      <c r="AC5" s="150"/>
+      <c r="AD5" s="151"/>
+      <c r="AE5" s="150"/>
+      <c r="AF5" s="150"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:32">
+      <c r="A6" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="63">
+        <v>13000</v>
+      </c>
+      <c r="D6" s="64">
+        <v>19500</v>
+      </c>
+      <c r="E6" s="64">
+        <v>23500</v>
+      </c>
+      <c r="F6" s="68"/>
+      <c r="G6" s="66">
+        <v>2</v>
+      </c>
+      <c r="H6" s="67">
+        <v>4</v>
+      </c>
+      <c r="I6" s="71"/>
+      <c r="J6" s="123">
+        <v>9</v>
+      </c>
+      <c r="K6" s="124">
+        <v>9</v>
+      </c>
+      <c r="L6" s="120"/>
+      <c r="M6" s="121">
+        <v>5</v>
+      </c>
+      <c r="N6" s="71">
+        <v>8</v>
+      </c>
+      <c r="O6" s="71">
+        <v>8</v>
+      </c>
+      <c r="P6" s="71">
+        <v>7</v>
+      </c>
+      <c r="Q6" s="122">
+        <v>8</v>
+      </c>
+      <c r="R6" s="124">
+        <v>8</v>
+      </c>
+      <c r="S6" s="120"/>
+      <c r="T6" s="121">
+        <v>4</v>
+      </c>
+      <c r="U6" s="71">
+        <v>7</v>
+      </c>
+      <c r="V6" s="71">
+        <v>7</v>
+      </c>
+      <c r="W6" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="X6" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y6" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z6" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB6" s="150"/>
+      <c r="AC6" s="150"/>
+      <c r="AD6" s="151"/>
+      <c r="AE6" s="150"/>
+      <c r="AF6" s="150"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:32">
+      <c r="A7" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="63">
+        <v>13000</v>
+      </c>
+      <c r="D7" s="64">
+        <v>19500</v>
+      </c>
+      <c r="E7" s="64">
+        <v>23500</v>
+      </c>
+      <c r="F7" s="68"/>
+      <c r="G7" s="66">
+        <v>2</v>
+      </c>
+      <c r="H7" s="67">
+        <v>4</v>
+      </c>
+      <c r="I7" s="71"/>
+      <c r="J7" s="123">
+        <v>9</v>
+      </c>
+      <c r="K7" s="124">
+        <v>9</v>
+      </c>
+      <c r="L7" s="120"/>
+      <c r="M7" s="121">
+        <v>5</v>
+      </c>
+      <c r="N7" s="71">
+        <v>8</v>
+      </c>
+      <c r="O7" s="71">
+        <v>8</v>
+      </c>
+      <c r="P7" s="71">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="122">
+        <v>8</v>
+      </c>
+      <c r="R7" s="124">
+        <v>8</v>
+      </c>
+      <c r="S7" s="120"/>
+      <c r="T7" s="121">
+        <v>4</v>
+      </c>
+      <c r="U7" s="71">
+        <v>7</v>
+      </c>
+      <c r="V7" s="71">
+        <v>7</v>
+      </c>
+      <c r="W7" s="71">
+        <v>5</v>
+      </c>
+      <c r="X7" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y7" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z7" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB7" s="150"/>
+      <c r="AC7" s="150"/>
+      <c r="AD7" s="151"/>
+      <c r="AE7" s="150"/>
+      <c r="AF7" s="150"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:32">
+      <c r="A8" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="63">
+        <v>12000</v>
+      </c>
+      <c r="D8" s="64">
+        <v>18500</v>
+      </c>
+      <c r="E8" s="64">
+        <v>24000</v>
+      </c>
+      <c r="F8" s="65">
+        <v>24500</v>
+      </c>
+      <c r="G8" s="66">
         <v>3</v>
       </c>
-      <c r="U3" s="119">
+      <c r="H8" s="67">
+        <v>5</v>
+      </c>
+      <c r="I8" s="71"/>
+      <c r="J8" s="125">
+        <v>10</v>
+      </c>
+      <c r="K8" s="122">
+        <v>12</v>
+      </c>
+      <c r="L8" s="124">
+        <v>12</v>
+      </c>
+      <c r="M8" s="120"/>
+      <c r="N8" s="121">
+        <v>6</v>
+      </c>
+      <c r="O8" s="71">
+        <v>10</v>
+      </c>
+      <c r="P8" s="71">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="71">
+        <v>10</v>
+      </c>
+      <c r="R8" s="122">
+        <v>11</v>
+      </c>
+      <c r="S8" s="124">
+        <v>11</v>
+      </c>
+      <c r="T8" s="120"/>
+      <c r="U8" s="121">
+        <v>6</v>
+      </c>
+      <c r="V8" s="71">
+        <v>9</v>
+      </c>
+      <c r="W8" s="71">
+        <v>9</v>
+      </c>
+      <c r="X8" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y8" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z8" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB8" s="150"/>
+      <c r="AC8" s="150"/>
+      <c r="AD8" s="151"/>
+      <c r="AE8" s="150"/>
+      <c r="AF8" s="150"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:32">
+      <c r="A9" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="63">
+        <v>12000</v>
+      </c>
+      <c r="D9" s="64">
+        <v>18500</v>
+      </c>
+      <c r="E9" s="64">
+        <v>23500</v>
+      </c>
+      <c r="F9" s="68"/>
+      <c r="G9" s="71">
+        <v>3</v>
+      </c>
+      <c r="H9" s="67">
+        <v>5</v>
+      </c>
+      <c r="I9" s="71"/>
+      <c r="J9" s="125">
+        <v>10</v>
+      </c>
+      <c r="K9" s="122">
+        <v>12</v>
+      </c>
+      <c r="L9" s="124">
+        <v>12</v>
+      </c>
+      <c r="M9" s="120"/>
+      <c r="N9" s="121">
+        <v>6</v>
+      </c>
+      <c r="O9" s="71">
+        <v>10</v>
+      </c>
+      <c r="P9" s="71">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="71">
+        <v>10</v>
+      </c>
+      <c r="R9" s="122">
+        <v>11</v>
+      </c>
+      <c r="S9" s="124">
+        <v>11</v>
+      </c>
+      <c r="T9" s="120"/>
+      <c r="U9" s="121">
+        <v>6</v>
+      </c>
+      <c r="V9" s="71">
+        <v>9</v>
+      </c>
+      <c r="W9" s="71">
+        <v>9</v>
+      </c>
+      <c r="X9" s="71">
+        <v>7</v>
+      </c>
+      <c r="Y9" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z9" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB9" s="150"/>
+      <c r="AC9" s="150"/>
+      <c r="AD9" s="151"/>
+      <c r="AE9" s="151"/>
+      <c r="AF9" s="151"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:32">
+      <c r="A10" s="61"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="76">
+        <v>1</v>
+      </c>
+      <c r="H10" s="77">
         <v>2</v>
       </c>
-      <c r="V3" s="119" t="s">
+      <c r="I10" s="126">
+        <v>3</v>
+      </c>
+      <c r="J10" s="127">
+        <v>4</v>
+      </c>
+      <c r="K10" s="128">
+        <v>5</v>
+      </c>
+      <c r="L10" s="128">
+        <v>6</v>
+      </c>
+      <c r="M10" s="128">
+        <v>7</v>
+      </c>
+      <c r="N10" s="128">
+        <v>8</v>
+      </c>
+      <c r="O10" s="128">
+        <v>9</v>
+      </c>
+      <c r="P10" s="128">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="128">
+        <v>11</v>
+      </c>
+      <c r="R10" s="128">
         <v>12</v>
       </c>
-      <c r="W3" s="119" t="s">
-        <v>12</v>
-      </c>
-      <c r="X3" s="119" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y3" s="119" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z3" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB3" s="153"/>
-      <c r="AC3" s="153"/>
-      <c r="AD3" s="154"/>
-      <c r="AE3" s="153"/>
-      <c r="AF3" s="153"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:32">
-      <c r="A4" s="64" t="s">
+      <c r="S10" s="128">
         <v>13</v>
       </c>
-      <c r="B4" s="65" t="s">
+      <c r="T10" s="128">
         <v>14</v>
       </c>
-      <c r="C4" s="66">
-        <v>10500</v>
-      </c>
-      <c r="D4" s="67">
-        <v>15000</v>
-      </c>
-      <c r="E4" s="67">
-        <v>18000</v>
-      </c>
-      <c r="F4" s="68">
-        <v>18500</v>
-      </c>
-      <c r="G4" s="69">
-        <v>1</v>
-      </c>
-      <c r="H4" s="70">
-        <v>2</v>
-      </c>
-      <c r="I4" s="74"/>
-      <c r="J4" s="124">
-        <v>6</v>
-      </c>
-      <c r="K4" s="125">
-        <v>6</v>
-      </c>
-      <c r="L4" s="126">
-        <v>6</v>
-      </c>
-      <c r="M4" s="74">
-        <v>5</v>
-      </c>
-      <c r="N4" s="74">
-        <v>5</v>
-      </c>
-      <c r="O4" s="74">
-        <v>4</v>
-      </c>
-      <c r="P4" s="127">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="129">
-        <v>5</v>
-      </c>
-      <c r="R4" s="125">
-        <v>4</v>
-      </c>
-      <c r="S4" s="126">
-        <v>4</v>
-      </c>
-      <c r="T4" s="74">
-        <v>3</v>
-      </c>
-      <c r="U4" s="74">
-        <v>2</v>
-      </c>
-      <c r="V4" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="W4" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="X4" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y4" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z4" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB4" s="153"/>
-      <c r="AC4" s="153"/>
-      <c r="AD4" s="154"/>
-      <c r="AE4" s="153"/>
-      <c r="AF4" s="153"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:32">
-      <c r="A5" s="64" t="s">
+      <c r="U10" s="128">
         <v>15</v>
       </c>
-      <c r="B5" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="66">
-        <v>13500</v>
-      </c>
-      <c r="D5" s="67">
-        <v>19500</v>
-      </c>
-      <c r="E5" s="67">
-        <v>21000</v>
-      </c>
-      <c r="F5" s="71"/>
-      <c r="G5" s="69">
-        <v>1</v>
-      </c>
-      <c r="H5" s="70">
-        <v>2</v>
-      </c>
-      <c r="I5" s="74"/>
-      <c r="J5" s="124">
-        <v>6</v>
-      </c>
-      <c r="K5" s="125">
-        <v>6</v>
-      </c>
-      <c r="L5" s="126">
-        <v>6</v>
-      </c>
-      <c r="M5" s="74">
-        <v>5</v>
-      </c>
-      <c r="N5" s="74">
-        <v>5</v>
-      </c>
-      <c r="O5" s="74">
-        <v>4</v>
-      </c>
-      <c r="P5" s="127">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="129">
-        <v>5</v>
-      </c>
-      <c r="R5" s="125">
-        <v>5</v>
-      </c>
-      <c r="S5" s="126">
-        <v>5</v>
-      </c>
-      <c r="T5" s="74">
-        <v>4</v>
-      </c>
-      <c r="U5" s="74">
-        <v>4</v>
-      </c>
-      <c r="V5" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="W5" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="X5" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y5" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z5" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB5" s="153"/>
-      <c r="AC5" s="153"/>
-      <c r="AD5" s="154"/>
-      <c r="AE5" s="153"/>
-      <c r="AF5" s="153"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:32">
-      <c r="A6" s="64" t="s">
+      <c r="V10" s="128">
         <v>16</v>
       </c>
-      <c r="B6" s="65" t="s">
+      <c r="W10" s="128">
         <v>17</v>
       </c>
-      <c r="C6" s="66">
-        <v>13000</v>
-      </c>
-      <c r="D6" s="67">
-        <v>19500</v>
-      </c>
-      <c r="E6" s="67">
-        <v>23500</v>
-      </c>
-      <c r="F6" s="71"/>
-      <c r="G6" s="69">
-        <v>2</v>
-      </c>
-      <c r="H6" s="70">
-        <v>4</v>
-      </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="128">
-        <v>9</v>
-      </c>
-      <c r="K6" s="129">
-        <v>9</v>
-      </c>
-      <c r="L6" s="125">
-        <v>9</v>
-      </c>
-      <c r="M6" s="126">
-        <v>9</v>
-      </c>
-      <c r="N6" s="74">
-        <v>8</v>
-      </c>
-      <c r="O6" s="74">
-        <v>8</v>
-      </c>
-      <c r="P6" s="74">
-        <v>7</v>
-      </c>
-      <c r="Q6" s="127">
-        <v>8</v>
-      </c>
-      <c r="R6" s="129">
-        <v>8</v>
-      </c>
-      <c r="S6" s="125">
-        <v>8</v>
-      </c>
-      <c r="T6" s="126">
-        <v>8</v>
-      </c>
-      <c r="U6" s="74">
-        <v>7</v>
-      </c>
-      <c r="V6" s="74">
-        <v>7</v>
-      </c>
-      <c r="W6" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="X6" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y6" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z6" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB6" s="153"/>
-      <c r="AC6" s="153"/>
-      <c r="AD6" s="154"/>
-      <c r="AE6" s="153"/>
-      <c r="AF6" s="153"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:32">
-      <c r="A7" s="64" t="s">
+      <c r="X10" s="128">
         <v>18</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="Y10" s="128">
         <v>19</v>
       </c>
-      <c r="C7" s="66">
-        <v>13000</v>
-      </c>
-      <c r="D7" s="67">
-        <v>19500</v>
-      </c>
-      <c r="E7" s="67">
-        <v>23500</v>
-      </c>
-      <c r="F7" s="71"/>
-      <c r="G7" s="69">
-        <v>2</v>
-      </c>
-      <c r="H7" s="70">
-        <v>4</v>
-      </c>
-      <c r="I7" s="74"/>
-      <c r="J7" s="128">
-        <v>9</v>
-      </c>
-      <c r="K7" s="129">
-        <v>9</v>
-      </c>
-      <c r="L7" s="125">
-        <v>9</v>
-      </c>
-      <c r="M7" s="126">
-        <v>9</v>
-      </c>
-      <c r="N7" s="74">
-        <v>8</v>
-      </c>
-      <c r="O7" s="74">
-        <v>8</v>
-      </c>
-      <c r="P7" s="74">
-        <v>7</v>
-      </c>
-      <c r="Q7" s="127">
-        <v>8</v>
-      </c>
-      <c r="R7" s="129">
-        <v>8</v>
-      </c>
-      <c r="S7" s="125">
-        <v>8</v>
-      </c>
-      <c r="T7" s="126">
-        <v>8</v>
-      </c>
-      <c r="U7" s="74">
-        <v>7</v>
-      </c>
-      <c r="V7" s="74">
-        <v>7</v>
-      </c>
-      <c r="W7" s="74">
-        <v>5</v>
-      </c>
-      <c r="X7" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y7" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z7" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB7" s="153"/>
-      <c r="AC7" s="153"/>
-      <c r="AD7" s="154"/>
-      <c r="AE7" s="153"/>
-      <c r="AF7" s="153"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:32">
-      <c r="A8" s="64" t="s">
+      <c r="Z10" s="152">
         <v>20</v>
       </c>
-      <c r="B8" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="66">
-        <v>12000</v>
-      </c>
-      <c r="D8" s="67">
-        <v>18500</v>
-      </c>
-      <c r="E8" s="67">
-        <v>24000</v>
-      </c>
-      <c r="F8" s="68">
-        <v>24500</v>
-      </c>
-      <c r="G8" s="69">
-        <v>3</v>
-      </c>
-      <c r="H8" s="70">
-        <v>5</v>
-      </c>
-      <c r="I8" s="74"/>
-      <c r="J8" s="130">
-        <v>10</v>
-      </c>
-      <c r="K8" s="127">
-        <v>12</v>
-      </c>
-      <c r="L8" s="129">
-        <v>12</v>
-      </c>
-      <c r="M8" s="125">
-        <v>12</v>
-      </c>
-      <c r="N8" s="126">
-        <v>12</v>
-      </c>
-      <c r="O8" s="74">
-        <v>10</v>
-      </c>
-      <c r="P8" s="74">
-        <v>10</v>
-      </c>
-      <c r="Q8" s="74">
-        <v>10</v>
-      </c>
-      <c r="R8" s="127">
-        <v>11</v>
-      </c>
-      <c r="S8" s="129">
-        <v>11</v>
-      </c>
-      <c r="T8" s="125">
-        <v>11</v>
-      </c>
-      <c r="U8" s="126">
-        <v>11</v>
-      </c>
-      <c r="V8" s="74">
-        <v>9</v>
-      </c>
-      <c r="W8" s="74">
-        <v>9</v>
-      </c>
-      <c r="X8" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y8" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z8" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB8" s="153"/>
-      <c r="AC8" s="153"/>
-      <c r="AD8" s="154"/>
-      <c r="AE8" s="153"/>
-      <c r="AF8" s="153"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:32">
-      <c r="A9" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="66">
-        <v>12000</v>
-      </c>
-      <c r="D9" s="67">
-        <v>18500</v>
-      </c>
-      <c r="E9" s="67">
-        <v>23500</v>
-      </c>
-      <c r="F9" s="71"/>
-      <c r="G9" s="74">
-        <v>3</v>
-      </c>
-      <c r="H9" s="70">
-        <v>5</v>
-      </c>
-      <c r="I9" s="74"/>
-      <c r="J9" s="131">
-        <v>10</v>
-      </c>
-      <c r="K9" s="132">
-        <v>12</v>
-      </c>
-      <c r="L9" s="133">
-        <v>12</v>
-      </c>
-      <c r="M9" s="134">
-        <v>12</v>
-      </c>
-      <c r="N9" s="135">
-        <v>12</v>
-      </c>
-      <c r="O9" s="85">
-        <v>10</v>
-      </c>
-      <c r="P9" s="85">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="85">
-        <v>10</v>
-      </c>
-      <c r="R9" s="132">
-        <v>11</v>
-      </c>
-      <c r="S9" s="133">
-        <v>11</v>
-      </c>
-      <c r="T9" s="134">
-        <v>11</v>
-      </c>
-      <c r="U9" s="135">
-        <v>11</v>
-      </c>
-      <c r="V9" s="85">
-        <v>9</v>
-      </c>
-      <c r="W9" s="85">
-        <v>9</v>
-      </c>
-      <c r="X9" s="85">
-        <v>7</v>
-      </c>
-      <c r="Y9" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z9" s="86" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB9" s="153"/>
-      <c r="AC9" s="153"/>
-      <c r="AD9" s="154"/>
-      <c r="AE9" s="154"/>
-      <c r="AF9" s="154"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:32">
-      <c r="A10" s="64"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="70"/>
-      <c r="AB10" s="153"/>
-      <c r="AC10" s="153"/>
-      <c r="AD10" s="154"/>
-      <c r="AE10" s="154"/>
-      <c r="AF10" s="154"/>
+      <c r="AB10" s="150"/>
+      <c r="AC10" s="150"/>
+      <c r="AD10" s="151"/>
+      <c r="AE10" s="151"/>
+      <c r="AF10" s="151"/>
     </row>
     <row r="11" customHeight="1" spans="1:32">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="70" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="78">
@@ -3796,78 +3980,74 @@
       <c r="E11" s="79">
         <v>21000</v>
       </c>
-      <c r="F11" s="71">
+      <c r="F11" s="68">
         <v>22000</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="70">
+      <c r="H11" s="67">
         <v>1</v>
       </c>
-      <c r="I11" s="74"/>
-      <c r="J11" s="120">
+      <c r="I11" s="71"/>
+      <c r="J11" s="119">
         <v>4</v>
       </c>
-      <c r="K11" s="121">
-        <v>4</v>
-      </c>
-      <c r="L11" s="122">
-        <v>4</v>
-      </c>
-      <c r="M11" s="119">
+      <c r="K11" s="120"/>
+      <c r="L11" s="121">
+        <v>2</v>
+      </c>
+      <c r="M11" s="71">
         <v>3</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="71">
         <v>3</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="71">
         <v>2</v>
       </c>
-      <c r="P11" s="123">
+      <c r="P11" s="122">
         <v>3</v>
       </c>
-      <c r="Q11" s="149">
+      <c r="Q11" s="124">
         <v>3</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="120"/>
+      <c r="S11" s="121">
+        <v>1</v>
+      </c>
+      <c r="T11" s="71">
         <v>2</v>
       </c>
-      <c r="S11" s="122">
-        <v>2</v>
-      </c>
-      <c r="T11" s="119">
-        <v>2</v>
-      </c>
-      <c r="U11" s="119">
+      <c r="U11" s="71">
         <v>1</v>
       </c>
-      <c r="V11" s="119" t="s">
+      <c r="V11" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="W11" s="119" t="s">
+      <c r="W11" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="X11" s="119" t="s">
+      <c r="X11" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="Y11" s="119" t="s">
+      <c r="Y11" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="Z11" s="63" t="s">
+      <c r="Z11" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="AB11" s="153"/>
-      <c r="AC11" s="154"/>
-      <c r="AD11" s="154"/>
-      <c r="AE11" s="154"/>
-      <c r="AF11" s="154"/>
+      <c r="AB11" s="150"/>
+      <c r="AC11" s="151"/>
+      <c r="AD11" s="151"/>
+      <c r="AE11" s="151"/>
+      <c r="AF11" s="151"/>
     </row>
     <row r="12" customHeight="1" spans="1:28">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="62" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="78">
@@ -3879,72 +4059,68 @@
       <c r="E12" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="71"/>
-      <c r="G12" s="69" t="s">
+      <c r="F12" s="68"/>
+      <c r="G12" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="70">
+      <c r="H12" s="67">
         <v>1</v>
       </c>
-      <c r="I12" s="74"/>
-      <c r="J12" s="124">
+      <c r="I12" s="71"/>
+      <c r="J12" s="119">
         <v>4</v>
       </c>
-      <c r="K12" s="125">
-        <v>4</v>
-      </c>
-      <c r="L12" s="126">
-        <v>4</v>
-      </c>
-      <c r="M12" s="74">
+      <c r="K12" s="120"/>
+      <c r="L12" s="121">
+        <v>2</v>
+      </c>
+      <c r="M12" s="71">
         <v>3</v>
       </c>
-      <c r="N12" s="74">
+      <c r="N12" s="71">
         <v>3</v>
       </c>
-      <c r="O12" s="74">
+      <c r="O12" s="71">
         <v>2</v>
       </c>
-      <c r="P12" s="127">
+      <c r="P12" s="122">
         <v>3</v>
       </c>
-      <c r="Q12" s="129">
+      <c r="Q12" s="124">
         <v>3</v>
       </c>
-      <c r="R12" s="125">
-        <v>3</v>
-      </c>
-      <c r="S12" s="126">
-        <v>3</v>
-      </c>
-      <c r="T12" s="74">
+      <c r="R12" s="120"/>
+      <c r="S12" s="121">
         <v>2</v>
       </c>
-      <c r="U12" s="74">
+      <c r="T12" s="71">
         <v>2</v>
       </c>
-      <c r="V12" s="69" t="s">
+      <c r="U12" s="71">
+        <v>2</v>
+      </c>
+      <c r="V12" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="W12" s="74" t="s">
+      <c r="W12" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="X12" s="74" t="s">
+      <c r="X12" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="Y12" s="74" t="s">
+      <c r="Y12" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="Z12" s="70" t="s">
+      <c r="Z12" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="AB12" s="153"/>
+      <c r="AB12" s="150"/>
     </row>
     <row r="13" customHeight="1" spans="1:28">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="62" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="78">
@@ -3956,69 +4132,65 @@
       <c r="E13" s="80">
         <v>20500</v>
       </c>
-      <c r="F13" s="71"/>
-      <c r="G13" s="69">
+      <c r="F13" s="68"/>
+      <c r="G13" s="66">
         <v>1</v>
       </c>
-      <c r="H13" s="70">
+      <c r="H13" s="67">
         <v>2</v>
       </c>
-      <c r="I13" s="74"/>
-      <c r="J13" s="128">
+      <c r="I13" s="71"/>
+      <c r="J13" s="123">
         <v>5</v>
       </c>
-      <c r="K13" s="129">
+      <c r="K13" s="124">
         <v>5</v>
       </c>
-      <c r="L13" s="125">
-        <v>5</v>
-      </c>
-      <c r="M13" s="126">
-        <v>5</v>
-      </c>
-      <c r="N13" s="74">
+      <c r="L13" s="120"/>
+      <c r="M13" s="121">
+        <v>3</v>
+      </c>
+      <c r="N13" s="71">
         <v>4</v>
       </c>
-      <c r="O13" s="74">
+      <c r="O13" s="71">
         <v>4</v>
       </c>
-      <c r="P13" s="74">
+      <c r="P13" s="71">
         <v>3</v>
       </c>
-      <c r="Q13" s="127">
+      <c r="Q13" s="122">
         <v>4</v>
       </c>
-      <c r="R13" s="129">
+      <c r="R13" s="124">
         <v>4</v>
       </c>
-      <c r="S13" s="125">
-        <v>4</v>
-      </c>
-      <c r="T13" s="126">
-        <v>4</v>
-      </c>
-      <c r="U13" s="74">
+      <c r="S13" s="120"/>
+      <c r="T13" s="121">
+        <v>2</v>
+      </c>
+      <c r="U13" s="71">
         <v>3</v>
       </c>
-      <c r="V13" s="74">
+      <c r="V13" s="71">
         <v>3</v>
       </c>
-      <c r="W13" s="74" t="s">
+      <c r="W13" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="X13" s="74" t="s">
+      <c r="X13" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="Y13" s="74" t="s">
+      <c r="Y13" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="Z13" s="70" t="s">
+      <c r="Z13" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="AB13" s="153"/>
+      <c r="AB13" s="150"/>
     </row>
     <row r="14" customHeight="1" spans="1:26">
-      <c r="A14" s="72" t="s">
+      <c r="A14" s="69" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="81" t="s">
@@ -4041,23 +4213,21 @@
         <v>4</v>
       </c>
       <c r="I14" s="85"/>
-      <c r="J14" s="131">
+      <c r="J14" s="129">
         <v>9</v>
       </c>
-      <c r="K14" s="136">
+      <c r="K14" s="130">
         <v>9</v>
       </c>
-      <c r="L14" s="132">
+      <c r="L14" s="131">
         <v>11</v>
       </c>
-      <c r="M14" s="133">
+      <c r="M14" s="132">
         <v>11</v>
       </c>
-      <c r="N14" s="134">
-        <v>11</v>
-      </c>
-      <c r="O14" s="135">
-        <v>11</v>
+      <c r="N14" s="133"/>
+      <c r="O14" s="134">
+        <v>6</v>
       </c>
       <c r="P14" s="85">
         <v>9</v>
@@ -4068,17 +4238,15 @@
       <c r="R14" s="85">
         <v>9</v>
       </c>
-      <c r="S14" s="132">
+      <c r="S14" s="131">
         <v>10</v>
       </c>
-      <c r="T14" s="133">
+      <c r="T14" s="132">
         <v>10</v>
       </c>
-      <c r="U14" s="134">
-        <v>10</v>
-      </c>
-      <c r="V14" s="135">
-        <v>10</v>
+      <c r="U14" s="133"/>
+      <c r="V14" s="134">
+        <v>5</v>
       </c>
       <c r="W14" s="85">
         <v>8</v>
@@ -4094,1378 +4262,1380 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:26">
-      <c r="A15" s="87"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="88"/>
-      <c r="I15" s="88"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="88"/>
-      <c r="M15" s="88"/>
-      <c r="N15" s="88"/>
-      <c r="O15" s="88"/>
-      <c r="P15" s="88"/>
-      <c r="Q15" s="88"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="88"/>
-      <c r="T15" s="88"/>
-      <c r="U15" s="88"/>
-      <c r="V15" s="88"/>
-      <c r="W15" s="88"/>
-      <c r="X15" s="88"/>
-      <c r="Y15" s="88"/>
-      <c r="Z15" s="88"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="87"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="87"/>
+      <c r="N15" s="87"/>
+      <c r="O15" s="87"/>
+      <c r="P15" s="87"/>
+      <c r="Q15" s="87"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="87"/>
+      <c r="T15" s="87"/>
+      <c r="U15" s="87"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="87"/>
+      <c r="X15" s="87"/>
+      <c r="Y15" s="87"/>
+      <c r="Z15" s="87"/>
     </row>
     <row r="16" customHeight="1" spans="1:26">
-      <c r="A16" s="87"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="137"/>
-      <c r="K16" s="138" t="s">
+      <c r="A16" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="L16" s="138"/>
-      <c r="M16" s="138"/>
-      <c r="N16" s="138"/>
-      <c r="O16" s="139" t="s">
+      <c r="B16" s="25"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="88"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="P16" s="139"/>
-      <c r="Q16" s="139"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="139"/>
-      <c r="T16" s="139"/>
-      <c r="U16" s="139"/>
-      <c r="V16" s="139"/>
-      <c r="W16" s="139"/>
-      <c r="X16" s="139"/>
-      <c r="Y16" s="139"/>
-      <c r="Z16" s="139"/>
+      <c r="L16" s="136"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="136"/>
+      <c r="O16" s="137" t="s">
+        <v>33</v>
+      </c>
+      <c r="P16" s="137"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="137"/>
+      <c r="S16" s="137"/>
+      <c r="T16" s="137"/>
+      <c r="U16" s="137"/>
+      <c r="V16" s="137"/>
+      <c r="W16" s="137"/>
+      <c r="X16" s="137"/>
+      <c r="Y16" s="137"/>
+      <c r="Z16" s="137"/>
     </row>
     <row r="17" customHeight="1" spans="1:26">
-      <c r="A17" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="88"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="140"/>
-      <c r="K17" s="138" t="s">
+      <c r="A17" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="L17" s="138"/>
-      <c r="M17" s="138"/>
-      <c r="N17" s="138"/>
-      <c r="O17" s="139" t="s">
+      <c r="B17" s="25"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="88"/>
+      <c r="I17" s="88"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="P17" s="139"/>
-      <c r="Q17" s="139"/>
-      <c r="R17" s="139"/>
-      <c r="S17" s="139"/>
-      <c r="T17" s="139"/>
-      <c r="U17" s="139"/>
-      <c r="V17" s="139"/>
-      <c r="W17" s="139"/>
-      <c r="X17" s="139"/>
-      <c r="Y17" s="139"/>
-      <c r="Z17" s="139"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="137" t="s">
+        <v>36</v>
+      </c>
+      <c r="P17" s="137"/>
+      <c r="Q17" s="137"/>
+      <c r="R17" s="137"/>
+      <c r="S17" s="137"/>
+      <c r="T17" s="137"/>
+      <c r="U17" s="137"/>
+      <c r="V17" s="137"/>
+      <c r="W17" s="137"/>
+      <c r="X17" s="137"/>
+      <c r="Y17" s="137"/>
+      <c r="Z17" s="137"/>
     </row>
     <row r="18" customHeight="1" spans="1:26">
-      <c r="A18" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="141"/>
-      <c r="K18" s="138" t="s">
+      <c r="A18" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="138"/>
-      <c r="M18" s="138"/>
-      <c r="N18" s="138"/>
-      <c r="O18" s="139" t="s">
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="88"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="P18" s="139"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="139"/>
-      <c r="S18" s="139"/>
-      <c r="T18" s="139"/>
-      <c r="U18" s="139"/>
-      <c r="V18" s="139"/>
-      <c r="W18" s="139"/>
-      <c r="X18" s="139"/>
-      <c r="Y18" s="139"/>
-      <c r="Z18" s="139"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="136"/>
+      <c r="N18" s="136"/>
+      <c r="O18" s="137" t="s">
+        <v>39</v>
+      </c>
+      <c r="P18" s="137"/>
+      <c r="Q18" s="137"/>
+      <c r="R18" s="137"/>
+      <c r="S18" s="137"/>
+      <c r="T18" s="137"/>
+      <c r="U18" s="137"/>
+      <c r="V18" s="137"/>
+      <c r="W18" s="137"/>
+      <c r="X18" s="137"/>
+      <c r="Y18" s="137"/>
+      <c r="Z18" s="137"/>
     </row>
     <row r="19" customHeight="1" spans="1:27">
-      <c r="A19" s="90" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="142"/>
-      <c r="K19" s="138" t="s">
+      <c r="A19" s="89"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="136" t="s">
         <v>40</v>
       </c>
-      <c r="L19" s="138"/>
-      <c r="M19" s="138"/>
-      <c r="N19" s="138"/>
-      <c r="O19" s="139"/>
-      <c r="P19" s="139"/>
-      <c r="Q19" s="139"/>
-      <c r="R19" s="139"/>
-      <c r="S19" s="139"/>
-      <c r="T19" s="139"/>
-      <c r="U19" s="139"/>
-      <c r="V19" s="139"/>
-      <c r="W19" s="139"/>
-      <c r="X19" s="139"/>
-      <c r="Y19" s="139"/>
-      <c r="Z19" s="139"/>
-      <c r="AA19" s="155"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="136"/>
+      <c r="N19" s="136"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="137"/>
+      <c r="Q19" s="137"/>
+      <c r="R19" s="137"/>
+      <c r="S19" s="137"/>
+      <c r="T19" s="137"/>
+      <c r="U19" s="137"/>
+      <c r="V19" s="137"/>
+      <c r="W19" s="137"/>
+      <c r="X19" s="137"/>
+      <c r="Y19" s="137"/>
+      <c r="Z19" s="137"/>
+      <c r="AA19" s="153"/>
     </row>
     <row r="20" customHeight="1" spans="1:27">
-      <c r="A20" s="90"/>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="143"/>
-      <c r="K20" s="144" t="s">
+      <c r="A20" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="144" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="P20" s="144"/>
-      <c r="Q20" s="144"/>
-      <c r="R20" s="144"/>
-      <c r="S20" s="144"/>
-      <c r="T20" s="144"/>
-      <c r="U20" s="144"/>
-      <c r="V20" s="144"/>
-      <c r="W20" s="144"/>
-      <c r="X20" s="144"/>
-      <c r="Y20" s="144"/>
-      <c r="Z20" s="144"/>
-      <c r="AA20" s="155"/>
+      <c r="L20" s="142"/>
+      <c r="M20" s="142"/>
+      <c r="N20" s="142"/>
+      <c r="O20" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="153"/>
     </row>
     <row r="21" customHeight="1" spans="1:27">
-      <c r="A21" s="91"/>
-      <c r="B21" s="91"/>
-      <c r="G21" s="92"/>
-      <c r="H21" s="93"/>
-      <c r="I21" s="146"/>
-      <c r="J21" s="147"/>
-      <c r="K21" s="147"/>
-      <c r="L21" s="147"/>
-      <c r="M21" s="148"/>
-      <c r="N21" s="148"/>
-      <c r="O21" s="148"/>
-      <c r="P21" s="147"/>
-      <c r="Q21" s="147"/>
-      <c r="R21" s="147"/>
-      <c r="S21" s="147"/>
-      <c r="T21" s="148"/>
-      <c r="U21" s="148"/>
-      <c r="V21" s="148"/>
-      <c r="W21" s="148"/>
-      <c r="X21" s="148"/>
-      <c r="Y21" s="148"/>
-      <c r="Z21" s="148"/>
-      <c r="AA21" s="155"/>
+      <c r="A21" s="90"/>
+      <c r="B21" s="90"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="143"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="145"/>
+      <c r="N21" s="145"/>
+      <c r="O21" s="145"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="144"/>
+      <c r="S21" s="144"/>
+      <c r="T21" s="145"/>
+      <c r="U21" s="145"/>
+      <c r="V21" s="145"/>
+      <c r="W21" s="145"/>
+      <c r="X21" s="145"/>
+      <c r="Y21" s="145"/>
+      <c r="Z21" s="145"/>
+      <c r="AA21" s="153"/>
     </row>
     <row r="22" customHeight="1" spans="2:26">
-      <c r="B22" s="94" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="95" t="s">
+      <c r="B22" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="96" t="s">
+      <c r="C22" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="96"/>
-      <c r="K22" s="96"/>
-      <c r="L22" s="96"/>
-      <c r="M22" s="96"/>
-      <c r="N22" s="96"/>
-      <c r="O22" s="96"/>
-      <c r="P22" s="96"/>
-      <c r="Q22" s="96"/>
-      <c r="R22" s="96"/>
-      <c r="S22" s="96"/>
-      <c r="T22" s="96"/>
-      <c r="U22" s="96"/>
-      <c r="V22" s="96"/>
-      <c r="W22" s="96"/>
-      <c r="X22" s="96"/>
-      <c r="Y22" s="96"/>
-      <c r="Z22" s="96"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
+      <c r="F22" s="94"/>
+      <c r="G22" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="94"/>
+      <c r="I22" s="94"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="94"/>
+      <c r="L22" s="94"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="94"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="94"/>
+      <c r="T22" s="94"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="94"/>
+      <c r="X22" s="94"/>
+      <c r="Y22" s="94"/>
+      <c r="Z22" s="94"/>
     </row>
     <row r="23" customHeight="1" spans="2:26">
-      <c r="B23" s="97" t="s">
+      <c r="B23" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="96" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="96"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="96" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="90"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="90"/>
+      <c r="R23" s="90"/>
+      <c r="S23" s="90"/>
+      <c r="T23" s="90"/>
+      <c r="U23" s="90"/>
+      <c r="V23" s="90"/>
+      <c r="W23" s="90"/>
+      <c r="X23" s="90"/>
+      <c r="Y23" s="90"/>
+      <c r="Z23" s="90"/>
+    </row>
+    <row r="24" customHeight="1" spans="2:26">
+      <c r="B24" s="95" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="96" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="90"/>
+      <c r="O24" s="90"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="90"/>
+      <c r="R24" s="90"/>
+      <c r="S24" s="90"/>
+      <c r="T24" s="90"/>
+      <c r="U24" s="90"/>
+      <c r="V24" s="90"/>
+      <c r="W24" s="90"/>
+      <c r="X24" s="90"/>
+      <c r="Y24" s="90"/>
+      <c r="Z24" s="90"/>
+    </row>
+    <row r="25" customHeight="1" spans="2:26">
+      <c r="B25" s="95" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="96" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="96"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="96" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="90"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="90"/>
+      <c r="O25" s="90"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="90"/>
+      <c r="R25" s="90"/>
+      <c r="S25" s="90"/>
+      <c r="T25" s="90"/>
+      <c r="U25" s="90"/>
+      <c r="V25" s="90"/>
+      <c r="W25" s="90"/>
+      <c r="X25" s="90"/>
+      <c r="Y25" s="90"/>
+      <c r="Z25" s="90"/>
+    </row>
+    <row r="26" customHeight="1" spans="2:26">
+      <c r="B26" s="95" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="96" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="96" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" s="90"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="90"/>
+      <c r="K26" s="90"/>
+      <c r="L26" s="90"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="90"/>
+      <c r="O26" s="90"/>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="90"/>
+      <c r="R26" s="90"/>
+      <c r="S26" s="90"/>
+      <c r="T26" s="90"/>
+      <c r="U26" s="90"/>
+      <c r="V26" s="90"/>
+      <c r="W26" s="90"/>
+      <c r="X26" s="90"/>
+      <c r="Y26" s="90"/>
+      <c r="Z26" s="90"/>
+    </row>
+    <row r="27" customHeight="1" spans="2:26">
+      <c r="B27" s="95" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="96" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="96"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="96"/>
+      <c r="G27" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="90"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="90"/>
+      <c r="K27" s="90"/>
+      <c r="L27" s="90"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="90"/>
+      <c r="O27" s="90"/>
+      <c r="P27" s="90"/>
+      <c r="Q27" s="90"/>
+      <c r="R27" s="90"/>
+      <c r="S27" s="90"/>
+      <c r="T27" s="90"/>
+      <c r="U27" s="90"/>
+      <c r="V27" s="90"/>
+      <c r="W27" s="90"/>
+      <c r="X27" s="90"/>
+      <c r="Y27" s="90"/>
+      <c r="Z27" s="90"/>
+    </row>
+    <row r="28" customHeight="1" spans="2:26">
+      <c r="B28" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="96" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96" t="s">
+        <v>62</v>
+      </c>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="90"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="90"/>
+      <c r="O28" s="90"/>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="90"/>
+      <c r="R28" s="90"/>
+      <c r="S28" s="90"/>
+      <c r="T28" s="90"/>
+      <c r="U28" s="90"/>
+      <c r="V28" s="90"/>
+      <c r="W28" s="90"/>
+      <c r="X28" s="90"/>
+      <c r="Y28" s="90"/>
+      <c r="Z28" s="90"/>
+    </row>
+    <row r="29" customHeight="1" spans="2:26">
+      <c r="B29" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="96" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="96"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="96" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" s="90"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="90"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="90"/>
+      <c r="R29" s="90"/>
+      <c r="S29" s="90"/>
+      <c r="T29" s="90"/>
+      <c r="U29" s="90"/>
+      <c r="V29" s="90"/>
+      <c r="W29" s="90"/>
+      <c r="X29" s="90"/>
+      <c r="Y29" s="90"/>
+      <c r="Z29" s="90"/>
+    </row>
+    <row r="30" customHeight="1" spans="2:26">
+      <c r="B30" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="96" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="96" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="90"/>
+      <c r="O30" s="90"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="90"/>
+      <c r="R30" s="90"/>
+      <c r="S30" s="90"/>
+      <c r="T30" s="90"/>
+      <c r="U30" s="90"/>
+      <c r="V30" s="90"/>
+      <c r="W30" s="90"/>
+      <c r="X30" s="90"/>
+      <c r="Y30" s="90"/>
+      <c r="Z30" s="90"/>
+    </row>
+    <row r="32" customHeight="1" spans="2:26">
+      <c r="B32" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="98" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="98" t="s">
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98"/>
+      <c r="N32" s="98"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="98"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="98"/>
+      <c r="U32" s="98"/>
+      <c r="V32" s="98"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="98"/>
+      <c r="Z32" s="98"/>
+    </row>
+    <row r="33" customHeight="1" spans="2:26">
+      <c r="B33" s="99" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="96"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="96" t="s">
+        <v>71</v>
+      </c>
+      <c r="H33" s="90"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="90"/>
+      <c r="M33" s="90"/>
+      <c r="N33" s="90"/>
+      <c r="O33" s="90"/>
+      <c r="P33" s="90"/>
+      <c r="Q33" s="90"/>
+      <c r="R33" s="90"/>
+      <c r="S33" s="90"/>
+      <c r="T33" s="90"/>
+      <c r="U33" s="90"/>
+      <c r="V33" s="90"/>
+      <c r="W33" s="90"/>
+      <c r="X33" s="90"/>
+      <c r="Y33" s="90"/>
+      <c r="Z33" s="90"/>
+    </row>
+    <row r="34" customHeight="1" spans="2:26">
+      <c r="B34" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="96" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="96"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="96"/>
+      <c r="G34" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" s="90"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="90"/>
+      <c r="M34" s="90"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="90"/>
+      <c r="P34" s="90"/>
+      <c r="Q34" s="90"/>
+      <c r="R34" s="90"/>
+      <c r="S34" s="90"/>
+      <c r="T34" s="90"/>
+      <c r="U34" s="90"/>
+      <c r="V34" s="90"/>
+      <c r="W34" s="90"/>
+      <c r="X34" s="90"/>
+      <c r="Y34" s="90"/>
+      <c r="Z34" s="90"/>
+    </row>
+    <row r="35" customHeight="1" spans="2:26">
+      <c r="B35" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="96" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="96" t="s">
+        <v>75</v>
+      </c>
+      <c r="H35" s="90"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="90"/>
+      <c r="K35" s="90"/>
+      <c r="L35" s="90"/>
+      <c r="M35" s="90"/>
+      <c r="N35" s="90"/>
+      <c r="O35" s="90"/>
+      <c r="P35" s="90"/>
+      <c r="Q35" s="90"/>
+      <c r="R35" s="90"/>
+      <c r="S35" s="90"/>
+      <c r="T35" s="90"/>
+      <c r="U35" s="90"/>
+      <c r="V35" s="90"/>
+      <c r="W35" s="90"/>
+      <c r="X35" s="90"/>
+      <c r="Y35" s="90"/>
+      <c r="Z35" s="90"/>
+    </row>
+    <row r="36" customHeight="1" spans="2:26">
+      <c r="B36" s="99" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="96" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="96"/>
+      <c r="E36" s="96"/>
+      <c r="F36" s="96"/>
+      <c r="G36" s="96" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="90"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="90"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="90"/>
+      <c r="N36" s="90"/>
+      <c r="O36" s="90"/>
+      <c r="P36" s="90"/>
+      <c r="Q36" s="90"/>
+      <c r="R36" s="90"/>
+      <c r="S36" s="90"/>
+      <c r="T36" s="90"/>
+      <c r="U36" s="90"/>
+      <c r="V36" s="90"/>
+      <c r="W36" s="90"/>
+      <c r="X36" s="90"/>
+      <c r="Y36" s="90"/>
+      <c r="Z36" s="90"/>
+    </row>
+    <row r="37" customHeight="1" spans="2:26">
+      <c r="B37" s="99" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="96" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="96"/>
+      <c r="E37" s="96"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="90"/>
+      <c r="I37" s="90"/>
+      <c r="J37" s="90"/>
+      <c r="K37" s="90"/>
+      <c r="L37" s="90"/>
+      <c r="M37" s="90"/>
+      <c r="N37" s="90"/>
+      <c r="O37" s="90"/>
+      <c r="P37" s="90"/>
+      <c r="Q37" s="90"/>
+      <c r="R37" s="90"/>
+      <c r="S37" s="90"/>
+      <c r="T37" s="90"/>
+      <c r="U37" s="90"/>
+      <c r="V37" s="90"/>
+      <c r="W37" s="90"/>
+      <c r="X37" s="90"/>
+      <c r="Y37" s="90"/>
+      <c r="Z37" s="90"/>
+    </row>
+    <row r="39" customHeight="1" spans="2:26">
+      <c r="B39" s="100" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="101" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="101"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="101"/>
+      <c r="G39" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="H39" s="101"/>
+      <c r="I39" s="101"/>
+      <c r="J39" s="101"/>
+      <c r="K39" s="101"/>
+      <c r="L39" s="101"/>
+      <c r="M39" s="101"/>
+      <c r="N39" s="101"/>
+      <c r="O39" s="101"/>
+      <c r="P39" s="101"/>
+      <c r="Q39" s="101"/>
+      <c r="R39" s="101"/>
+      <c r="S39" s="101"/>
+      <c r="T39" s="101"/>
+      <c r="U39" s="101"/>
+      <c r="V39" s="101"/>
+      <c r="W39" s="101"/>
+      <c r="X39" s="101"/>
+      <c r="Y39" s="101"/>
+      <c r="Z39" s="101"/>
+    </row>
+    <row r="40" customHeight="1" spans="2:26">
+      <c r="B40" s="102" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="96" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="96"/>
+      <c r="E40" s="96"/>
+      <c r="F40" s="96"/>
+      <c r="G40" s="96" t="s">
+        <v>84</v>
+      </c>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="90"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="90"/>
+      <c r="R40" s="90"/>
+      <c r="S40" s="90"/>
+      <c r="T40" s="90"/>
+      <c r="U40" s="90"/>
+      <c r="V40" s="90"/>
+      <c r="W40" s="90"/>
+      <c r="X40" s="90"/>
+      <c r="Y40" s="90"/>
+      <c r="Z40" s="90"/>
+    </row>
+    <row r="41" customHeight="1" spans="2:26">
+      <c r="B41" s="102" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="96" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="90"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="90"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="90"/>
+      <c r="P41" s="90"/>
+      <c r="Q41" s="90"/>
+      <c r="R41" s="90"/>
+      <c r="S41" s="90"/>
+      <c r="T41" s="90"/>
+      <c r="U41" s="90"/>
+      <c r="V41" s="90"/>
+      <c r="W41" s="90"/>
+      <c r="X41" s="90"/>
+      <c r="Y41" s="90"/>
+      <c r="Z41" s="90"/>
+    </row>
+    <row r="42" customHeight="1" spans="2:26">
+      <c r="B42" s="102" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="96" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="96"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="96" t="s">
+        <v>90</v>
+      </c>
+      <c r="H42" s="90"/>
+      <c r="I42" s="90"/>
+      <c r="J42" s="90"/>
+      <c r="K42" s="90"/>
+      <c r="L42" s="90"/>
+      <c r="M42" s="90"/>
+      <c r="N42" s="90"/>
+      <c r="O42" s="90"/>
+      <c r="P42" s="90"/>
+      <c r="Q42" s="90"/>
+      <c r="R42" s="90"/>
+      <c r="S42" s="90"/>
+      <c r="T42" s="90"/>
+      <c r="U42" s="90"/>
+      <c r="V42" s="90"/>
+      <c r="W42" s="90"/>
+      <c r="X42" s="90"/>
+      <c r="Y42" s="90"/>
+      <c r="Z42" s="90"/>
+    </row>
+    <row r="43" customHeight="1" spans="2:26">
+      <c r="B43" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="96" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="96"/>
+      <c r="E43" s="96"/>
+      <c r="F43" s="96"/>
+      <c r="G43" s="96" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" s="90"/>
+      <c r="I43" s="90"/>
+      <c r="J43" s="90"/>
+      <c r="K43" s="90"/>
+      <c r="L43" s="90"/>
+      <c r="M43" s="90"/>
+      <c r="N43" s="90"/>
+      <c r="O43" s="90"/>
+      <c r="P43" s="90"/>
+      <c r="Q43" s="90"/>
+      <c r="R43" s="90"/>
+      <c r="S43" s="90"/>
+      <c r="T43" s="90"/>
+      <c r="U43" s="90"/>
+      <c r="V43" s="90"/>
+      <c r="W43" s="90"/>
+      <c r="X43" s="90"/>
+      <c r="Y43" s="90"/>
+      <c r="Z43" s="90"/>
+    </row>
+    <row r="45" customHeight="1" spans="2:26">
+      <c r="B45" s="100" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="101" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="101"/>
+      <c r="E45" s="101"/>
+      <c r="F45" s="101"/>
+      <c r="G45" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="H45" s="101"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="101"/>
+      <c r="M45" s="101"/>
+      <c r="N45" s="101"/>
+      <c r="O45" s="101"/>
+      <c r="P45" s="101"/>
+      <c r="Q45" s="101"/>
+      <c r="R45" s="101"/>
+      <c r="S45" s="101"/>
+      <c r="T45" s="101"/>
+      <c r="U45" s="101"/>
+      <c r="V45" s="101"/>
+      <c r="W45" s="101"/>
+      <c r="X45" s="101"/>
+      <c r="Y45" s="101"/>
+      <c r="Z45" s="101"/>
+    </row>
+    <row r="46" customHeight="1" spans="2:26">
+      <c r="B46" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98" t="s">
-        <v>48</v>
-      </c>
-      <c r="H23" s="91"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="91"/>
-      <c r="R23" s="91"/>
-      <c r="S23" s="91"/>
-      <c r="T23" s="91"/>
-      <c r="U23" s="91"/>
-      <c r="V23" s="91"/>
-      <c r="W23" s="91"/>
-      <c r="X23" s="91"/>
-      <c r="Y23" s="91"/>
-      <c r="Z23" s="91"/>
-    </row>
-    <row r="24" customHeight="1" spans="2:26">
-      <c r="B24" s="97" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="98" t="s">
+      <c r="C46" s="96" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="96"/>
+      <c r="E46" s="96"/>
+      <c r="F46" s="96"/>
+      <c r="G46" s="96" t="s">
+        <v>84</v>
+      </c>
+      <c r="H46" s="90"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="90"/>
+      <c r="K46" s="90"/>
+      <c r="L46" s="90"/>
+      <c r="M46" s="90"/>
+      <c r="N46" s="90"/>
+      <c r="O46" s="90"/>
+      <c r="P46" s="90"/>
+      <c r="Q46" s="90"/>
+      <c r="R46" s="90"/>
+      <c r="S46" s="90"/>
+      <c r="T46" s="90"/>
+      <c r="U46" s="90"/>
+      <c r="V46" s="90"/>
+      <c r="W46" s="90"/>
+      <c r="X46" s="90"/>
+      <c r="Y46" s="90"/>
+      <c r="Z46" s="90"/>
+    </row>
+    <row r="47" customHeight="1" spans="2:26">
+      <c r="B47" s="102" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" s="96" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" s="96"/>
+      <c r="E47" s="96"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="96" t="s">
+        <v>96</v>
+      </c>
+      <c r="H47" s="90"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="90"/>
+      <c r="K47" s="90"/>
+      <c r="L47" s="90"/>
+      <c r="M47" s="90"/>
+      <c r="N47" s="90"/>
+      <c r="O47" s="90"/>
+      <c r="P47" s="90"/>
+      <c r="Q47" s="90"/>
+      <c r="R47" s="90"/>
+      <c r="S47" s="90"/>
+      <c r="T47" s="90"/>
+      <c r="U47" s="90"/>
+      <c r="V47" s="90"/>
+      <c r="W47" s="90"/>
+      <c r="X47" s="90"/>
+      <c r="Y47" s="90"/>
+      <c r="Z47" s="90"/>
+    </row>
+    <row r="48" customHeight="1" spans="2:26">
+      <c r="B48" s="102" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="96" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" s="96"/>
+      <c r="E48" s="96"/>
+      <c r="F48" s="96"/>
+      <c r="G48" s="96" t="s">
+        <v>87</v>
+      </c>
+      <c r="H48" s="90"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="90"/>
+      <c r="K48" s="90"/>
+      <c r="L48" s="90"/>
+      <c r="M48" s="90"/>
+      <c r="N48" s="90"/>
+      <c r="O48" s="90"/>
+      <c r="P48" s="90"/>
+      <c r="Q48" s="90"/>
+      <c r="R48" s="90"/>
+      <c r="S48" s="90"/>
+      <c r="T48" s="90"/>
+      <c r="U48" s="90"/>
+      <c r="V48" s="90"/>
+      <c r="W48" s="90"/>
+      <c r="X48" s="90"/>
+      <c r="Y48" s="90"/>
+      <c r="Z48" s="90"/>
+    </row>
+    <row r="49" customHeight="1" spans="2:26">
+      <c r="B49" s="102" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="96" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" s="96"/>
+      <c r="E49" s="96"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="96" t="s">
+        <v>90</v>
+      </c>
+      <c r="H49" s="90"/>
+      <c r="I49" s="90"/>
+      <c r="J49" s="90"/>
+      <c r="K49" s="90"/>
+      <c r="L49" s="90"/>
+      <c r="M49" s="90"/>
+      <c r="N49" s="90"/>
+      <c r="O49" s="90"/>
+      <c r="P49" s="90"/>
+      <c r="Q49" s="90"/>
+      <c r="R49" s="90"/>
+      <c r="S49" s="90"/>
+      <c r="T49" s="90"/>
+      <c r="U49" s="90"/>
+      <c r="V49" s="90"/>
+      <c r="W49" s="90"/>
+      <c r="X49" s="90"/>
+      <c r="Y49" s="90"/>
+      <c r="Z49" s="90"/>
+    </row>
+    <row r="50" customHeight="1" spans="2:26">
+      <c r="B50" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" s="96" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="96"/>
+      <c r="E50" s="96"/>
+      <c r="F50" s="96"/>
+      <c r="G50" s="96" t="s">
+        <v>92</v>
+      </c>
+      <c r="H50" s="90"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="90"/>
+      <c r="K50" s="90"/>
+      <c r="L50" s="90"/>
+      <c r="M50" s="90"/>
+      <c r="N50" s="90"/>
+      <c r="O50" s="90"/>
+      <c r="P50" s="90"/>
+      <c r="Q50" s="90"/>
+      <c r="R50" s="90"/>
+      <c r="S50" s="90"/>
+      <c r="T50" s="90"/>
+      <c r="U50" s="90"/>
+      <c r="V50" s="90"/>
+      <c r="W50" s="90"/>
+      <c r="X50" s="90"/>
+      <c r="Y50" s="90"/>
+      <c r="Z50" s="90"/>
+    </row>
+    <row r="52" customHeight="1" spans="2:26">
+      <c r="B52" s="103" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="104" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="104"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104" t="s">
+        <v>46</v>
+      </c>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="104"/>
+      <c r="M52" s="104"/>
+      <c r="N52" s="104"/>
+      <c r="O52" s="104"/>
+      <c r="P52" s="104"/>
+      <c r="Q52" s="104"/>
+      <c r="R52" s="104"/>
+      <c r="S52" s="104"/>
+      <c r="T52" s="104"/>
+      <c r="U52" s="104"/>
+      <c r="V52" s="104"/>
+      <c r="W52" s="104"/>
+      <c r="X52" s="104"/>
+      <c r="Y52" s="104"/>
+      <c r="Z52" s="104"/>
+    </row>
+    <row r="53" customHeight="1" spans="2:26">
+      <c r="B53" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98" t="s">
+      <c r="C53" s="106" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" s="106"/>
+      <c r="E53" s="106"/>
+      <c r="F53" s="106"/>
+      <c r="G53" s="96" t="s">
+        <v>84</v>
+      </c>
+      <c r="H53" s="90"/>
+      <c r="I53" s="90"/>
+      <c r="J53" s="90"/>
+      <c r="K53" s="90"/>
+      <c r="L53" s="90"/>
+      <c r="M53" s="90"/>
+      <c r="N53" s="90"/>
+      <c r="O53" s="90"/>
+      <c r="P53" s="90"/>
+      <c r="Q53" s="90"/>
+      <c r="R53" s="90"/>
+      <c r="S53" s="90"/>
+      <c r="T53" s="90"/>
+      <c r="U53" s="90"/>
+      <c r="V53" s="90"/>
+      <c r="W53" s="90"/>
+      <c r="X53" s="90"/>
+      <c r="Y53" s="90"/>
+      <c r="Z53" s="90"/>
+    </row>
+    <row r="54" customHeight="1" spans="2:26">
+      <c r="B54" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="91"/>
-      <c r="P24" s="91"/>
-      <c r="Q24" s="91"/>
-      <c r="R24" s="91"/>
-      <c r="S24" s="91"/>
-      <c r="T24" s="91"/>
-      <c r="U24" s="91"/>
-      <c r="V24" s="91"/>
-      <c r="W24" s="91"/>
-      <c r="X24" s="91"/>
-      <c r="Y24" s="91"/>
-      <c r="Z24" s="91"/>
-    </row>
-    <row r="25" customHeight="1" spans="2:26">
-      <c r="B25" s="97" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="98" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="98" t="s">
-        <v>52</v>
-      </c>
-      <c r="H25" s="91"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="91"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="91"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="91"/>
-      <c r="Q25" s="91"/>
-      <c r="R25" s="91"/>
-      <c r="S25" s="91"/>
-      <c r="T25" s="91"/>
-      <c r="U25" s="91"/>
-      <c r="V25" s="91"/>
-      <c r="W25" s="91"/>
-      <c r="X25" s="91"/>
-      <c r="Y25" s="91"/>
-      <c r="Z25" s="91"/>
-    </row>
-    <row r="26" customHeight="1" spans="2:26">
-      <c r="B26" s="97" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="98" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="98"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="98"/>
-      <c r="G26" s="98" t="s">
-        <v>55</v>
-      </c>
-      <c r="H26" s="91"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="91"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="91"/>
-      <c r="M26" s="91"/>
-      <c r="N26" s="91"/>
-      <c r="O26" s="91"/>
-      <c r="P26" s="91"/>
-      <c r="Q26" s="91"/>
-      <c r="R26" s="91"/>
-      <c r="S26" s="91"/>
-      <c r="T26" s="91"/>
-      <c r="U26" s="91"/>
-      <c r="V26" s="91"/>
-      <c r="W26" s="91"/>
-      <c r="X26" s="91"/>
-      <c r="Y26" s="91"/>
-      <c r="Z26" s="91"/>
-    </row>
-    <row r="27" customHeight="1" spans="2:26">
-      <c r="B27" s="97" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="98" t="s">
+      <c r="C54" s="106" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="106"/>
+      <c r="E54" s="106"/>
+      <c r="F54" s="106"/>
+      <c r="G54" s="96" t="s">
+        <v>99</v>
+      </c>
+      <c r="H54" s="90"/>
+      <c r="I54" s="90"/>
+      <c r="J54" s="90"/>
+      <c r="K54" s="90"/>
+      <c r="L54" s="90"/>
+      <c r="M54" s="90"/>
+      <c r="N54" s="90"/>
+      <c r="O54" s="90"/>
+      <c r="P54" s="90"/>
+      <c r="Q54" s="90"/>
+      <c r="R54" s="90"/>
+      <c r="S54" s="90"/>
+      <c r="T54" s="90"/>
+      <c r="U54" s="90"/>
+      <c r="V54" s="90"/>
+      <c r="W54" s="90"/>
+      <c r="X54" s="90"/>
+      <c r="Y54" s="90"/>
+      <c r="Z54" s="90"/>
+    </row>
+    <row r="55" customHeight="1" spans="2:26">
+      <c r="B55" s="105" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" s="96"/>
+      <c r="E55" s="96"/>
+      <c r="F55" s="96"/>
+      <c r="G55" s="96" t="s">
+        <v>101</v>
+      </c>
+      <c r="H55" s="90"/>
+      <c r="I55" s="90"/>
+      <c r="J55" s="90"/>
+      <c r="K55" s="90"/>
+      <c r="L55" s="90"/>
+      <c r="M55" s="90"/>
+      <c r="N55" s="90"/>
+      <c r="O55" s="90"/>
+      <c r="P55" s="90"/>
+      <c r="Q55" s="90"/>
+      <c r="R55" s="90"/>
+      <c r="S55" s="90"/>
+      <c r="T55" s="90"/>
+      <c r="U55" s="90"/>
+      <c r="V55" s="90"/>
+      <c r="W55" s="90"/>
+      <c r="X55" s="90"/>
+      <c r="Y55" s="90"/>
+      <c r="Z55" s="90"/>
+    </row>
+    <row r="56" customHeight="1" spans="2:26">
+      <c r="B56" s="105" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="D56" s="96"/>
+      <c r="E56" s="96"/>
+      <c r="F56" s="96"/>
+      <c r="G56" s="96" t="s">
+        <v>103</v>
+      </c>
+      <c r="H56" s="90"/>
+      <c r="I56" s="90"/>
+      <c r="J56" s="90"/>
+      <c r="K56" s="90"/>
+      <c r="L56" s="90"/>
+      <c r="M56" s="90"/>
+      <c r="N56" s="90"/>
+      <c r="O56" s="90"/>
+      <c r="P56" s="90"/>
+      <c r="Q56" s="90"/>
+      <c r="R56" s="90"/>
+      <c r="S56" s="90"/>
+      <c r="T56" s="90"/>
+      <c r="U56" s="90"/>
+      <c r="V56" s="90"/>
+      <c r="W56" s="90"/>
+      <c r="X56" s="90"/>
+      <c r="Y56" s="90"/>
+      <c r="Z56" s="90"/>
+    </row>
+    <row r="57" customHeight="1" spans="2:26">
+      <c r="B57" s="105" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="96" t="s">
+        <v>105</v>
+      </c>
+      <c r="D57" s="96"/>
+      <c r="E57" s="96"/>
+      <c r="F57" s="96"/>
+      <c r="G57" s="96" t="s">
+        <v>106</v>
+      </c>
+      <c r="H57" s="90"/>
+      <c r="I57" s="90"/>
+      <c r="J57" s="90"/>
+      <c r="K57" s="90"/>
+      <c r="L57" s="90"/>
+      <c r="M57" s="90"/>
+      <c r="N57" s="90"/>
+      <c r="O57" s="90"/>
+      <c r="P57" s="90"/>
+      <c r="Q57" s="90"/>
+      <c r="R57" s="90"/>
+      <c r="S57" s="90"/>
+      <c r="T57" s="90"/>
+      <c r="U57" s="90"/>
+      <c r="V57" s="90"/>
+      <c r="W57" s="90"/>
+      <c r="X57" s="90"/>
+      <c r="Y57" s="90"/>
+      <c r="Z57" s="90"/>
+    </row>
+    <row r="58" customHeight="1" spans="2:26">
+      <c r="B58" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="98"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="98" t="s">
-        <v>58</v>
-      </c>
-      <c r="H27" s="91"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="91"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="91"/>
-      <c r="M27" s="91"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="91"/>
-      <c r="P27" s="91"/>
-      <c r="Q27" s="91"/>
-      <c r="R27" s="91"/>
-      <c r="S27" s="91"/>
-      <c r="T27" s="91"/>
-      <c r="U27" s="91"/>
-      <c r="V27" s="91"/>
-      <c r="W27" s="91"/>
-      <c r="X27" s="91"/>
-      <c r="Y27" s="91"/>
-      <c r="Z27" s="91"/>
-    </row>
-    <row r="28" customHeight="1" spans="2:26">
-      <c r="B28" s="97" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="98" t="s">
+      <c r="C58" s="96" t="s">
+        <v>107</v>
+      </c>
+      <c r="D58" s="96"/>
+      <c r="E58" s="96"/>
+      <c r="F58" s="96"/>
+      <c r="G58" s="96" t="s">
+        <v>62</v>
+      </c>
+      <c r="H58" s="90"/>
+      <c r="I58" s="90"/>
+      <c r="J58" s="90"/>
+      <c r="K58" s="90"/>
+      <c r="L58" s="90"/>
+      <c r="M58" s="90"/>
+      <c r="N58" s="90"/>
+      <c r="O58" s="90"/>
+      <c r="P58" s="90"/>
+      <c r="Q58" s="90"/>
+      <c r="R58" s="90"/>
+      <c r="S58" s="90"/>
+      <c r="T58" s="90"/>
+      <c r="U58" s="90"/>
+      <c r="V58" s="90"/>
+      <c r="W58" s="90"/>
+      <c r="X58" s="90"/>
+      <c r="Y58" s="90"/>
+      <c r="Z58" s="90"/>
+    </row>
+    <row r="59" customHeight="1" spans="2:26">
+      <c r="B59" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="98"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="98"/>
-      <c r="G28" s="98" t="s">
-        <v>61</v>
-      </c>
-      <c r="H28" s="91"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="91"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="91"/>
-      <c r="M28" s="91"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="91"/>
-      <c r="P28" s="91"/>
-      <c r="Q28" s="91"/>
-      <c r="R28" s="91"/>
-      <c r="S28" s="91"/>
-      <c r="T28" s="91"/>
-      <c r="U28" s="91"/>
-      <c r="V28" s="91"/>
-      <c r="W28" s="91"/>
-      <c r="X28" s="91"/>
-      <c r="Y28" s="91"/>
-      <c r="Z28" s="91"/>
-    </row>
-    <row r="29" customHeight="1" spans="2:26">
-      <c r="B29" s="97" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="98" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="98"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
-      <c r="G29" s="98" t="s">
+      <c r="C59" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="H29" s="91"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="91"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="91"/>
-      <c r="M29" s="91"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="91"/>
-      <c r="P29" s="91"/>
-      <c r="Q29" s="91"/>
-      <c r="R29" s="91"/>
-      <c r="S29" s="91"/>
-      <c r="T29" s="91"/>
-      <c r="U29" s="91"/>
-      <c r="V29" s="91"/>
-      <c r="W29" s="91"/>
-      <c r="X29" s="91"/>
-      <c r="Y29" s="91"/>
-      <c r="Z29" s="91"/>
-    </row>
-    <row r="30" customHeight="1" spans="2:26">
-      <c r="B30" s="97" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="98" t="s">
+      <c r="D59" s="96"/>
+      <c r="E59" s="96"/>
+      <c r="F59" s="96"/>
+      <c r="G59" s="96" t="s">
+        <v>108</v>
+      </c>
+      <c r="H59" s="90"/>
+      <c r="I59" s="90"/>
+      <c r="J59" s="90"/>
+      <c r="K59" s="90"/>
+      <c r="L59" s="90"/>
+      <c r="M59" s="90"/>
+      <c r="N59" s="90"/>
+      <c r="O59" s="90"/>
+      <c r="P59" s="90"/>
+      <c r="Q59" s="90"/>
+      <c r="R59" s="90"/>
+      <c r="S59" s="90"/>
+      <c r="T59" s="90"/>
+      <c r="U59" s="90"/>
+      <c r="V59" s="90"/>
+      <c r="W59" s="90"/>
+      <c r="X59" s="90"/>
+      <c r="Y59" s="90"/>
+      <c r="Z59" s="90"/>
+    </row>
+    <row r="60" customHeight="1" spans="2:26">
+      <c r="B60" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="98"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="98"/>
-      <c r="G30" s="98" t="s">
-        <v>67</v>
-      </c>
-      <c r="H30" s="91"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="91"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="91"/>
-      <c r="M30" s="91"/>
-      <c r="N30" s="91"/>
-      <c r="O30" s="91"/>
-      <c r="P30" s="91"/>
-      <c r="Q30" s="91"/>
-      <c r="R30" s="91"/>
-      <c r="S30" s="91"/>
-      <c r="T30" s="91"/>
-      <c r="U30" s="91"/>
-      <c r="V30" s="91"/>
-      <c r="W30" s="91"/>
-      <c r="X30" s="91"/>
-      <c r="Y30" s="91"/>
-      <c r="Z30" s="91"/>
-    </row>
-    <row r="32" customHeight="1" spans="2:26">
-      <c r="B32" s="99" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="100" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="100"/>
-      <c r="E32" s="100"/>
-      <c r="F32" s="100"/>
-      <c r="G32" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="H32" s="101"/>
-      <c r="I32" s="101"/>
-      <c r="J32" s="101"/>
-      <c r="K32" s="101"/>
-      <c r="L32" s="101"/>
-      <c r="M32" s="101"/>
-      <c r="N32" s="101"/>
-      <c r="O32" s="101"/>
-      <c r="P32" s="101"/>
-      <c r="Q32" s="101"/>
-      <c r="R32" s="101"/>
-      <c r="S32" s="101"/>
-      <c r="T32" s="101"/>
-      <c r="U32" s="101"/>
-      <c r="V32" s="101"/>
-      <c r="W32" s="101"/>
-      <c r="X32" s="101"/>
-      <c r="Y32" s="101"/>
-      <c r="Z32" s="101"/>
-    </row>
-    <row r="33" customHeight="1" spans="2:26">
-      <c r="B33" s="102" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="98" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="98" t="s">
-        <v>70</v>
-      </c>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="91"/>
-      <c r="M33" s="91"/>
-      <c r="N33" s="91"/>
-      <c r="O33" s="91"/>
-      <c r="P33" s="91"/>
-      <c r="Q33" s="91"/>
-      <c r="R33" s="91"/>
-      <c r="S33" s="91"/>
-      <c r="T33" s="91"/>
-      <c r="U33" s="91"/>
-      <c r="V33" s="91"/>
-      <c r="W33" s="91"/>
-      <c r="X33" s="91"/>
-      <c r="Y33" s="91"/>
-      <c r="Z33" s="91"/>
-    </row>
-    <row r="34" customHeight="1" spans="2:26">
-      <c r="B34" s="102" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="98" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="H34" s="91"/>
-      <c r="I34" s="91"/>
-      <c r="J34" s="91"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="91"/>
-      <c r="M34" s="91"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="91"/>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="91"/>
-      <c r="S34" s="91"/>
-      <c r="T34" s="91"/>
-      <c r="U34" s="91"/>
-      <c r="V34" s="91"/>
-      <c r="W34" s="91"/>
-      <c r="X34" s="91"/>
-      <c r="Y34" s="91"/>
-      <c r="Z34" s="91"/>
-    </row>
-    <row r="35" customHeight="1" spans="2:26">
-      <c r="B35" s="102" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="98"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="98"/>
-      <c r="G35" s="98" t="s">
-        <v>74</v>
-      </c>
-      <c r="H35" s="91"/>
-      <c r="I35" s="91"/>
-      <c r="J35" s="91"/>
-      <c r="K35" s="91"/>
-      <c r="L35" s="91"/>
-      <c r="M35" s="91"/>
-      <c r="N35" s="91"/>
-      <c r="O35" s="91"/>
-      <c r="P35" s="91"/>
-      <c r="Q35" s="91"/>
-      <c r="R35" s="91"/>
-      <c r="S35" s="91"/>
-      <c r="T35" s="91"/>
-      <c r="U35" s="91"/>
-      <c r="V35" s="91"/>
-      <c r="W35" s="91"/>
-      <c r="X35" s="91"/>
-      <c r="Y35" s="91"/>
-      <c r="Z35" s="91"/>
-    </row>
-    <row r="36" customHeight="1" spans="2:26">
-      <c r="B36" s="102" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="98" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="98" t="s">
-        <v>77</v>
-      </c>
-      <c r="H36" s="91"/>
-      <c r="I36" s="91"/>
-      <c r="J36" s="91"/>
-      <c r="K36" s="91"/>
-      <c r="L36" s="91"/>
-      <c r="M36" s="91"/>
-      <c r="N36" s="91"/>
-      <c r="O36" s="91"/>
-      <c r="P36" s="91"/>
-      <c r="Q36" s="91"/>
-      <c r="R36" s="91"/>
-      <c r="S36" s="91"/>
-      <c r="T36" s="91"/>
-      <c r="U36" s="91"/>
-      <c r="V36" s="91"/>
-      <c r="W36" s="91"/>
-      <c r="X36" s="91"/>
-      <c r="Y36" s="91"/>
-      <c r="Z36" s="91"/>
-    </row>
-    <row r="37" customHeight="1" spans="2:26">
-      <c r="B37" s="102" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="98" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" s="98"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="98" t="s">
-        <v>80</v>
-      </c>
-      <c r="H37" s="91"/>
-      <c r="I37" s="91"/>
-      <c r="J37" s="91"/>
-      <c r="K37" s="91"/>
-      <c r="L37" s="91"/>
-      <c r="M37" s="91"/>
-      <c r="N37" s="91"/>
-      <c r="O37" s="91"/>
-      <c r="P37" s="91"/>
-      <c r="Q37" s="91"/>
-      <c r="R37" s="91"/>
-      <c r="S37" s="91"/>
-      <c r="T37" s="91"/>
-      <c r="U37" s="91"/>
-      <c r="V37" s="91"/>
-      <c r="W37" s="91"/>
-      <c r="X37" s="91"/>
-      <c r="Y37" s="91"/>
-      <c r="Z37" s="91"/>
-    </row>
-    <row r="39" customHeight="1" spans="2:26">
-      <c r="B39" s="103" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="104" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="104"/>
-      <c r="E39" s="104"/>
-      <c r="F39" s="104"/>
-      <c r="G39" s="105" t="s">
-        <v>45</v>
-      </c>
-      <c r="H39" s="105"/>
-      <c r="I39" s="105"/>
-      <c r="J39" s="105"/>
-      <c r="K39" s="105"/>
-      <c r="L39" s="105"/>
-      <c r="M39" s="105"/>
-      <c r="N39" s="105"/>
-      <c r="O39" s="105"/>
-      <c r="P39" s="105"/>
-      <c r="Q39" s="105"/>
-      <c r="R39" s="105"/>
-      <c r="S39" s="105"/>
-      <c r="T39" s="105"/>
-      <c r="U39" s="105"/>
-      <c r="V39" s="105"/>
-      <c r="W39" s="105"/>
-      <c r="X39" s="105"/>
-      <c r="Y39" s="105"/>
-      <c r="Z39" s="105"/>
-    </row>
-    <row r="40" customHeight="1" spans="2:26">
-      <c r="B40" s="106" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="98" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="98"/>
-      <c r="E40" s="98"/>
-      <c r="F40" s="98"/>
-      <c r="G40" s="98" t="s">
-        <v>83</v>
-      </c>
-      <c r="H40" s="91"/>
-      <c r="I40" s="91"/>
-      <c r="J40" s="91"/>
-      <c r="K40" s="91"/>
-      <c r="L40" s="91"/>
-      <c r="M40" s="91"/>
-      <c r="N40" s="91"/>
-      <c r="O40" s="91"/>
-      <c r="P40" s="91"/>
-      <c r="Q40" s="91"/>
-      <c r="R40" s="91"/>
-      <c r="S40" s="91"/>
-      <c r="T40" s="91"/>
-      <c r="U40" s="91"/>
-      <c r="V40" s="91"/>
-      <c r="W40" s="91"/>
-      <c r="X40" s="91"/>
-      <c r="Y40" s="91"/>
-      <c r="Z40" s="91"/>
-    </row>
-    <row r="41" customHeight="1" spans="2:26">
-      <c r="B41" s="106" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="98" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" s="98"/>
-      <c r="E41" s="98"/>
-      <c r="F41" s="98"/>
-      <c r="G41" s="98" t="s">
-        <v>86</v>
-      </c>
-      <c r="H41" s="91"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="91"/>
-      <c r="M41" s="91"/>
-      <c r="N41" s="91"/>
-      <c r="O41" s="91"/>
-      <c r="P41" s="91"/>
-      <c r="Q41" s="91"/>
-      <c r="R41" s="91"/>
-      <c r="S41" s="91"/>
-      <c r="T41" s="91"/>
-      <c r="U41" s="91"/>
-      <c r="V41" s="91"/>
-      <c r="W41" s="91"/>
-      <c r="X41" s="91"/>
-      <c r="Y41" s="91"/>
-      <c r="Z41" s="91"/>
-    </row>
-    <row r="42" customHeight="1" spans="2:26">
-      <c r="B42" s="106" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" s="98" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" s="98"/>
-      <c r="E42" s="98"/>
-      <c r="F42" s="98"/>
-      <c r="G42" s="98" t="s">
-        <v>89</v>
-      </c>
-      <c r="H42" s="91"/>
-      <c r="I42" s="91"/>
-      <c r="J42" s="91"/>
-      <c r="K42" s="91"/>
-      <c r="L42" s="91"/>
-      <c r="M42" s="91"/>
-      <c r="N42" s="91"/>
-      <c r="O42" s="91"/>
-      <c r="P42" s="91"/>
-      <c r="Q42" s="91"/>
-      <c r="R42" s="91"/>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
-      <c r="V42" s="91"/>
-      <c r="W42" s="91"/>
-      <c r="X42" s="91"/>
-      <c r="Y42" s="91"/>
-      <c r="Z42" s="91"/>
-    </row>
-    <row r="43" customHeight="1" spans="2:26">
-      <c r="B43" s="106" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" s="98" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43" s="98"/>
-      <c r="E43" s="98"/>
-      <c r="F43" s="98"/>
-      <c r="G43" s="98" t="s">
-        <v>91</v>
-      </c>
-      <c r="H43" s="91"/>
-      <c r="I43" s="91"/>
-      <c r="J43" s="91"/>
-      <c r="K43" s="91"/>
-      <c r="L43" s="91"/>
-      <c r="M43" s="91"/>
-      <c r="N43" s="91"/>
-      <c r="O43" s="91"/>
-      <c r="P43" s="91"/>
-      <c r="Q43" s="91"/>
-      <c r="R43" s="91"/>
-      <c r="S43" s="91"/>
-      <c r="T43" s="91"/>
-      <c r="U43" s="91"/>
-      <c r="V43" s="91"/>
-      <c r="W43" s="91"/>
-      <c r="X43" s="91"/>
-      <c r="Y43" s="91"/>
-      <c r="Z43" s="91"/>
-    </row>
-    <row r="45" customHeight="1" spans="2:26">
-      <c r="B45" s="103" t="s">
-        <v>43</v>
-      </c>
-      <c r="C45" s="104" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="104"/>
-      <c r="E45" s="104"/>
-      <c r="F45" s="104"/>
-      <c r="G45" s="105" t="s">
-        <v>45</v>
-      </c>
-      <c r="H45" s="105"/>
-      <c r="I45" s="105"/>
-      <c r="J45" s="105"/>
-      <c r="K45" s="105"/>
-      <c r="L45" s="105"/>
-      <c r="M45" s="105"/>
-      <c r="N45" s="105"/>
-      <c r="O45" s="105"/>
-      <c r="P45" s="105"/>
-      <c r="Q45" s="105"/>
-      <c r="R45" s="105"/>
-      <c r="S45" s="105"/>
-      <c r="T45" s="105"/>
-      <c r="U45" s="105"/>
-      <c r="V45" s="105"/>
-      <c r="W45" s="105"/>
-      <c r="X45" s="105"/>
-      <c r="Y45" s="105"/>
-      <c r="Z45" s="105"/>
-    </row>
-    <row r="46" customHeight="1" spans="2:26">
-      <c r="B46" s="106" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="98" t="s">
-        <v>92</v>
-      </c>
-      <c r="D46" s="98"/>
-      <c r="E46" s="98"/>
-      <c r="F46" s="98"/>
-      <c r="G46" s="98" t="s">
-        <v>83</v>
-      </c>
-      <c r="H46" s="91"/>
-      <c r="I46" s="91"/>
-      <c r="J46" s="91"/>
-      <c r="K46" s="91"/>
-      <c r="L46" s="91"/>
-      <c r="M46" s="91"/>
-      <c r="N46" s="91"/>
-      <c r="O46" s="91"/>
-      <c r="P46" s="91"/>
-      <c r="Q46" s="91"/>
-      <c r="R46" s="91"/>
-      <c r="S46" s="91"/>
-      <c r="T46" s="91"/>
-      <c r="U46" s="91"/>
-      <c r="V46" s="91"/>
-      <c r="W46" s="91"/>
-      <c r="X46" s="91"/>
-      <c r="Y46" s="91"/>
-      <c r="Z46" s="91"/>
-    </row>
-    <row r="47" customHeight="1" spans="2:26">
-      <c r="B47" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="98" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" s="98"/>
-      <c r="E47" s="98"/>
-      <c r="F47" s="98"/>
-      <c r="G47" s="98" t="s">
-        <v>95</v>
-      </c>
-      <c r="H47" s="91"/>
-      <c r="I47" s="91"/>
-      <c r="J47" s="91"/>
-      <c r="K47" s="91"/>
-      <c r="L47" s="91"/>
-      <c r="M47" s="91"/>
-      <c r="N47" s="91"/>
-      <c r="O47" s="91"/>
-      <c r="P47" s="91"/>
-      <c r="Q47" s="91"/>
-      <c r="R47" s="91"/>
-      <c r="S47" s="91"/>
-      <c r="T47" s="91"/>
-      <c r="U47" s="91"/>
-      <c r="V47" s="91"/>
-      <c r="W47" s="91"/>
-      <c r="X47" s="91"/>
-      <c r="Y47" s="91"/>
-      <c r="Z47" s="91"/>
-    </row>
-    <row r="48" customHeight="1" spans="2:26">
-      <c r="B48" s="106" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" s="98" t="s">
-        <v>94</v>
-      </c>
-      <c r="D48" s="98"/>
-      <c r="E48" s="98"/>
-      <c r="F48" s="98"/>
-      <c r="G48" s="98" t="s">
-        <v>86</v>
-      </c>
-      <c r="H48" s="91"/>
-      <c r="I48" s="91"/>
-      <c r="J48" s="91"/>
-      <c r="K48" s="91"/>
-      <c r="L48" s="91"/>
-      <c r="M48" s="91"/>
-      <c r="N48" s="91"/>
-      <c r="O48" s="91"/>
-      <c r="P48" s="91"/>
-      <c r="Q48" s="91"/>
-      <c r="R48" s="91"/>
-      <c r="S48" s="91"/>
-      <c r="T48" s="91"/>
-      <c r="U48" s="91"/>
-      <c r="V48" s="91"/>
-      <c r="W48" s="91"/>
-      <c r="X48" s="91"/>
-      <c r="Y48" s="91"/>
-      <c r="Z48" s="91"/>
-    </row>
-    <row r="49" customHeight="1" spans="2:26">
-      <c r="B49" s="106" t="s">
-        <v>87</v>
-      </c>
-      <c r="C49" s="98" t="s">
-        <v>88</v>
-      </c>
-      <c r="D49" s="98"/>
-      <c r="E49" s="98"/>
-      <c r="F49" s="98"/>
-      <c r="G49" s="98" t="s">
-        <v>89</v>
-      </c>
-      <c r="H49" s="91"/>
-      <c r="I49" s="91"/>
-      <c r="J49" s="91"/>
-      <c r="K49" s="91"/>
-      <c r="L49" s="91"/>
-      <c r="M49" s="91"/>
-      <c r="N49" s="91"/>
-      <c r="O49" s="91"/>
-      <c r="P49" s="91"/>
-      <c r="Q49" s="91"/>
-      <c r="R49" s="91"/>
-      <c r="S49" s="91"/>
-      <c r="T49" s="91"/>
-      <c r="U49" s="91"/>
-      <c r="V49" s="91"/>
-      <c r="W49" s="91"/>
-      <c r="X49" s="91"/>
-      <c r="Y49" s="91"/>
-      <c r="Z49" s="91"/>
-    </row>
-    <row r="50" customHeight="1" spans="2:26">
-      <c r="B50" s="106" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="98" t="s">
-        <v>90</v>
-      </c>
-      <c r="D50" s="98"/>
-      <c r="E50" s="98"/>
-      <c r="F50" s="98"/>
-      <c r="G50" s="98" t="s">
-        <v>91</v>
-      </c>
-      <c r="H50" s="91"/>
-      <c r="I50" s="91"/>
-      <c r="J50" s="91"/>
-      <c r="K50" s="91"/>
-      <c r="L50" s="91"/>
-      <c r="M50" s="91"/>
-      <c r="N50" s="91"/>
-      <c r="O50" s="91"/>
-      <c r="P50" s="91"/>
-      <c r="Q50" s="91"/>
-      <c r="R50" s="91"/>
-      <c r="S50" s="91"/>
-      <c r="T50" s="91"/>
-      <c r="U50" s="91"/>
-      <c r="V50" s="91"/>
-      <c r="W50" s="91"/>
-      <c r="X50" s="91"/>
-      <c r="Y50" s="91"/>
-      <c r="Z50" s="91"/>
-    </row>
-    <row r="52" customHeight="1" spans="2:26">
-      <c r="B52" s="107" t="s">
-        <v>43</v>
-      </c>
-      <c r="C52" s="108" t="s">
-        <v>31</v>
-      </c>
-      <c r="D52" s="108"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="109" t="s">
-        <v>45</v>
-      </c>
-      <c r="H52" s="109"/>
-      <c r="I52" s="109"/>
-      <c r="J52" s="109"/>
-      <c r="K52" s="109"/>
-      <c r="L52" s="109"/>
-      <c r="M52" s="109"/>
-      <c r="N52" s="109"/>
-      <c r="O52" s="109"/>
-      <c r="P52" s="109"/>
-      <c r="Q52" s="109"/>
-      <c r="R52" s="109"/>
-      <c r="S52" s="109"/>
-      <c r="T52" s="109"/>
-      <c r="U52" s="109"/>
-      <c r="V52" s="109"/>
-      <c r="W52" s="109"/>
-      <c r="X52" s="109"/>
-      <c r="Y52" s="109"/>
-      <c r="Z52" s="109"/>
-    </row>
-    <row r="53" customHeight="1" spans="2:26">
-      <c r="B53" s="110" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="111" t="s">
-        <v>96</v>
-      </c>
-      <c r="D53" s="111"/>
-      <c r="E53" s="111"/>
-      <c r="F53" s="111"/>
-      <c r="G53" s="98" t="s">
-        <v>83</v>
-      </c>
-      <c r="H53" s="91"/>
-      <c r="I53" s="91"/>
-      <c r="J53" s="91"/>
-      <c r="K53" s="91"/>
-      <c r="L53" s="91"/>
-      <c r="M53" s="91"/>
-      <c r="N53" s="91"/>
-      <c r="O53" s="91"/>
-      <c r="P53" s="91"/>
-      <c r="Q53" s="91"/>
-      <c r="R53" s="91"/>
-      <c r="S53" s="91"/>
-      <c r="T53" s="91"/>
-      <c r="U53" s="91"/>
-      <c r="V53" s="91"/>
-      <c r="W53" s="91"/>
-      <c r="X53" s="91"/>
-      <c r="Y53" s="91"/>
-      <c r="Z53" s="91"/>
-    </row>
-    <row r="54" customHeight="1" spans="2:26">
-      <c r="B54" s="110" t="s">
-        <v>49</v>
-      </c>
-      <c r="C54" s="111" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" s="111"/>
-      <c r="E54" s="111"/>
-      <c r="F54" s="111"/>
-      <c r="G54" s="98" t="s">
-        <v>98</v>
-      </c>
-      <c r="H54" s="91"/>
-      <c r="I54" s="91"/>
-      <c r="J54" s="91"/>
-      <c r="K54" s="91"/>
-      <c r="L54" s="91"/>
-      <c r="M54" s="91"/>
-      <c r="N54" s="91"/>
-      <c r="O54" s="91"/>
-      <c r="P54" s="91"/>
-      <c r="Q54" s="91"/>
-      <c r="R54" s="91"/>
-      <c r="S54" s="91"/>
-      <c r="T54" s="91"/>
-      <c r="U54" s="91"/>
-      <c r="V54" s="91"/>
-      <c r="W54" s="91"/>
-      <c r="X54" s="91"/>
-      <c r="Y54" s="91"/>
-      <c r="Z54" s="91"/>
-    </row>
-    <row r="55" customHeight="1" spans="2:26">
-      <c r="B55" s="110" t="s">
-        <v>93</v>
-      </c>
-      <c r="C55" s="98" t="s">
-        <v>37</v>
-      </c>
-      <c r="D55" s="98"/>
-      <c r="E55" s="98"/>
-      <c r="F55" s="98"/>
-      <c r="G55" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H55" s="91"/>
-      <c r="I55" s="91"/>
-      <c r="J55" s="91"/>
-      <c r="K55" s="91"/>
-      <c r="L55" s="91"/>
-      <c r="M55" s="91"/>
-      <c r="N55" s="91"/>
-      <c r="O55" s="91"/>
-      <c r="P55" s="91"/>
-      <c r="Q55" s="91"/>
-      <c r="R55" s="91"/>
-      <c r="S55" s="91"/>
-      <c r="T55" s="91"/>
-      <c r="U55" s="91"/>
-      <c r="V55" s="91"/>
-      <c r="W55" s="91"/>
-      <c r="X55" s="91"/>
-      <c r="Y55" s="91"/>
-      <c r="Z55" s="91"/>
-    </row>
-    <row r="56" customHeight="1" spans="2:26">
-      <c r="B56" s="110" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" s="98" t="s">
-        <v>100</v>
-      </c>
-      <c r="D56" s="98"/>
-      <c r="E56" s="98"/>
-      <c r="F56" s="98"/>
-      <c r="G56" s="98" t="s">
-        <v>101</v>
-      </c>
-      <c r="H56" s="91"/>
-      <c r="I56" s="91"/>
-      <c r="J56" s="91"/>
-      <c r="K56" s="91"/>
-      <c r="L56" s="91"/>
-      <c r="M56" s="91"/>
-      <c r="N56" s="91"/>
-      <c r="O56" s="91"/>
-      <c r="P56" s="91"/>
-      <c r="Q56" s="91"/>
-      <c r="R56" s="91"/>
-      <c r="S56" s="91"/>
-      <c r="T56" s="91"/>
-      <c r="U56" s="91"/>
-      <c r="V56" s="91"/>
-      <c r="W56" s="91"/>
-      <c r="X56" s="91"/>
-      <c r="Y56" s="91"/>
-      <c r="Z56" s="91"/>
-    </row>
-    <row r="57" customHeight="1" spans="2:26">
-      <c r="B57" s="110" t="s">
-        <v>102</v>
-      </c>
-      <c r="C57" s="98" t="s">
-        <v>103</v>
-      </c>
-      <c r="D57" s="98"/>
-      <c r="E57" s="98"/>
-      <c r="F57" s="98"/>
-      <c r="G57" s="98" t="s">
-        <v>104</v>
-      </c>
-      <c r="H57" s="91"/>
-      <c r="I57" s="91"/>
-      <c r="J57" s="91"/>
-      <c r="K57" s="91"/>
-      <c r="L57" s="91"/>
-      <c r="M57" s="91"/>
-      <c r="N57" s="91"/>
-      <c r="O57" s="91"/>
-      <c r="P57" s="91"/>
-      <c r="Q57" s="91"/>
-      <c r="R57" s="91"/>
-      <c r="S57" s="91"/>
-      <c r="T57" s="91"/>
-      <c r="U57" s="91"/>
-      <c r="V57" s="91"/>
-      <c r="W57" s="91"/>
-      <c r="X57" s="91"/>
-      <c r="Y57" s="91"/>
-      <c r="Z57" s="91"/>
-    </row>
-    <row r="58" customHeight="1" spans="2:26">
-      <c r="B58" s="110" t="s">
-        <v>56</v>
-      </c>
-      <c r="C58" s="98" t="s">
-        <v>105</v>
-      </c>
-      <c r="D58" s="98"/>
-      <c r="E58" s="98"/>
-      <c r="F58" s="98"/>
-      <c r="G58" s="98" t="s">
-        <v>61</v>
-      </c>
-      <c r="H58" s="91"/>
-      <c r="I58" s="91"/>
-      <c r="J58" s="91"/>
-      <c r="K58" s="91"/>
-      <c r="L58" s="91"/>
-      <c r="M58" s="91"/>
-      <c r="N58" s="91"/>
-      <c r="O58" s="91"/>
-      <c r="P58" s="91"/>
-      <c r="Q58" s="91"/>
-      <c r="R58" s="91"/>
-      <c r="S58" s="91"/>
-      <c r="T58" s="91"/>
-      <c r="U58" s="91"/>
-      <c r="V58" s="91"/>
-      <c r="W58" s="91"/>
-      <c r="X58" s="91"/>
-      <c r="Y58" s="91"/>
-      <c r="Z58" s="91"/>
-    </row>
-    <row r="59" customHeight="1" spans="2:26">
-      <c r="B59" s="110" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="98" t="s">
-        <v>63</v>
-      </c>
-      <c r="D59" s="98"/>
-      <c r="E59" s="98"/>
-      <c r="F59" s="98"/>
-      <c r="G59" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="H59" s="91"/>
-      <c r="I59" s="91"/>
-      <c r="J59" s="91"/>
-      <c r="K59" s="91"/>
-      <c r="L59" s="91"/>
-      <c r="M59" s="91"/>
-      <c r="N59" s="91"/>
-      <c r="O59" s="91"/>
-      <c r="P59" s="91"/>
-      <c r="Q59" s="91"/>
-      <c r="R59" s="91"/>
-      <c r="S59" s="91"/>
-      <c r="T59" s="91"/>
-      <c r="U59" s="91"/>
-      <c r="V59" s="91"/>
-      <c r="W59" s="91"/>
-      <c r="X59" s="91"/>
-      <c r="Y59" s="91"/>
-      <c r="Z59" s="91"/>
-    </row>
-    <row r="60" customHeight="1" spans="2:26">
-      <c r="B60" s="110" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60" s="98" t="s">
-        <v>107</v>
-      </c>
-      <c r="D60" s="98"/>
-      <c r="E60" s="98"/>
-      <c r="F60" s="98"/>
-      <c r="G60" s="98" t="s">
-        <v>108</v>
-      </c>
-      <c r="H60" s="91"/>
-      <c r="I60" s="91"/>
-      <c r="J60" s="91"/>
-      <c r="K60" s="91"/>
-      <c r="L60" s="91"/>
-      <c r="M60" s="91"/>
-      <c r="N60" s="91"/>
-      <c r="O60" s="91"/>
-      <c r="P60" s="91"/>
-      <c r="Q60" s="91"/>
-      <c r="R60" s="91"/>
-      <c r="S60" s="91"/>
-      <c r="T60" s="91"/>
-      <c r="U60" s="91"/>
-      <c r="V60" s="91"/>
-      <c r="W60" s="91"/>
-      <c r="X60" s="91"/>
-      <c r="Y60" s="91"/>
-      <c r="Z60" s="91"/>
+      <c r="C60" s="96" t="s">
+        <v>109</v>
+      </c>
+      <c r="D60" s="96"/>
+      <c r="E60" s="96"/>
+      <c r="F60" s="96"/>
+      <c r="G60" s="96" t="s">
+        <v>110</v>
+      </c>
+      <c r="H60" s="90"/>
+      <c r="I60" s="90"/>
+      <c r="J60" s="90"/>
+      <c r="K60" s="90"/>
+      <c r="L60" s="90"/>
+      <c r="M60" s="90"/>
+      <c r="N60" s="90"/>
+      <c r="O60" s="90"/>
+      <c r="P60" s="90"/>
+      <c r="Q60" s="90"/>
+      <c r="R60" s="90"/>
+      <c r="S60" s="90"/>
+      <c r="T60" s="90"/>
+      <c r="U60" s="90"/>
+      <c r="V60" s="90"/>
+      <c r="W60" s="90"/>
+      <c r="X60" s="90"/>
+      <c r="Y60" s="90"/>
+      <c r="Z60" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="91">
@@ -5479,11 +5649,11 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="K17:N17"/>
     <mergeCell ref="O17:Z17"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="K18:N18"/>
     <mergeCell ref="O18:Z18"/>
     <mergeCell ref="K19:N19"/>
     <mergeCell ref="O19:Z19"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="K20:N20"/>
     <mergeCell ref="O20:Z20"/>
     <mergeCell ref="A21:B21"/>
@@ -5559,13 +5729,13 @@
     <mergeCell ref="G60:Z60"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A19:E20"/>
+    <mergeCell ref="A18:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B57:B60 B53:B54 B46 B23:B25 B27:B31" numberStoredAsText="1"/>
+    <ignoredError sqref="B57:B60 B53:B55 B46 B23:B25 B27:B31" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5576,2025 +5746,2025 @@
   <dimension ref="A1:W33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="28" customWidth="1"/>
-    <col min="2" max="15" width="6.625" style="28" customWidth="1"/>
-    <col min="16" max="16" width="9" style="28"/>
-    <col min="17" max="17" width="15.625" style="28" customWidth="1"/>
-    <col min="18" max="18" width="20.625" style="28" customWidth="1"/>
-    <col min="19" max="19" width="9" style="28"/>
-    <col min="20" max="20" width="39.625" style="28" customWidth="1"/>
-    <col min="21" max="21" width="9.5" style="28" customWidth="1"/>
-    <col min="22" max="22" width="20.625" style="28" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="28"/>
+    <col min="1" max="1" width="15.625" style="25" customWidth="1"/>
+    <col min="2" max="15" width="6.625" style="25" customWidth="1"/>
+    <col min="16" max="16" width="9" style="25"/>
+    <col min="17" max="17" width="15.625" style="25" customWidth="1"/>
+    <col min="18" max="18" width="20.625" style="25" customWidth="1"/>
+    <col min="19" max="19" width="9" style="25"/>
+    <col min="20" max="20" width="39.625" style="25" customWidth="1"/>
+    <col min="21" max="21" width="9.5" style="25" customWidth="1"/>
+    <col min="22" max="22" width="20.625" style="25" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="30">
+      <c r="A1" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="27">
         <v>10</v>
       </c>
-      <c r="C1" s="30">
+      <c r="C1" s="27">
         <v>20</v>
       </c>
-      <c r="D1" s="30">
+      <c r="D1" s="27">
         <v>30</v>
       </c>
-      <c r="E1" s="30">
+      <c r="E1" s="27">
         <v>40</v>
       </c>
-      <c r="F1" s="31">
+      <c r="F1" s="28">
         <v>50</v>
       </c>
-      <c r="G1" s="30">
+      <c r="G1" s="27">
         <v>60</v>
       </c>
-      <c r="H1" s="31">
+      <c r="H1" s="28">
         <v>70</v>
       </c>
-      <c r="I1" s="30">
+      <c r="I1" s="27">
         <v>80</v>
       </c>
-      <c r="J1" s="30">
+      <c r="J1" s="27">
         <v>90</v>
       </c>
-      <c r="K1" s="30">
+      <c r="K1" s="27">
         <v>100</v>
       </c>
-      <c r="L1" s="30">
+      <c r="L1" s="27">
         <v>110</v>
       </c>
-      <c r="M1" s="30">
+      <c r="M1" s="27">
         <v>120</v>
       </c>
-      <c r="N1" s="30">
+      <c r="N1" s="27">
         <v>130</v>
       </c>
-      <c r="O1" s="38">
+      <c r="O1" s="35">
         <v>140</v>
       </c>
-      <c r="Q1" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="R1" s="39" t="s">
-        <v>111</v>
+      <c r="Q1" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="R1" s="36" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:18">
-      <c r="A2" s="32"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="38"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="35"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:18">
-      <c r="A3" s="33">
+      <c r="A3" s="30">
         <v>0</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="31">
         <f>ROUND($A3*B$1,0)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="31">
         <f t="shared" ref="C3:O3" si="0">ROUND($A3*C$1,0)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G3" s="34">
+      <c r="G3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J3" s="34">
+      <c r="J3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M3" s="34">
+      <c r="M3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N3" s="34">
+      <c r="N3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O3" s="34">
+      <c r="O3" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q3" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="R3" s="41" t="s">
-        <v>113</v>
+      <c r="Q3" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="R3" s="38" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:18">
-      <c r="A4" s="35">
+      <c r="A4" s="32">
         <v>0.01</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="33">
         <f>ROUND($A4*B$1,0)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="33">
         <f>ROUND($A4*C$1,0)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="33">
         <f>ROUND($A4*D$1,0)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="33">
         <f>ROUND($A4*E$1,0)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="33">
         <f>ROUND($A4*F$1,0)</f>
         <v>1</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="33">
         <f>ROUND($A4*G$1,0)</f>
         <v>1</v>
       </c>
-      <c r="H4" s="36">
+      <c r="H4" s="33">
         <f>ROUND($A4*H$1,0)</f>
         <v>1</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="33">
         <f>ROUND($A4*I$1,0)</f>
         <v>1</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="33">
         <f>ROUND($A4*J$1,0)</f>
         <v>1</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="33">
         <f>ROUND($A4*K$1,0)</f>
         <v>1</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="33">
         <f>ROUND($A4*L$1,0)</f>
         <v>1</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="33">
         <f>ROUND($A4*M$1,0)</f>
         <v>1</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="33">
         <f>ROUND($A4*N$1,0)</f>
         <v>1</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="33">
         <f>ROUND($A4*O$1,0)</f>
         <v>1</v>
       </c>
-      <c r="Q4" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="R4" s="41" t="s">
-        <v>115</v>
+      <c r="Q4" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="R4" s="38" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:18">
-      <c r="A5" s="37">
+      <c r="A5" s="34">
         <v>0.02</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="31">
         <f t="shared" ref="B5:B33" si="1">ROUND($A5*B$1,0)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="31">
         <f t="shared" ref="C5:C33" si="2">ROUND($A5*C$1,0)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="31">
         <f t="shared" ref="D5:D33" si="3">ROUND($A5*D$1,0)</f>
         <v>1</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="31">
         <f t="shared" ref="E5:E33" si="4">ROUND($A5*E$1,0)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="31">
         <f t="shared" ref="F5:F33" si="5">ROUND($A5*F$1,0)</f>
         <v>1</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="31">
         <f t="shared" ref="G5:G33" si="6">ROUND($A5*G$1,0)</f>
         <v>1</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="31">
         <f t="shared" ref="H5:H33" si="7">ROUND($A5*H$1,0)</f>
         <v>1</v>
       </c>
-      <c r="I5" s="34">
+      <c r="I5" s="31">
         <f t="shared" ref="I5:I33" si="8">ROUND($A5*I$1,0)</f>
         <v>2</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="31">
         <f t="shared" ref="J5:J33" si="9">ROUND($A5*J$1,0)</f>
         <v>2</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="31">
         <f t="shared" ref="K5:K33" si="10">ROUND($A5*K$1,0)</f>
         <v>2</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="31">
         <f t="shared" ref="L5:L33" si="11">ROUND($A5*L$1,0)</f>
         <v>2</v>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="31">
         <f t="shared" ref="M5:M33" si="12">ROUND($A5*M$1,0)</f>
         <v>2</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="31">
         <f t="shared" ref="N5:N33" si="13">ROUND($A5*N$1,0)</f>
         <v>3</v>
       </c>
-      <c r="O5" s="34">
+      <c r="O5" s="31">
         <f t="shared" ref="O5:O33" si="14">ROUND($A5*O$1,0)</f>
         <v>3</v>
       </c>
-      <c r="Q5" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="R5" s="41" t="s">
-        <v>117</v>
+      <c r="Q5" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="R5" s="38" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:18">
-      <c r="A6" s="35">
+      <c r="A6" s="32">
         <v>0.03</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="33">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="33">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="33">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="33">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="33">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="33">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="33">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="33">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="33">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="M6" s="36">
+      <c r="M6" s="33">
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="33">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="O6" s="36">
+      <c r="O6" s="33">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="Q6" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="R6" s="41" t="s">
-        <v>119</v>
+      <c r="Q6" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="R6" s="38" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:18">
-      <c r="A7" s="37">
+      <c r="A7" s="34">
         <v>0.04</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="31">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="31">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="31">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="31">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="31">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="31">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="31">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="31">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="31">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="31">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="M7" s="34">
+      <c r="M7" s="31">
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="31">
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="O7" s="34">
+      <c r="O7" s="31">
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="Q7" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="R7" s="41" t="s">
-        <v>121</v>
+      <c r="Q7" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="R7" s="38" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:18">
-      <c r="A8" s="35">
+      <c r="A8" s="32">
         <v>0.05</v>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="33">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="33">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="33">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="33">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="33">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="33">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="33">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="J8" s="36">
+      <c r="J8" s="33">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="K8" s="36">
+      <c r="K8" s="33">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="33">
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="M8" s="36">
+      <c r="M8" s="33">
         <f t="shared" si="12"/>
         <v>6</v>
       </c>
-      <c r="N8" s="36">
+      <c r="N8" s="33">
         <f t="shared" si="13"/>
         <v>7</v>
       </c>
-      <c r="O8" s="36">
+      <c r="O8" s="33">
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="Q8" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="R8" s="41" t="s">
-        <v>123</v>
+      <c r="Q8" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="R8" s="38" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:18">
-      <c r="A9" s="37">
+      <c r="A9" s="34">
         <v>0.06</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="31">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="31">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="31">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="31">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="31">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="31">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="31">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="31">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="K9" s="34">
+      <c r="K9" s="31">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="31">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="31">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="31">
         <f t="shared" si="13"/>
         <v>8</v>
       </c>
-      <c r="O9" s="34">
+      <c r="O9" s="31">
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="Q9" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="R9" s="41" t="s">
-        <v>125</v>
+      <c r="Q9" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="R9" s="38" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:18">
-      <c r="A10" s="35">
+      <c r="A10" s="32">
         <v>0.07</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="33">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="33">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="33">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="33">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="33">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="33">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="33">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="33">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="33">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="L10" s="36">
+      <c r="L10" s="33">
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="M10" s="36">
+      <c r="M10" s="33">
         <f t="shared" si="12"/>
         <v>8</v>
       </c>
-      <c r="N10" s="36">
+      <c r="N10" s="33">
         <f t="shared" si="13"/>
         <v>9</v>
       </c>
-      <c r="O10" s="36">
+      <c r="O10" s="33">
         <f t="shared" si="14"/>
         <v>10</v>
       </c>
-      <c r="Q10" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="R10" s="41" t="s">
-        <v>125</v>
+      <c r="Q10" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="R10" s="38" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:15">
-      <c r="A11" s="37">
+      <c r="A11" s="34">
         <v>0.08</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="31">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="31">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="31">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="31">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="31">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="31">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="31">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="31">
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="K11" s="34">
+      <c r="K11" s="31">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="31">
         <f t="shared" si="11"/>
         <v>9</v>
       </c>
-      <c r="M11" s="34">
+      <c r="M11" s="31">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="N11" s="34">
+      <c r="N11" s="31">
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="O11" s="34">
+      <c r="O11" s="31">
         <f t="shared" si="14"/>
         <v>11</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:15">
-      <c r="A12" s="35">
+      <c r="A12" s="32">
         <v>0.09</v>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="33">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="33">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="33">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="33">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="33">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="33">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="33">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="J12" s="36">
+      <c r="J12" s="33">
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="K12" s="36">
+      <c r="K12" s="33">
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
-      <c r="L12" s="36">
+      <c r="L12" s="33">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="M12" s="36">
+      <c r="M12" s="33">
         <f t="shared" si="12"/>
         <v>11</v>
       </c>
-      <c r="N12" s="36">
+      <c r="N12" s="33">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
-      <c r="O12" s="36">
+      <c r="O12" s="33">
         <f t="shared" si="14"/>
         <v>13</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:15">
-      <c r="A13" s="37">
+      <c r="A13" s="34">
         <v>0.1</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="31">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="31">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="31">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="31">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="31">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="31">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="31">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="J13" s="34">
+      <c r="J13" s="31">
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="K13" s="34">
+      <c r="K13" s="31">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="31">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
-      <c r="M13" s="34">
+      <c r="M13" s="31">
         <f t="shared" si="12"/>
         <v>12</v>
       </c>
-      <c r="N13" s="34">
+      <c r="N13" s="31">
         <f t="shared" si="13"/>
         <v>13</v>
       </c>
-      <c r="O13" s="34">
+      <c r="O13" s="31">
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:15">
-      <c r="A14" s="35">
+      <c r="A14" s="32">
         <v>0.11</v>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="33">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="33">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="33">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="33">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="33">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="33">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="33">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="J14" s="36">
+      <c r="J14" s="33">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="K14" s="36">
+      <c r="K14" s="33">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
-      <c r="L14" s="36">
+      <c r="L14" s="33">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="M14" s="36">
+      <c r="M14" s="33">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="N14" s="36">
+      <c r="N14" s="33">
         <f t="shared" si="13"/>
         <v>14</v>
       </c>
-      <c r="O14" s="36">
+      <c r="O14" s="33">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:15">
-      <c r="A15" s="37">
+      <c r="A15" s="34">
         <v>0.12</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="31">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="31">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="31">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="31">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="31">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="31">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="31">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="31">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="K15" s="34">
+      <c r="K15" s="31">
         <f t="shared" si="10"/>
         <v>12</v>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="31">
         <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="M15" s="34">
+      <c r="M15" s="31">
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="N15" s="34">
+      <c r="N15" s="31">
         <f t="shared" si="13"/>
         <v>16</v>
       </c>
-      <c r="O15" s="34">
+      <c r="O15" s="31">
         <f t="shared" si="14"/>
         <v>17</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:15">
-      <c r="A16" s="35">
+      <c r="A16" s="32">
         <v>0.13</v>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="33">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="33">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="33">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="33">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="33">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="33">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="33">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="J16" s="36">
+      <c r="J16" s="33">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="K16" s="36">
+      <c r="K16" s="33">
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
-      <c r="L16" s="36">
+      <c r="L16" s="33">
         <f t="shared" si="11"/>
         <v>14</v>
       </c>
-      <c r="M16" s="36">
+      <c r="M16" s="33">
         <f t="shared" si="12"/>
         <v>16</v>
       </c>
-      <c r="N16" s="36">
+      <c r="N16" s="33">
         <f t="shared" si="13"/>
         <v>17</v>
       </c>
-      <c r="O16" s="36">
+      <c r="O16" s="33">
         <f t="shared" si="14"/>
         <v>18</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:15">
-      <c r="A17" s="37">
+      <c r="A17" s="34">
         <v>0.14</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="31">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="31">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="31">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="31">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="31">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="31">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="I17" s="34">
+      <c r="I17" s="31">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J17" s="31">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="K17" s="34">
+      <c r="K17" s="31">
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="31">
         <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="M17" s="34">
+      <c r="M17" s="31">
         <f t="shared" si="12"/>
         <v>17</v>
       </c>
-      <c r="N17" s="34">
+      <c r="N17" s="31">
         <f t="shared" si="13"/>
         <v>18</v>
       </c>
-      <c r="O17" s="34">
+      <c r="O17" s="31">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:15">
-      <c r="A18" s="35">
+      <c r="A18" s="32">
         <v>0.15</v>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="33">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="33">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="33">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="33">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="33">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="33">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="33">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="I18" s="36">
+      <c r="I18" s="33">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="J18" s="36">
+      <c r="J18" s="33">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="K18" s="36">
+      <c r="K18" s="33">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
-      <c r="L18" s="36">
+      <c r="L18" s="33">
         <f t="shared" si="11"/>
         <v>17</v>
       </c>
-      <c r="M18" s="36">
+      <c r="M18" s="33">
         <f t="shared" si="12"/>
         <v>18</v>
       </c>
-      <c r="N18" s="36">
+      <c r="N18" s="33">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="O18" s="36">
+      <c r="O18" s="33">
         <f t="shared" si="14"/>
         <v>21</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:15">
-      <c r="A19" s="37">
+      <c r="A19" s="34">
         <v>0.16</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="31">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="31">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="31">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="31">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="31">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="31">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="I19" s="34">
+      <c r="I19" s="31">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="31">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="K19" s="34">
+      <c r="K19" s="31">
         <f t="shared" si="10"/>
         <v>16</v>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="31">
         <f t="shared" si="11"/>
         <v>18</v>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="31">
         <f t="shared" si="12"/>
         <v>19</v>
       </c>
-      <c r="N19" s="34">
+      <c r="N19" s="31">
         <f t="shared" si="13"/>
         <v>21</v>
       </c>
-      <c r="O19" s="34">
+      <c r="O19" s="31">
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:15">
-      <c r="A20" s="35">
+      <c r="A20" s="32">
         <v>0.17</v>
       </c>
-      <c r="B20" s="36">
+      <c r="B20" s="33">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="33">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="33">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="33">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="33">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="33">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="33">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="33">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="J20" s="36">
+      <c r="J20" s="33">
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="K20" s="36">
+      <c r="K20" s="33">
         <f t="shared" si="10"/>
         <v>17</v>
       </c>
-      <c r="L20" s="36">
+      <c r="L20" s="33">
         <f t="shared" si="11"/>
         <v>19</v>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="33">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="N20" s="36">
+      <c r="N20" s="33">
         <f t="shared" si="13"/>
         <v>22</v>
       </c>
-      <c r="O20" s="36">
+      <c r="O20" s="33">
         <f t="shared" si="14"/>
         <v>24</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:15">
-      <c r="A21" s="37">
+      <c r="A21" s="34">
         <v>0.18</v>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="31">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="31">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="31">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="31">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="31">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="31">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="31">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="J21" s="34">
+      <c r="J21" s="31">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="K21" s="34">
+      <c r="K21" s="31">
         <f t="shared" si="10"/>
         <v>18</v>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="31">
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="M21" s="34">
+      <c r="M21" s="31">
         <f t="shared" si="12"/>
         <v>22</v>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="31">
         <f t="shared" si="13"/>
         <v>23</v>
       </c>
-      <c r="O21" s="34">
+      <c r="O21" s="31">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:15">
-      <c r="A22" s="35">
+      <c r="A22" s="32">
         <v>0.19</v>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="33">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="33">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="33">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="33">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="33">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="33">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="33">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="33">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="J22" s="36">
+      <c r="J22" s="33">
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="33">
         <f t="shared" si="10"/>
         <v>19</v>
       </c>
-      <c r="L22" s="36">
+      <c r="L22" s="33">
         <f t="shared" si="11"/>
         <v>21</v>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="33">
         <f t="shared" si="12"/>
         <v>23</v>
       </c>
-      <c r="N22" s="36">
+      <c r="N22" s="33">
         <f t="shared" si="13"/>
         <v>25</v>
       </c>
-      <c r="O22" s="36">
+      <c r="O22" s="33">
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:15">
-      <c r="A23" s="37">
+      <c r="A23" s="34">
         <v>0.2</v>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="31">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="31">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="31">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="31">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="31">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="I23" s="34">
+      <c r="I23" s="31">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="J23" s="34">
+      <c r="J23" s="31">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="K23" s="34">
+      <c r="K23" s="31">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="31">
         <f t="shared" si="11"/>
         <v>22</v>
       </c>
-      <c r="M23" s="34">
+      <c r="M23" s="31">
         <f t="shared" si="12"/>
         <v>24</v>
       </c>
-      <c r="N23" s="34">
+      <c r="N23" s="31">
         <f t="shared" si="13"/>
         <v>26</v>
       </c>
-      <c r="O23" s="34">
+      <c r="O23" s="31">
         <f t="shared" si="14"/>
         <v>28</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:15">
-      <c r="A24" s="35">
+      <c r="A24" s="32">
         <v>0.21</v>
       </c>
-      <c r="B24" s="36">
+      <c r="B24" s="33">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="33">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="33">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="33">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="33">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="33">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="33">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="I24" s="36">
+      <c r="I24" s="33">
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="J24" s="36">
+      <c r="J24" s="33">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="33">
         <f t="shared" si="10"/>
         <v>21</v>
       </c>
-      <c r="L24" s="36">
+      <c r="L24" s="33">
         <f t="shared" si="11"/>
         <v>23</v>
       </c>
-      <c r="M24" s="36">
+      <c r="M24" s="33">
         <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="N24" s="36">
+      <c r="N24" s="33">
         <f t="shared" si="13"/>
         <v>27</v>
       </c>
-      <c r="O24" s="36">
+      <c r="O24" s="33">
         <f t="shared" si="14"/>
         <v>29</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:15">
-      <c r="A25" s="37">
+      <c r="A25" s="34">
         <v>0.22</v>
       </c>
-      <c r="B25" s="34">
+      <c r="B25" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="31">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="31">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="31">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="31">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="31">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="31">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="31">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="J25" s="34">
+      <c r="J25" s="31">
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="K25" s="34">
+      <c r="K25" s="31">
         <f t="shared" si="10"/>
         <v>22</v>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="31">
         <f t="shared" si="11"/>
         <v>24</v>
       </c>
-      <c r="M25" s="34">
+      <c r="M25" s="31">
         <f t="shared" si="12"/>
         <v>26</v>
       </c>
-      <c r="N25" s="34">
+      <c r="N25" s="31">
         <f t="shared" si="13"/>
         <v>29</v>
       </c>
-      <c r="O25" s="34">
+      <c r="O25" s="31">
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:15">
-      <c r="A26" s="35">
+      <c r="A26" s="32">
         <v>0.23</v>
       </c>
-      <c r="B26" s="36">
+      <c r="B26" s="33">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="33">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="33">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="33">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="33">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="33">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="H26" s="36">
+      <c r="H26" s="33">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
-      <c r="I26" s="36">
+      <c r="I26" s="33">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="J26" s="36">
+      <c r="J26" s="33">
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="K26" s="36">
+      <c r="K26" s="33">
         <f t="shared" si="10"/>
         <v>23</v>
       </c>
-      <c r="L26" s="36">
+      <c r="L26" s="33">
         <f t="shared" si="11"/>
         <v>25</v>
       </c>
-      <c r="M26" s="36">
+      <c r="M26" s="33">
         <f t="shared" si="12"/>
         <v>28</v>
       </c>
-      <c r="N26" s="36">
+      <c r="N26" s="33">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
-      <c r="O26" s="36">
+      <c r="O26" s="33">
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:15">
-      <c r="A27" s="37">
+      <c r="A27" s="34">
         <v>0.24</v>
       </c>
-      <c r="B27" s="34">
+      <c r="B27" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="31">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="31">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="31">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="31">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="31">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="31">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="31">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J27" s="31">
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K27" s="31">
         <f t="shared" si="10"/>
         <v>24</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="31">
         <f t="shared" si="11"/>
         <v>26</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="31">
         <f t="shared" si="12"/>
         <v>29</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="31">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="31">
         <f t="shared" si="14"/>
         <v>34</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:15">
-      <c r="A28" s="35">
+      <c r="A28" s="32">
         <v>0.25</v>
       </c>
-      <c r="B28" s="36">
+      <c r="B28" s="33">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C28" s="36">
+      <c r="C28" s="33">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D28" s="36">
+      <c r="D28" s="33">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="33">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F28" s="36">
+      <c r="F28" s="33">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="G28" s="36">
+      <c r="G28" s="33">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="H28" s="36">
+      <c r="H28" s="33">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="I28" s="36">
+      <c r="I28" s="33">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="J28" s="36">
+      <c r="J28" s="33">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="K28" s="36">
+      <c r="K28" s="33">
         <f t="shared" si="10"/>
         <v>25</v>
       </c>
-      <c r="L28" s="36">
+      <c r="L28" s="33">
         <f t="shared" si="11"/>
         <v>28</v>
       </c>
-      <c r="M28" s="36">
+      <c r="M28" s="33">
         <f t="shared" si="12"/>
         <v>30</v>
       </c>
-      <c r="N28" s="36">
+      <c r="N28" s="33">
         <f t="shared" si="13"/>
         <v>33</v>
       </c>
-      <c r="O28" s="36">
+      <c r="O28" s="33">
         <f t="shared" si="14"/>
         <v>35</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:15">
-      <c r="A29" s="37">
+      <c r="A29" s="34">
         <v>0.26</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="31">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="31">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="31">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E29" s="31">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="31">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="31">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="31">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="I29" s="34">
+      <c r="I29" s="31">
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="J29" s="34">
+      <c r="J29" s="31">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="K29" s="34">
+      <c r="K29" s="31">
         <f t="shared" si="10"/>
         <v>26</v>
       </c>
-      <c r="L29" s="34">
+      <c r="L29" s="31">
         <f t="shared" si="11"/>
         <v>29</v>
       </c>
-      <c r="M29" s="34">
+      <c r="M29" s="31">
         <f t="shared" si="12"/>
         <v>31</v>
       </c>
-      <c r="N29" s="34">
+      <c r="N29" s="31">
         <f t="shared" si="13"/>
         <v>34</v>
       </c>
-      <c r="O29" s="34">
+      <c r="O29" s="31">
         <f t="shared" si="14"/>
         <v>36</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:15">
-      <c r="A30" s="35">
+      <c r="A30" s="32">
         <v>0.27</v>
       </c>
-      <c r="B30" s="36">
+      <c r="B30" s="33">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="33">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="33">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="33">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="33">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="33">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="33">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="33">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="33">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="33">
         <f t="shared" si="10"/>
         <v>27</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="33">
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="33">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="33">
         <f t="shared" si="13"/>
         <v>35</v>
       </c>
-      <c r="O30" s="36">
+      <c r="O30" s="33">
         <f t="shared" si="14"/>
         <v>38</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:15">
-      <c r="A31" s="37">
+      <c r="A31" s="34">
         <v>0.28</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="31">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="31">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="31">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="31">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="31">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="31">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="31">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="31">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="31">
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="K31" s="34">
+      <c r="K31" s="31">
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="31">
         <f t="shared" si="11"/>
         <v>31</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="31">
         <f t="shared" si="12"/>
         <v>34</v>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="31">
         <f t="shared" si="13"/>
         <v>36</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="31">
         <f t="shared" si="14"/>
         <v>39</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:15">
-      <c r="A32" s="35">
+      <c r="A32" s="32">
         <v>0.29</v>
       </c>
-      <c r="B32" s="36">
+      <c r="B32" s="33">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C32" s="36">
+      <c r="C32" s="33">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D32" s="36">
+      <c r="D32" s="33">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="33">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="F32" s="36">
+      <c r="F32" s="33">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="G32" s="36">
+      <c r="G32" s="33">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="H32" s="36">
+      <c r="H32" s="33">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="I32" s="36">
+      <c r="I32" s="33">
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="J32" s="36">
+      <c r="J32" s="33">
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="K32" s="36">
+      <c r="K32" s="33">
         <f t="shared" si="10"/>
         <v>29</v>
       </c>
-      <c r="L32" s="36">
+      <c r="L32" s="33">
         <f t="shared" si="11"/>
         <v>32</v>
       </c>
-      <c r="M32" s="36">
+      <c r="M32" s="33">
         <f t="shared" si="12"/>
         <v>35</v>
       </c>
-      <c r="N32" s="36">
+      <c r="N32" s="33">
         <f t="shared" si="13"/>
         <v>38</v>
       </c>
-      <c r="O32" s="36">
+      <c r="O32" s="33">
         <f t="shared" si="14"/>
         <v>41</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:15">
-      <c r="A33" s="37">
+      <c r="A33" s="34">
         <v>0.3</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="31">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="31">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="31">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="31">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="31">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="31">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="31">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="31">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="31">
         <f t="shared" si="9"/>
         <v>27</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="31">
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="31">
         <f t="shared" si="11"/>
         <v>33</v>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="31">
         <f t="shared" si="12"/>
         <v>36</v>
       </c>
-      <c r="N33" s="34">
+      <c r="N33" s="31">
         <f t="shared" si="13"/>
         <v>39</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="31">
         <f t="shared" si="14"/>
         <v>42</v>
       </c>
@@ -7633,204 +7803,238 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="39.625" style="21" customWidth="1"/>
-    <col min="2" max="2" width="9.5" style="21" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="21"/>
+    <col min="1" max="1" width="39.625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="17" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="1:2">
-      <c r="A1" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" ht="20.25" spans="1:2">
-      <c r="A2" s="24" t="s">
+    <row r="1" customHeight="1" spans="1:2">
+      <c r="A1" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B1" s="19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="3" ht="20.25" spans="1:2">
-      <c r="A3" s="24" t="s">
+    <row r="2" customHeight="1" spans="1:2">
+      <c r="A2" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" ht="20.25" spans="1:2">
-      <c r="A4" s="24" t="s">
+    <row r="3" customHeight="1" spans="1:2">
+      <c r="A3" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B3" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:2">
+      <c r="A4" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:2">
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:2">
+      <c r="A6" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" ht="20.25" spans="1:2">
-      <c r="A5" s="24" t="s">
+    <row r="7" customHeight="1" spans="1:2">
+      <c r="A7" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="22">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:2">
+      <c r="A9" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:2">
+      <c r="A11" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:2">
+      <c r="A12" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" ht="20.25" spans="1:2">
-      <c r="A6" s="24"/>
-      <c r="B6" s="26"/>
-    </row>
-    <row r="7" ht="20.25" spans="1:2">
-      <c r="A7" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" ht="20.25" spans="1:2">
-      <c r="A8" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="25" t="s">
+    </row>
+    <row r="13" customHeight="1" spans="1:2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="23"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:2">
+      <c r="A14" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:2">
+      <c r="A15" s="20"/>
+      <c r="B15" s="23"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:2">
+      <c r="A16" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:2">
+      <c r="A17" s="20"/>
+      <c r="B17" s="23"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:2">
+      <c r="A18" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="9" ht="20.25" spans="1:2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="26"/>
-    </row>
-    <row r="10" ht="20.25" spans="1:2">
-      <c r="A10" s="24" t="s">
+    <row r="19" customHeight="1" spans="1:2">
+      <c r="A19" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" ht="20.25" spans="1:2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="26"/>
-    </row>
-    <row r="12" ht="20.25" spans="1:2">
-      <c r="A12" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" ht="20.25" spans="1:2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="26"/>
-    </row>
-    <row r="14" ht="20.25" spans="1:2">
-      <c r="A14" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" ht="20.25" spans="1:2">
-      <c r="A15" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" ht="20.25" spans="1:2">
-      <c r="A16" s="24"/>
-      <c r="B16" s="26"/>
-    </row>
-    <row r="17" ht="20.25" spans="1:2">
-      <c r="A17" s="24" t="s">
+    </row>
+    <row r="20" customHeight="1" spans="1:2">
+      <c r="A20" s="20"/>
+      <c r="B20" s="23"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:2">
+      <c r="A21" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:2">
+      <c r="A22" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="B17" s="25" t="s">
+    </row>
+    <row r="23" customHeight="1" spans="1:2">
+      <c r="A23" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="18" ht="20.25" spans="1:2">
-      <c r="A18" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" ht="20.25" spans="1:2">
-      <c r="A19" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" ht="20.25" spans="1:2">
-      <c r="A20" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="21" ht="20.25" spans="1:2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="26"/>
-    </row>
-    <row r="22" ht="20.25" spans="1:2">
-      <c r="A22" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="25" t="s">
+    <row r="24" customHeight="1" spans="1:2">
+      <c r="A24" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:2">
+      <c r="A25" s="20"/>
+      <c r="B25" s="23"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:2">
+      <c r="A26" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:2">
+      <c r="A27" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="23" ht="20.25" spans="1:2">
-      <c r="A23" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" ht="20.25" spans="1:2">
-      <c r="A24" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" ht="21" spans="1:2">
-      <c r="A25" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" ht="19.5" spans="1:2">
-      <c r="A26" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="B26" s="27"/>
+    <row r="28" customHeight="1" spans="1:2">
+      <c r="A28" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:2">
+      <c r="A29" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:2">
+      <c r="A30" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="24"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:1">
+      <c r="A31" s="17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:1">
+      <c r="A32" s="17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:1">
+      <c r="A33" s="17" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A26:B26"/>
+  <mergeCells count="4">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B2:B25" numberStoredAsText="1"/>
+    <ignoredError sqref="B6:B9 B2:B4 B11:B29" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7838,8 +8042,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="34.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
@@ -7851,18 +8055,21 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" spans="1:5">
+        <v>162</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="H1" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -7876,128 +8083,146 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" spans="1:5">
-      <c r="A3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" spans="1:5">
-      <c r="A4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" spans="1:5">
-      <c r="A5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" ht="15.75" spans="1:5">
-      <c r="A6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" ht="15.75" spans="1:5">
-      <c r="A7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="8"/>
+      <c r="H2" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="H5" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="H6" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="H7" s="4" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="8" ht="15.75" spans="1:5">
-      <c r="A8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>166</v>
+      <c r="A8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:5">
-      <c r="A9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" s="8"/>
+      <c r="A9" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="7"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+        <v>162</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2"/>
@@ -8015,122 +8240,95 @@
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:5">
-      <c r="A13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="A13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" spans="1:5">
+      <c r="A14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="14" ht="15.75" spans="1:5">
-      <c r="A14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E14" s="9"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" ht="15.75" spans="1:5">
-      <c r="A15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="8"/>
+      <c r="A15" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" ht="15.75" spans="1:5">
-      <c r="A16" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E16" s="11"/>
+      <c r="A16" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" ht="15.75" spans="1:5">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" ht="15.75" spans="1:5">
-      <c r="A18" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="B18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" spans="1:5">
-      <c r="A19" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="B19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" spans="1:5">
-      <c r="A20" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="20"/>
-      <c r="E21" s="17" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22" spans="5:5">
-      <c r="E22" s="17" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="5:5">
-      <c r="E23" s="17" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="5:5">
-      <c r="E24" s="17" t="s">
-        <v>181</v>
-      </c>
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" ht="15.75" spans="1:4">
+      <c r="A18" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="D18" s="13"/>
+    </row>
+    <row r="19" ht="15.75" spans="1:4">
+      <c r="A19" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="D19" s="13"/>
+    </row>
+    <row r="20" ht="15.75" spans="1:1">
+      <c r="A20" s="15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
